--- a/research/traditional_assets/database/data/finland/finland_restaurant_dining.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_restaurant_dining.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="hlse_noho" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,46 +590,49 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0272</v>
+        <v>0.112</v>
+      </c>
+      <c r="E2">
+        <v>-0.117</v>
       </c>
       <c r="F2">
-        <v>0.341</v>
+        <v>-0.188</v>
       </c>
       <c r="G2">
-        <v>-0.07920792079207921</v>
+        <v>0.008472121650977552</v>
       </c>
       <c r="H2">
-        <v>-0.07920792079207921</v>
+        <v>0.008472121650977552</v>
       </c>
       <c r="I2">
-        <v>-0.209668025626092</v>
+        <v>0.06806661839246923</v>
       </c>
       <c r="J2">
-        <v>-0.209668025626092</v>
+        <v>0.0465015869578458</v>
       </c>
       <c r="K2">
-        <v>-26</v>
+        <v>3.1</v>
       </c>
       <c r="L2">
-        <v>-0.151426907396622</v>
+        <v>0.0112237509051412</v>
       </c>
       <c r="M2">
-        <v>0.957</v>
+        <v>0.098</v>
       </c>
       <c r="N2">
-        <v>0.005772014475271411</v>
+        <v>0.0006603773584905661</v>
       </c>
       <c r="O2">
-        <v>-0.03680769230769231</v>
+        <v>0.03161290322580645</v>
       </c>
       <c r="P2">
-        <v>0.957</v>
+        <v>0.098</v>
       </c>
       <c r="Q2">
-        <v>0.005772014475271411</v>
+        <v>0.0006603773584905661</v>
       </c>
       <c r="R2">
-        <v>-0.03680769230769231</v>
+        <v>0.03161290322580645</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +641,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>12.6</v>
+        <v>4.41</v>
       </c>
       <c r="V2">
-        <v>0.07599517490952955</v>
+        <v>0.02971698113207547</v>
       </c>
       <c r="W2">
-        <v>-0.2559055118110236</v>
+        <v>0.04234972677595628</v>
       </c>
       <c r="X2">
-        <v>0.141577842516539</v>
+        <v>0.1823556465042398</v>
       </c>
       <c r="Y2">
-        <v>-0.3974833543275627</v>
+        <v>-0.1400059197282836</v>
       </c>
       <c r="Z2">
-        <v>0.5810490693739423</v>
+        <v>0.9660720531654425</v>
       </c>
       <c r="AA2">
-        <v>-0.1218274111675127</v>
+        <v>0.04492388358781746</v>
       </c>
       <c r="AB2">
-        <v>0.06028364478534072</v>
+        <v>0.08837870263121278</v>
       </c>
       <c r="AC2">
-        <v>-0.1821110559528534</v>
+        <v>-0.04345481904339532</v>
       </c>
       <c r="AD2">
-        <v>382.8</v>
+        <v>299.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>382.8</v>
+        <v>299.1</v>
       </c>
       <c r="AG2">
-        <v>370.2</v>
+        <v>294.69</v>
       </c>
       <c r="AH2">
-        <v>0.6977761574917973</v>
+        <v>0.6683798882681565</v>
       </c>
       <c r="AI2">
-        <v>0.8332607749238138</v>
+        <v>0.7856579984239558</v>
       </c>
       <c r="AJ2">
-        <v>0.6906716417910448</v>
+        <v>0.6650793292559073</v>
       </c>
       <c r="AK2">
-        <v>0.8285586392121755</v>
+        <v>0.7831459778362434</v>
       </c>
       <c r="AL2">
-        <v>13.4</v>
+        <v>12.2</v>
       </c>
       <c r="AM2">
-        <v>12.35</v>
+        <v>11.238</v>
       </c>
       <c r="AN2">
-        <v>-30.624</v>
+        <v>9.806557377049181</v>
       </c>
       <c r="AO2">
-        <v>-2.686567164179104</v>
+        <v>1.540983606557377</v>
       </c>
       <c r="AP2">
-        <v>-29.616</v>
+        <v>9.661967213114753</v>
       </c>
       <c r="AQ2">
-        <v>-2.91497975708502</v>
+        <v>1.672895533012992</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +727,49 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0272</v>
+        <v>0.112</v>
+      </c>
+      <c r="E3">
+        <v>-0.117</v>
       </c>
       <c r="F3">
-        <v>0.341</v>
+        <v>-0.188</v>
       </c>
       <c r="G3">
-        <v>-0.07920792079207921</v>
+        <v>0.008472121650977552</v>
       </c>
       <c r="H3">
-        <v>-0.07920792079207921</v>
+        <v>0.008472121650977552</v>
       </c>
       <c r="I3">
-        <v>-0.209668025626092</v>
+        <v>0.06806661839246923</v>
       </c>
       <c r="J3">
-        <v>-0.209668025626092</v>
+        <v>0.0465015869578458</v>
       </c>
       <c r="K3">
-        <v>-26</v>
+        <v>3.1</v>
       </c>
       <c r="L3">
-        <v>-0.151426907396622</v>
+        <v>0.0112237509051412</v>
       </c>
       <c r="M3">
-        <v>0.957</v>
+        <v>0.098</v>
       </c>
       <c r="N3">
-        <v>0.005772014475271411</v>
+        <v>0.0006603773584905661</v>
       </c>
       <c r="O3">
-        <v>-0.03680769230769231</v>
+        <v>0.03161290322580645</v>
       </c>
       <c r="P3">
-        <v>0.957</v>
+        <v>0.098</v>
       </c>
       <c r="Q3">
-        <v>0.005772014475271411</v>
+        <v>0.0006603773584905661</v>
       </c>
       <c r="R3">
-        <v>-0.03680769230769231</v>
+        <v>0.03161290322580645</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +778,8774 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>12.6</v>
+        <v>4.41</v>
       </c>
       <c r="V3">
-        <v>0.07599517490952955</v>
+        <v>0.02971698113207547</v>
       </c>
       <c r="W3">
-        <v>-0.2559055118110236</v>
+        <v>0.04234972677595628</v>
       </c>
       <c r="X3">
-        <v>0.141577842516539</v>
+        <v>0.1823556465042398</v>
       </c>
       <c r="Y3">
-        <v>-0.3974833543275627</v>
+        <v>-0.1400059197282836</v>
       </c>
       <c r="Z3">
-        <v>0.5810490693739423</v>
+        <v>0.9660720531654425</v>
       </c>
       <c r="AA3">
-        <v>-0.1218274111675127</v>
+        <v>0.04492388358781746</v>
       </c>
       <c r="AB3">
-        <v>0.06028364478534072</v>
+        <v>0.08837870263121278</v>
       </c>
       <c r="AC3">
-        <v>-0.1821110559528534</v>
+        <v>-0.04345481904339532</v>
       </c>
       <c r="AD3">
-        <v>382.8</v>
+        <v>299.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>382.8</v>
+        <v>299.1</v>
       </c>
       <c r="AG3">
-        <v>370.2</v>
+        <v>294.69</v>
       </c>
       <c r="AH3">
-        <v>0.6977761574917973</v>
+        <v>0.6683798882681565</v>
       </c>
       <c r="AI3">
-        <v>0.8332607749238138</v>
+        <v>0.7856579984239558</v>
       </c>
       <c r="AJ3">
-        <v>0.6906716417910448</v>
+        <v>0.6650793292559073</v>
       </c>
       <c r="AK3">
-        <v>0.8285586392121755</v>
+        <v>0.7831459778362434</v>
       </c>
       <c r="AL3">
-        <v>13.4</v>
+        <v>12.2</v>
       </c>
       <c r="AM3">
-        <v>12.35</v>
+        <v>11.238</v>
       </c>
       <c r="AN3">
-        <v>-30.624</v>
+        <v>9.806557377049181</v>
       </c>
       <c r="AO3">
-        <v>-2.686567164179104</v>
+        <v>1.540983606557377</v>
       </c>
       <c r="AP3">
-        <v>-29.616</v>
+        <v>9.661967213114753</v>
       </c>
       <c r="AQ3">
-        <v>-2.91497975708502</v>
+        <v>1.672895533012992</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NoHo Partners Oyj (HLSE:NOHO)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HLSE:NOHO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Restaurant/Dining</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.668379888268157</v>
+      </c>
+      <c r="F2">
+        <v>0.01</v>
+      </c>
+      <c r="G2">
+        <v>148.4</v>
+      </c>
+      <c r="H2">
+        <v>342.653779409854</v>
+      </c>
+      <c r="I2">
+        <v>443.09</v>
+      </c>
+      <c r="J2">
+        <v>342.718779409854</v>
+      </c>
+      <c r="K2">
+        <v>299.1</v>
+      </c>
+      <c r="L2">
+        <v>4.475</v>
+      </c>
+      <c r="M2">
+        <v>0.08837870263121279</v>
+      </c>
+      <c r="N2">
+        <v>0.102898697441359</v>
+      </c>
+      <c r="O2">
+        <v>0.0417515596330275</v>
+      </c>
+      <c r="P2">
+        <v>0.8198055865921789</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.18235564650424</v>
+      </c>
+      <c r="T2">
+        <v>0.09565721371256281</v>
+      </c>
+      <c r="U2">
+        <v>2.1737819127401</v>
+      </c>
+      <c r="V2">
+        <v>0.860956610115068</v>
+      </c>
+      <c r="W2">
+        <v>-12.16510859698867</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>148.4</v>
+      </c>
+      <c r="AB2">
+        <v>0.0660395809086869</v>
+      </c>
+      <c r="AC2">
+        <v>0.05218944954128441</v>
+      </c>
+      <c r="AD2">
+        <v>0.2</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>30.5</v>
+      </c>
+      <c r="AH2">
+        <v>43.5</v>
+      </c>
+      <c r="AI2">
+        <v>17.62</v>
+      </c>
+      <c r="AJ2">
+        <v>299.1</v>
+      </c>
+      <c r="AK2">
+        <v>299.1</v>
+      </c>
+      <c r="AL2">
+        <v>12.2</v>
+      </c>
+      <c r="AM2">
+        <v>299.1</v>
+      </c>
+      <c r="AN2">
+        <v>4.41</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>-299.1</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>4.41</v>
+      </c>
+      <c r="H2">
+        <v>148.4</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>30.5</v>
+      </c>
+      <c r="K2">
+        <v>43.5</v>
+      </c>
+      <c r="L2">
+        <v>-13</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>-13</v>
+      </c>
+      <c r="O2">
+        <v>-2.6</v>
+      </c>
+      <c r="P2">
+        <v>-10.4</v>
+      </c>
+      <c r="Q2">
+        <v>33.1</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>-Inf</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.102898697441359</v>
+      </c>
+      <c r="C3">
+        <v>342.6537794098538</v>
+      </c>
+      <c r="D3">
+        <v>342.7187794098538</v>
+      </c>
+      <c r="E3">
+        <v>-294.625</v>
+      </c>
+      <c r="F3">
+        <v>4.475000000000001</v>
+      </c>
+      <c r="G3">
+        <v>4.41</v>
+      </c>
+      <c r="H3">
+        <v>148.4</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>30.5</v>
+      </c>
+      <c r="K3">
+        <v>43.5</v>
+      </c>
+      <c r="L3">
+        <v>-13</v>
+      </c>
+      <c r="M3">
+        <v>1.06863</v>
+      </c>
+      <c r="N3">
+        <v>-14.06863</v>
+      </c>
+      <c r="O3">
+        <v>-2.813726</v>
+      </c>
+      <c r="P3">
+        <v>-11.254904</v>
+      </c>
+      <c r="Q3">
+        <v>32.245096</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.09565721371256283</v>
+      </c>
+      <c r="T3">
+        <v>0.8609566101150677</v>
+      </c>
+      <c r="U3">
+        <v>0.2388</v>
+      </c>
+      <c r="V3">
+        <v>-2.433021719397733</v>
+      </c>
+      <c r="W3">
+        <v>0.8198055865921786</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>-12.16510859698867</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.104898697441359</v>
+      </c>
+      <c r="C4">
+        <v>327.8088691793563</v>
+      </c>
+      <c r="D4">
+        <v>332.3488691793563</v>
+      </c>
+      <c r="E4">
+        <v>-290.15</v>
+      </c>
+      <c r="F4">
+        <v>8.950000000000001</v>
+      </c>
+      <c r="G4">
+        <v>4.41</v>
+      </c>
+      <c r="H4">
+        <v>148.4</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>30.5</v>
+      </c>
+      <c r="K4">
+        <v>43.5</v>
+      </c>
+      <c r="L4">
+        <v>-13</v>
+      </c>
+      <c r="M4">
+        <v>2.13726</v>
+      </c>
+      <c r="N4">
+        <v>-15.13726</v>
+      </c>
+      <c r="O4">
+        <v>-3.027451999999999</v>
+      </c>
+      <c r="P4">
+        <v>-12.109808</v>
+      </c>
+      <c r="Q4">
+        <v>31.390192</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.09623738936269102</v>
+      </c>
+      <c r="T4">
+        <v>0.8697418816468543</v>
+      </c>
+      <c r="U4">
+        <v>0.2388</v>
+      </c>
+      <c r="V4">
+        <v>-1.216510859698866</v>
+      </c>
+      <c r="W4">
+        <v>0.5293027932960893</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>-6.082554298494333</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.106898697441359</v>
+      </c>
+      <c r="C5">
+        <v>313.5730695850454</v>
+      </c>
+      <c r="D5">
+        <v>322.5880695850454</v>
+      </c>
+      <c r="E5">
+        <v>-285.675</v>
+      </c>
+      <c r="F5">
+        <v>13.425</v>
+      </c>
+      <c r="G5">
+        <v>4.41</v>
+      </c>
+      <c r="H5">
+        <v>148.4</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>30.5</v>
+      </c>
+      <c r="K5">
+        <v>43.5</v>
+      </c>
+      <c r="L5">
+        <v>-13</v>
+      </c>
+      <c r="M5">
+        <v>3.20589</v>
+      </c>
+      <c r="N5">
+        <v>-16.20589</v>
+      </c>
+      <c r="O5">
+        <v>-3.241177999999999</v>
+      </c>
+      <c r="P5">
+        <v>-12.964712</v>
+      </c>
+      <c r="Q5">
+        <v>30.535288</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.09682952739735795</v>
+      </c>
+      <c r="T5">
+        <v>0.8787082927978528</v>
+      </c>
+      <c r="U5">
+        <v>0.2388</v>
+      </c>
+      <c r="V5">
+        <v>-0.8110072397992443</v>
+      </c>
+      <c r="W5">
+        <v>0.4324685288640596</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>-4.055036198996222</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.108898697441359</v>
+      </c>
+      <c r="C6">
+        <v>299.8942446536362</v>
+      </c>
+      <c r="D6">
+        <v>313.3842446536362</v>
+      </c>
+      <c r="E6">
+        <v>-281.2</v>
+      </c>
+      <c r="F6">
+        <v>17.9</v>
+      </c>
+      <c r="G6">
+        <v>4.41</v>
+      </c>
+      <c r="H6">
+        <v>148.4</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>30.5</v>
+      </c>
+      <c r="K6">
+        <v>43.5</v>
+      </c>
+      <c r="L6">
+        <v>-13</v>
+      </c>
+      <c r="M6">
+        <v>4.274520000000001</v>
+      </c>
+      <c r="N6">
+        <v>-17.27452</v>
+      </c>
+      <c r="O6">
+        <v>-3.454904</v>
+      </c>
+      <c r="P6">
+        <v>-13.819616</v>
+      </c>
+      <c r="Q6">
+        <v>29.680384</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.09743400164108042</v>
+      </c>
+      <c r="T6">
+        <v>0.8878615041811637</v>
+      </c>
+      <c r="U6">
+        <v>0.2388</v>
+      </c>
+      <c r="V6">
+        <v>-0.6082554298494331</v>
+      </c>
+      <c r="W6">
+        <v>0.3840513966480447</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>-3.041277149247167</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.110898697441359</v>
+      </c>
+      <c r="C7">
+        <v>286.7260433677594</v>
+      </c>
+      <c r="D7">
+        <v>304.6910433677593</v>
+      </c>
+      <c r="E7">
+        <v>-276.725</v>
+      </c>
+      <c r="F7">
+        <v>22.375</v>
+      </c>
+      <c r="G7">
+        <v>4.41</v>
+      </c>
+      <c r="H7">
+        <v>148.4</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>30.5</v>
+      </c>
+      <c r="K7">
+        <v>43.5</v>
+      </c>
+      <c r="L7">
+        <v>-13</v>
+      </c>
+      <c r="M7">
+        <v>5.343150000000001</v>
+      </c>
+      <c r="N7">
+        <v>-18.34315</v>
+      </c>
+      <c r="O7">
+        <v>-3.668629999999999</v>
+      </c>
+      <c r="P7">
+        <v>-14.67452</v>
+      </c>
+      <c r="Q7">
+        <v>28.82548</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.09805120165835496</v>
+      </c>
+      <c r="T7">
+        <v>0.8972074147514918</v>
+      </c>
+      <c r="U7">
+        <v>0.2388</v>
+      </c>
+      <c r="V7">
+        <v>-0.4866043438795466</v>
+      </c>
+      <c r="W7">
+        <v>0.3550011173184358</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>-2.433021719397733</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.112898697441359</v>
+      </c>
+      <c r="C8">
+        <v>274.0271189564325</v>
+      </c>
+      <c r="D8">
+        <v>296.4671189564325</v>
+      </c>
+      <c r="E8">
+        <v>-272.25</v>
+      </c>
+      <c r="F8">
+        <v>26.85</v>
+      </c>
+      <c r="G8">
+        <v>4.41</v>
+      </c>
+      <c r="H8">
+        <v>148.4</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>30.5</v>
+      </c>
+      <c r="K8">
+        <v>43.5</v>
+      </c>
+      <c r="L8">
+        <v>-13</v>
+      </c>
+      <c r="M8">
+        <v>6.41178</v>
+      </c>
+      <c r="N8">
+        <v>-19.41178</v>
+      </c>
+      <c r="O8">
+        <v>-3.882355999999999</v>
+      </c>
+      <c r="P8">
+        <v>-15.529424</v>
+      </c>
+      <c r="Q8">
+        <v>27.970576</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.09868153359089063</v>
+      </c>
+      <c r="T8">
+        <v>0.9067521744828906</v>
+      </c>
+      <c r="U8">
+        <v>0.2388</v>
+      </c>
+      <c r="V8">
+        <v>-0.4055036198996221</v>
+      </c>
+      <c r="W8">
+        <v>0.3356342644320298</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>-2.027518099498111</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.114898697441359</v>
+      </c>
+      <c r="C9">
+        <v>261.7604712955803</v>
+      </c>
+      <c r="D9">
+        <v>288.6754712955802</v>
+      </c>
+      <c r="E9">
+        <v>-267.775</v>
+      </c>
+      <c r="F9">
+        <v>31.325</v>
+      </c>
+      <c r="G9">
+        <v>4.41</v>
+      </c>
+      <c r="H9">
+        <v>148.4</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>30.5</v>
+      </c>
+      <c r="K9">
+        <v>43.5</v>
+      </c>
+      <c r="L9">
+        <v>-13</v>
+      </c>
+      <c r="M9">
+        <v>7.480410000000001</v>
+      </c>
+      <c r="N9">
+        <v>-20.48041</v>
+      </c>
+      <c r="O9">
+        <v>-4.096081999999999</v>
+      </c>
+      <c r="P9">
+        <v>-16.384328</v>
+      </c>
+      <c r="Q9">
+        <v>27.115672</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.09932542104885719</v>
+      </c>
+      <c r="T9">
+        <v>0.916502197864427</v>
+      </c>
+      <c r="U9">
+        <v>0.2388</v>
+      </c>
+      <c r="V9">
+        <v>-0.3475745313425332</v>
+      </c>
+      <c r="W9">
+        <v>0.321800798084597</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>-1.737872656712666</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.116898697441359</v>
+      </c>
+      <c r="C10">
+        <v>249.8928903498523</v>
+      </c>
+      <c r="D10">
+        <v>281.2828903498523</v>
+      </c>
+      <c r="E10">
+        <v>-263.3</v>
+      </c>
+      <c r="F10">
+        <v>35.8</v>
+      </c>
+      <c r="G10">
+        <v>4.41</v>
+      </c>
+      <c r="H10">
+        <v>148.4</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>30.5</v>
+      </c>
+      <c r="K10">
+        <v>43.5</v>
+      </c>
+      <c r="L10">
+        <v>-13</v>
+      </c>
+      <c r="M10">
+        <v>8.549040000000002</v>
+      </c>
+      <c r="N10">
+        <v>-21.54904</v>
+      </c>
+      <c r="O10">
+        <v>-4.309807999999999</v>
+      </c>
+      <c r="P10">
+        <v>-17.239232</v>
+      </c>
+      <c r="Q10">
+        <v>26.260768</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.09998330606025782</v>
+      </c>
+      <c r="T10">
+        <v>0.9264641782759968</v>
+      </c>
+      <c r="U10">
+        <v>0.2388</v>
+      </c>
+      <c r="V10">
+        <v>-0.3041277149247166</v>
+      </c>
+      <c r="W10">
+        <v>0.3114256983240223</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>-1.520638574623583</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.118898697441359</v>
+      </c>
+      <c r="C11">
+        <v>238.3944829953</v>
+      </c>
+      <c r="D11">
+        <v>274.2594829952999</v>
+      </c>
+      <c r="E11">
+        <v>-258.825</v>
+      </c>
+      <c r="F11">
+        <v>40.275</v>
+      </c>
+      <c r="G11">
+        <v>4.41</v>
+      </c>
+      <c r="H11">
+        <v>148.4</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>30.5</v>
+      </c>
+      <c r="K11">
+        <v>43.5</v>
+      </c>
+      <c r="L11">
+        <v>-13</v>
+      </c>
+      <c r="M11">
+        <v>9.61767</v>
+      </c>
+      <c r="N11">
+        <v>-22.61767</v>
+      </c>
+      <c r="O11">
+        <v>-4.523533999999999</v>
+      </c>
+      <c r="P11">
+        <v>-18.094136</v>
+      </c>
+      <c r="Q11">
+        <v>25.405864</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.100655650082898</v>
+      </c>
+      <c r="T11">
+        <v>0.9366451033119968</v>
+      </c>
+      <c r="U11">
+        <v>0.2388</v>
+      </c>
+      <c r="V11">
+        <v>-0.2703357465997481</v>
+      </c>
+      <c r="W11">
+        <v>0.3033561762880199</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>-1.351678732998741</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.120898697441359</v>
+      </c>
+      <c r="C12">
+        <v>227.2382690042693</v>
+      </c>
+      <c r="D12">
+        <v>267.5782690042693</v>
+      </c>
+      <c r="E12">
+        <v>-254.35</v>
+      </c>
+      <c r="F12">
+        <v>44.75</v>
+      </c>
+      <c r="G12">
+        <v>4.41</v>
+      </c>
+      <c r="H12">
+        <v>148.4</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>30.5</v>
+      </c>
+      <c r="K12">
+        <v>43.5</v>
+      </c>
+      <c r="L12">
+        <v>-13</v>
+      </c>
+      <c r="M12">
+        <v>10.6863</v>
+      </c>
+      <c r="N12">
+        <v>-23.6863</v>
+      </c>
+      <c r="O12">
+        <v>-4.737259999999999</v>
+      </c>
+      <c r="P12">
+        <v>-18.94904</v>
+      </c>
+      <c r="Q12">
+        <v>24.55096</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1013429350838191</v>
+      </c>
+      <c r="T12">
+        <v>0.9470522711265746</v>
+      </c>
+      <c r="U12">
+        <v>0.2388</v>
+      </c>
+      <c r="V12">
+        <v>-0.2433021719397733</v>
+      </c>
+      <c r="W12">
+        <v>0.2969005586592179</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>-1.216510859698867</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.122898697441359</v>
+      </c>
+      <c r="C13">
+        <v>216.3998346790029</v>
+      </c>
+      <c r="D13">
+        <v>261.2148346790029</v>
+      </c>
+      <c r="E13">
+        <v>-249.875</v>
+      </c>
+      <c r="F13">
+        <v>49.225</v>
+      </c>
+      <c r="G13">
+        <v>4.41</v>
+      </c>
+      <c r="H13">
+        <v>148.4</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>30.5</v>
+      </c>
+      <c r="K13">
+        <v>43.5</v>
+      </c>
+      <c r="L13">
+        <v>-13</v>
+      </c>
+      <c r="M13">
+        <v>11.75493</v>
+      </c>
+      <c r="N13">
+        <v>-24.75493</v>
+      </c>
+      <c r="O13">
+        <v>-4.950985999999999</v>
+      </c>
+      <c r="P13">
+        <v>-19.803944</v>
+      </c>
+      <c r="Q13">
+        <v>23.696056</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1020456646915025</v>
+      </c>
+      <c r="T13">
+        <v>0.9576933078808058</v>
+      </c>
+      <c r="U13">
+        <v>0.2388</v>
+      </c>
+      <c r="V13">
+        <v>-0.2211837926725212</v>
+      </c>
+      <c r="W13">
+        <v>0.2916186896901981</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>-1.105918963362606</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.124898697441359</v>
+      </c>
+      <c r="C14">
+        <v>205.857034760034</v>
+      </c>
+      <c r="D14">
+        <v>255.147034760034</v>
+      </c>
+      <c r="E14">
+        <v>-245.4</v>
+      </c>
+      <c r="F14">
+        <v>53.7</v>
+      </c>
+      <c r="G14">
+        <v>4.41</v>
+      </c>
+      <c r="H14">
+        <v>148.4</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>30.5</v>
+      </c>
+      <c r="K14">
+        <v>43.5</v>
+      </c>
+      <c r="L14">
+        <v>-13</v>
+      </c>
+      <c r="M14">
+        <v>12.82356</v>
+      </c>
+      <c r="N14">
+        <v>-25.82356</v>
+      </c>
+      <c r="O14">
+        <v>-5.164711999999999</v>
+      </c>
+      <c r="P14">
+        <v>-20.658848</v>
+      </c>
+      <c r="Q14">
+        <v>22.841152</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1027643654266332</v>
+      </c>
+      <c r="T14">
+        <v>0.9685761863794513</v>
+      </c>
+      <c r="U14">
+        <v>0.2388</v>
+      </c>
+      <c r="V14">
+        <v>-0.2027518099498111</v>
+      </c>
+      <c r="W14">
+        <v>0.2872171322160149</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>-1.013759049749055</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.126898697441359</v>
+      </c>
+      <c r="C15">
+        <v>195.5897349378972</v>
+      </c>
+      <c r="D15">
+        <v>249.3547349378972</v>
+      </c>
+      <c r="E15">
+        <v>-240.925</v>
+      </c>
+      <c r="F15">
+        <v>58.175</v>
+      </c>
+      <c r="G15">
+        <v>4.41</v>
+      </c>
+      <c r="H15">
+        <v>148.4</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>30.5</v>
+      </c>
+      <c r="K15">
+        <v>43.5</v>
+      </c>
+      <c r="L15">
+        <v>-13</v>
+      </c>
+      <c r="M15">
+        <v>13.89219</v>
+      </c>
+      <c r="N15">
+        <v>-26.89219</v>
+      </c>
+      <c r="O15">
+        <v>-5.378437999999998</v>
+      </c>
+      <c r="P15">
+        <v>-21.513752</v>
+      </c>
+      <c r="Q15">
+        <v>21.986248</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1034995880177439</v>
+      </c>
+      <c r="T15">
+        <v>0.9797092459930081</v>
+      </c>
+      <c r="U15">
+        <v>0.2388</v>
+      </c>
+      <c r="V15">
+        <v>-0.1871555168767487</v>
+      </c>
+      <c r="W15">
+        <v>0.2834927374301676</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>-0.9357775843837435</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.128898697441359</v>
+      </c>
+      <c r="C16">
+        <v>185.5795886590025</v>
+      </c>
+      <c r="D16">
+        <v>243.8195886590025</v>
+      </c>
+      <c r="E16">
+        <v>-236.45</v>
+      </c>
+      <c r="F16">
+        <v>62.65000000000001</v>
+      </c>
+      <c r="G16">
+        <v>4.41</v>
+      </c>
+      <c r="H16">
+        <v>148.4</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>30.5</v>
+      </c>
+      <c r="K16">
+        <v>43.5</v>
+      </c>
+      <c r="L16">
+        <v>-13</v>
+      </c>
+      <c r="M16">
+        <v>14.96082</v>
+      </c>
+      <c r="N16">
+        <v>-27.96082</v>
+      </c>
+      <c r="O16">
+        <v>-5.592163999999999</v>
+      </c>
+      <c r="P16">
+        <v>-22.368656</v>
+      </c>
+      <c r="Q16">
+        <v>21.131344</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1042519088086479</v>
+      </c>
+      <c r="T16">
+        <v>0.9911012139696711</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>-0.1737872656712666</v>
+      </c>
+      <c r="W16">
+        <v>0.2803003990422985</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>-0.8689363283563334</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.130898697441359</v>
+      </c>
+      <c r="C17">
+        <v>175.8098430125889</v>
+      </c>
+      <c r="D17">
+        <v>238.5248430125889</v>
+      </c>
+      <c r="E17">
+        <v>-231.975</v>
+      </c>
+      <c r="F17">
+        <v>67.125</v>
+      </c>
+      <c r="G17">
+        <v>4.41</v>
+      </c>
+      <c r="H17">
+        <v>148.4</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>30.5</v>
+      </c>
+      <c r="K17">
+        <v>43.5</v>
+      </c>
+      <c r="L17">
+        <v>-13</v>
+      </c>
+      <c r="M17">
+        <v>16.02945</v>
+      </c>
+      <c r="N17">
+        <v>-29.02945</v>
+      </c>
+      <c r="O17">
+        <v>-5.805889999999999</v>
+      </c>
+      <c r="P17">
+        <v>-23.22356</v>
+      </c>
+      <c r="Q17">
+        <v>20.27644</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1050219312652202</v>
+      </c>
+      <c r="T17">
+        <v>1.002761228251667</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>-0.1622014479598489</v>
+      </c>
+      <c r="W17">
+        <v>0.2775337057728119</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>-0.8110072397992445</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.132898697441359</v>
+      </c>
+      <c r="C18">
+        <v>166.2651693720746</v>
+      </c>
+      <c r="D18">
+        <v>233.4551693720746</v>
+      </c>
+      <c r="E18">
+        <v>-227.5</v>
+      </c>
+      <c r="F18">
+        <v>71.60000000000001</v>
+      </c>
+      <c r="G18">
+        <v>4.41</v>
+      </c>
+      <c r="H18">
+        <v>148.4</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>30.5</v>
+      </c>
+      <c r="K18">
+        <v>43.5</v>
+      </c>
+      <c r="L18">
+        <v>-13</v>
+      </c>
+      <c r="M18">
+        <v>17.09808</v>
+      </c>
+      <c r="N18">
+        <v>-30.09808</v>
+      </c>
+      <c r="O18">
+        <v>-6.019615999999999</v>
+      </c>
+      <c r="P18">
+        <v>-24.078464</v>
+      </c>
+      <c r="Q18">
+        <v>19.421536</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1058102875898062</v>
+      </c>
+      <c r="T18">
+        <v>1.01469886192133</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>-0.1520638574623583</v>
+      </c>
+      <c r="W18">
+        <v>0.2751128491620112</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>-0.7603192873117917</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.134898697441359</v>
+      </c>
+      <c r="C19">
+        <v>156.9315151844976</v>
+      </c>
+      <c r="D19">
+        <v>228.5965151844977</v>
+      </c>
+      <c r="E19">
+        <v>-223.025</v>
+      </c>
+      <c r="F19">
+        <v>76.075</v>
+      </c>
+      <c r="G19">
+        <v>4.41</v>
+      </c>
+      <c r="H19">
+        <v>148.4</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>30.5</v>
+      </c>
+      <c r="K19">
+        <v>43.5</v>
+      </c>
+      <c r="L19">
+        <v>-13</v>
+      </c>
+      <c r="M19">
+        <v>18.16671</v>
+      </c>
+      <c r="N19">
+        <v>-31.16671</v>
+      </c>
+      <c r="O19">
+        <v>-6.233341999999999</v>
+      </c>
+      <c r="P19">
+        <v>-24.933368</v>
+      </c>
+      <c r="Q19">
+        <v>18.566632</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.106617640452334</v>
+      </c>
+      <c r="T19">
+        <v>1.026924149414358</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>-0.1431189246704549</v>
+      </c>
+      <c r="W19">
+        <v>0.2729767992113046</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>-0.7155946233522745</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.136898697441359</v>
+      </c>
+      <c r="C20">
+        <v>147.7959738899276</v>
+      </c>
+      <c r="D20">
+        <v>223.9359738899275</v>
+      </c>
+      <c r="E20">
+        <v>-218.55</v>
+      </c>
+      <c r="F20">
+        <v>80.55</v>
+      </c>
+      <c r="G20">
+        <v>4.41</v>
+      </c>
+      <c r="H20">
+        <v>148.4</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>30.5</v>
+      </c>
+      <c r="K20">
+        <v>43.5</v>
+      </c>
+      <c r="L20">
+        <v>-13</v>
+      </c>
+      <c r="M20">
+        <v>19.23534</v>
+      </c>
+      <c r="N20">
+        <v>-32.23534</v>
+      </c>
+      <c r="O20">
+        <v>-6.447067999999999</v>
+      </c>
+      <c r="P20">
+        <v>-25.788272</v>
+      </c>
+      <c r="Q20">
+        <v>17.711728</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1074446848480941</v>
+      </c>
+      <c r="T20">
+        <v>1.039447614651118</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>-0.135167873299874</v>
+      </c>
+      <c r="W20">
+        <v>0.2710780881440099</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>-0.6758393664993705</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.138898697441359</v>
+      </c>
+      <c r="C21">
+        <v>138.8466704351575</v>
+      </c>
+      <c r="D21">
+        <v>219.4616704351575</v>
+      </c>
+      <c r="E21">
+        <v>-214.075</v>
+      </c>
+      <c r="F21">
+        <v>85.02500000000001</v>
+      </c>
+      <c r="G21">
+        <v>4.41</v>
+      </c>
+      <c r="H21">
+        <v>148.4</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>30.5</v>
+      </c>
+      <c r="K21">
+        <v>43.5</v>
+      </c>
+      <c r="L21">
+        <v>-13</v>
+      </c>
+      <c r="M21">
+        <v>20.30397</v>
+      </c>
+      <c r="N21">
+        <v>-33.30397000000001</v>
+      </c>
+      <c r="O21">
+        <v>-6.660794</v>
+      </c>
+      <c r="P21">
+        <v>-26.64317600000001</v>
+      </c>
+      <c r="Q21">
+        <v>16.85682399999999</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1082921500931323</v>
+      </c>
+      <c r="T21">
+        <v>1.052280301251749</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>-0.1280537747051438</v>
+      </c>
+      <c r="W21">
+        <v>0.2693792413995884</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>-0.6402688735257194</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.140898697441359</v>
+      </c>
+      <c r="C22">
+        <v>130.0726602433535</v>
+      </c>
+      <c r="D22">
+        <v>215.1626602433535</v>
+      </c>
+      <c r="E22">
+        <v>-209.6</v>
+      </c>
+      <c r="F22">
+        <v>89.5</v>
+      </c>
+      <c r="G22">
+        <v>4.41</v>
+      </c>
+      <c r="H22">
+        <v>148.4</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>30.5</v>
+      </c>
+      <c r="K22">
+        <v>43.5</v>
+      </c>
+      <c r="L22">
+        <v>-13</v>
+      </c>
+      <c r="M22">
+        <v>21.3726</v>
+      </c>
+      <c r="N22">
+        <v>-34.37260000000001</v>
+      </c>
+      <c r="O22">
+        <v>-6.87452</v>
+      </c>
+      <c r="P22">
+        <v>-27.49808000000001</v>
+      </c>
+      <c r="Q22">
+        <v>16.00191999999999</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1091608019692965</v>
+      </c>
+      <c r="T22">
+        <v>1.065433805017396</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>-0.1216510859698866</v>
+      </c>
+      <c r="W22">
+        <v>0.267850279329609</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>-0.6082554298494336</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.142898697441359</v>
+      </c>
+      <c r="C23">
+        <v>121.463839829999</v>
+      </c>
+      <c r="D23">
+        <v>211.028839829999</v>
+      </c>
+      <c r="E23">
+        <v>-205.125</v>
+      </c>
+      <c r="F23">
+        <v>93.97499999999999</v>
+      </c>
+      <c r="G23">
+        <v>4.41</v>
+      </c>
+      <c r="H23">
+        <v>148.4</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>30.5</v>
+      </c>
+      <c r="K23">
+        <v>43.5</v>
+      </c>
+      <c r="L23">
+        <v>-13</v>
+      </c>
+      <c r="M23">
+        <v>22.44123</v>
+      </c>
+      <c r="N23">
+        <v>-35.44123</v>
+      </c>
+      <c r="O23">
+        <v>-7.088245999999999</v>
+      </c>
+      <c r="P23">
+        <v>-28.35298400000001</v>
+      </c>
+      <c r="Q23">
+        <v>15.14701599999999</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.110051445032199</v>
+      </c>
+      <c r="T23">
+        <v>1.078920308878376</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>-0.1158581771141778</v>
+      </c>
+      <c r="W23">
+        <v>0.2664669326948657</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>-0.5792908855708891</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.144898697441359</v>
+      </c>
+      <c r="C24">
+        <v>113.010867528376</v>
+      </c>
+      <c r="D24">
+        <v>207.050867528376</v>
+      </c>
+      <c r="E24">
+        <v>-200.65</v>
+      </c>
+      <c r="F24">
+        <v>98.45</v>
+      </c>
+      <c r="G24">
+        <v>4.41</v>
+      </c>
+      <c r="H24">
+        <v>148.4</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>30.5</v>
+      </c>
+      <c r="K24">
+        <v>43.5</v>
+      </c>
+      <c r="L24">
+        <v>-13</v>
+      </c>
+      <c r="M24">
+        <v>23.50986</v>
+      </c>
+      <c r="N24">
+        <v>-36.50986</v>
+      </c>
+      <c r="O24">
+        <v>-7.301971999999999</v>
+      </c>
+      <c r="P24">
+        <v>-29.207888</v>
+      </c>
+      <c r="Q24">
+        <v>14.292112</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1109649250967144</v>
+      </c>
+      <c r="T24">
+        <v>1.092752620530663</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>-0.1105918963362606</v>
+      </c>
+      <c r="W24">
+        <v>0.2652093448450991</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>-0.552959481681303</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.146898697441359</v>
+      </c>
+      <c r="C25">
+        <v>104.7050930152844</v>
+      </c>
+      <c r="D25">
+        <v>203.2200930152844</v>
+      </c>
+      <c r="E25">
+        <v>-196.175</v>
+      </c>
+      <c r="F25">
+        <v>102.925</v>
+      </c>
+      <c r="G25">
+        <v>4.41</v>
+      </c>
+      <c r="H25">
+        <v>148.4</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>30.5</v>
+      </c>
+      <c r="K25">
+        <v>43.5</v>
+      </c>
+      <c r="L25">
+        <v>-13</v>
+      </c>
+      <c r="M25">
+        <v>24.57849000000001</v>
+      </c>
+      <c r="N25">
+        <v>-37.57849</v>
+      </c>
+      <c r="O25">
+        <v>-7.515697999999999</v>
+      </c>
+      <c r="P25">
+        <v>-30.062792</v>
+      </c>
+      <c r="Q25">
+        <v>13.437208</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1119021319161522</v>
+      </c>
+      <c r="T25">
+        <v>1.106944213005087</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>-0.1057835530172927</v>
+      </c>
+      <c r="W25">
+        <v>0.2640611124605295</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>-0.5289177650864636</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.148898697441359</v>
+      </c>
+      <c r="C26">
+        <v>96.53849451797215</v>
+      </c>
+      <c r="D26">
+        <v>199.5284945179721</v>
+      </c>
+      <c r="E26">
+        <v>-191.7</v>
+      </c>
+      <c r="F26">
+        <v>107.4</v>
+      </c>
+      <c r="G26">
+        <v>4.41</v>
+      </c>
+      <c r="H26">
+        <v>148.4</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>30.5</v>
+      </c>
+      <c r="K26">
+        <v>43.5</v>
+      </c>
+      <c r="L26">
+        <v>-13</v>
+      </c>
+      <c r="M26">
+        <v>25.64712</v>
+      </c>
+      <c r="N26">
+        <v>-38.64712</v>
+      </c>
+      <c r="O26">
+        <v>-7.729423999999998</v>
+      </c>
+      <c r="P26">
+        <v>-30.917696</v>
+      </c>
+      <c r="Q26">
+        <v>12.582304</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1128640020729437</v>
+      </c>
+      <c r="T26">
+        <v>1.121509268439365</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>-0.1013759049749055</v>
+      </c>
+      <c r="W26">
+        <v>0.2630085661080074</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>-0.5068795248745277</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.150898697441359</v>
+      </c>
+      <c r="C27">
+        <v>88.50362274297046</v>
+      </c>
+      <c r="D27">
+        <v>195.9686227429705</v>
+      </c>
+      <c r="E27">
+        <v>-187.225</v>
+      </c>
+      <c r="F27">
+        <v>111.875</v>
+      </c>
+      <c r="G27">
+        <v>4.41</v>
+      </c>
+      <c r="H27">
+        <v>148.4</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>30.5</v>
+      </c>
+      <c r="K27">
+        <v>43.5</v>
+      </c>
+      <c r="L27">
+        <v>-13</v>
+      </c>
+      <c r="M27">
+        <v>26.71575</v>
+      </c>
+      <c r="N27">
+        <v>-39.71575</v>
+      </c>
+      <c r="O27">
+        <v>-7.943149999999998</v>
+      </c>
+      <c r="P27">
+        <v>-31.7726</v>
+      </c>
+      <c r="Q27">
+        <v>11.7274</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1138515221005829</v>
+      </c>
+      <c r="T27">
+        <v>1.136462725351889</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>-0.09732086877590931</v>
+      </c>
+      <c r="W27">
+        <v>0.2620402234636872</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>-0.4866043438795467</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.152898697441359</v>
+      </c>
+      <c r="C28">
+        <v>80.59355070205272</v>
+      </c>
+      <c r="D28">
+        <v>192.5335507020527</v>
+      </c>
+      <c r="E28">
+        <v>-182.75</v>
+      </c>
+      <c r="F28">
+        <v>116.35</v>
+      </c>
+      <c r="G28">
+        <v>4.41</v>
+      </c>
+      <c r="H28">
+        <v>148.4</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>30.5</v>
+      </c>
+      <c r="K28">
+        <v>43.5</v>
+      </c>
+      <c r="L28">
+        <v>-13</v>
+      </c>
+      <c r="M28">
+        <v>27.78438</v>
+      </c>
+      <c r="N28">
+        <v>-40.78438</v>
+      </c>
+      <c r="O28">
+        <v>-8.156875999999999</v>
+      </c>
+      <c r="P28">
+        <v>-32.627504</v>
+      </c>
+      <c r="Q28">
+        <v>10.872496</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1148657318586989</v>
+      </c>
+      <c r="T28">
+        <v>1.151820329748537</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>-0.09357775843837433</v>
+      </c>
+      <c r="W28">
+        <v>0.2611463687150838</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>-0.4678887921918717</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.154898697441359</v>
+      </c>
+      <c r="C29">
+        <v>72.80182872419768</v>
+      </c>
+      <c r="D29">
+        <v>189.2168287241977</v>
+      </c>
+      <c r="E29">
+        <v>-178.275</v>
+      </c>
+      <c r="F29">
+        <v>120.825</v>
+      </c>
+      <c r="G29">
+        <v>4.41</v>
+      </c>
+      <c r="H29">
+        <v>148.4</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>30.5</v>
+      </c>
+      <c r="K29">
+        <v>43.5</v>
+      </c>
+      <c r="L29">
+        <v>-13</v>
+      </c>
+      <c r="M29">
+        <v>28.85301</v>
+      </c>
+      <c r="N29">
+        <v>-41.85301</v>
+      </c>
+      <c r="O29">
+        <v>-8.370601999999998</v>
+      </c>
+      <c r="P29">
+        <v>-33.482408</v>
+      </c>
+      <c r="Q29">
+        <v>10.017592</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1159077281855304</v>
+      </c>
+      <c r="T29">
+        <v>1.167598690430024</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>-0.09011191553324936</v>
+      </c>
+      <c r="W29">
+        <v>0.2603187254293399</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>-0.4505595776662468</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.156898697441359</v>
+      </c>
+      <c r="C30">
+        <v>65.12244403878395</v>
+      </c>
+      <c r="D30">
+        <v>186.012444038784</v>
+      </c>
+      <c r="E30">
+        <v>-173.8</v>
+      </c>
+      <c r="F30">
+        <v>125.3</v>
+      </c>
+      <c r="G30">
+        <v>4.41</v>
+      </c>
+      <c r="H30">
+        <v>148.4</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>30.5</v>
+      </c>
+      <c r="K30">
+        <v>43.5</v>
+      </c>
+      <c r="L30">
+        <v>-13</v>
+      </c>
+      <c r="M30">
+        <v>29.92164</v>
+      </c>
+      <c r="N30">
+        <v>-42.92164</v>
+      </c>
+      <c r="O30">
+        <v>-8.584327999999999</v>
+      </c>
+      <c r="P30">
+        <v>-34.337312</v>
+      </c>
+      <c r="Q30">
+        <v>9.162687999999996</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1169786688547739</v>
+      </c>
+      <c r="T30">
+        <v>1.183815338908218</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>-0.08689363283563331</v>
+      </c>
+      <c r="W30">
+        <v>0.2595501995211493</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>-0.4344681641781667</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.158898697441359</v>
+      </c>
+      <c r="C31">
+        <v>57.54978439714455</v>
+      </c>
+      <c r="D31">
+        <v>182.9147843971445</v>
+      </c>
+      <c r="E31">
+        <v>-169.325</v>
+      </c>
+      <c r="F31">
+        <v>129.775</v>
+      </c>
+      <c r="G31">
+        <v>4.41</v>
+      </c>
+      <c r="H31">
+        <v>148.4</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>30.5</v>
+      </c>
+      <c r="K31">
+        <v>43.5</v>
+      </c>
+      <c r="L31">
+        <v>-13</v>
+      </c>
+      <c r="M31">
+        <v>30.99027</v>
+      </c>
+      <c r="N31">
+        <v>-43.99027</v>
+      </c>
+      <c r="O31">
+        <v>-8.798053999999997</v>
+      </c>
+      <c r="P31">
+        <v>-35.192216</v>
+      </c>
+      <c r="Q31">
+        <v>8.307783999999998</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.118079776866813</v>
+      </c>
+      <c r="T31">
+        <v>1.200488794385799</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>-0.08389730066888736</v>
+      </c>
+      <c r="W31">
+        <v>0.2588346753997303</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>-0.4194865033444368</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.160898697441359</v>
+      </c>
+      <c r="C32">
+        <v>50.07860526943523</v>
+      </c>
+      <c r="D32">
+        <v>179.9186052694352</v>
+      </c>
+      <c r="E32">
+        <v>-164.85</v>
+      </c>
+      <c r="F32">
+        <v>134.25</v>
+      </c>
+      <c r="G32">
+        <v>4.41</v>
+      </c>
+      <c r="H32">
+        <v>148.4</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>30.5</v>
+      </c>
+      <c r="K32">
+        <v>43.5</v>
+      </c>
+      <c r="L32">
+        <v>-13</v>
+      </c>
+      <c r="M32">
+        <v>32.0589</v>
+      </c>
+      <c r="N32">
+        <v>-45.0589</v>
+      </c>
+      <c r="O32">
+        <v>-9.011779999999998</v>
+      </c>
+      <c r="P32">
+        <v>-36.04712000000001</v>
+      </c>
+      <c r="Q32">
+        <v>7.452879999999993</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1192123451077674</v>
+      </c>
+      <c r="T32">
+        <v>1.217638634305596</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>-0.08110072397992443</v>
+      </c>
+      <c r="W32">
+        <v>0.258166852886406</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>-0.4055036198996222</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.162898697441359</v>
+      </c>
+      <c r="C33">
+        <v>42.70400021347641</v>
+      </c>
+      <c r="D33">
+        <v>177.0190002134764</v>
+      </c>
+      <c r="E33">
+        <v>-160.375</v>
+      </c>
+      <c r="F33">
+        <v>138.725</v>
+      </c>
+      <c r="G33">
+        <v>4.41</v>
+      </c>
+      <c r="H33">
+        <v>148.4</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>30.5</v>
+      </c>
+      <c r="K33">
+        <v>43.5</v>
+      </c>
+      <c r="L33">
+        <v>-13</v>
+      </c>
+      <c r="M33">
+        <v>33.12753</v>
+      </c>
+      <c r="N33">
+        <v>-46.12753</v>
+      </c>
+      <c r="O33">
+        <v>-9.225505999999998</v>
+      </c>
+      <c r="P33">
+        <v>-36.902024</v>
+      </c>
+      <c r="Q33">
+        <v>6.597975999999996</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1203777414136771</v>
+      </c>
+      <c r="T33">
+        <v>1.235285571034663</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>-0.07848457159347526</v>
+      </c>
+      <c r="W33">
+        <v>0.2575421156965219</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>-0.3924228579673763</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.164898697441359</v>
+      </c>
+      <c r="C34">
+        <v>35.42137406339981</v>
+      </c>
+      <c r="D34">
+        <v>174.2113740633998</v>
+      </c>
+      <c r="E34">
+        <v>-155.9</v>
+      </c>
+      <c r="F34">
+        <v>143.2</v>
+      </c>
+      <c r="G34">
+        <v>4.41</v>
+      </c>
+      <c r="H34">
+        <v>148.4</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>30.5</v>
+      </c>
+      <c r="K34">
+        <v>43.5</v>
+      </c>
+      <c r="L34">
+        <v>-13</v>
+      </c>
+      <c r="M34">
+        <v>34.19616000000001</v>
+      </c>
+      <c r="N34">
+        <v>-47.19616000000001</v>
+      </c>
+      <c r="O34">
+        <v>-9.439231999999999</v>
+      </c>
+      <c r="P34">
+        <v>-37.75692800000001</v>
+      </c>
+      <c r="Q34">
+        <v>5.743071999999991</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1215774140815253</v>
+      </c>
+      <c r="T34">
+        <v>1.253451535314584</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>-0.07603192873117914</v>
+      </c>
+      <c r="W34">
+        <v>0.2569564245810056</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>-0.3801596436558958</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.166898697441359</v>
+      </c>
+      <c r="C35">
+        <v>28.22641862992401</v>
+      </c>
+      <c r="D35">
+        <v>171.491418629924</v>
+      </c>
+      <c r="E35">
+        <v>-151.425</v>
+      </c>
+      <c r="F35">
+        <v>147.675</v>
+      </c>
+      <c r="G35">
+        <v>4.41</v>
+      </c>
+      <c r="H35">
+        <v>148.4</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>30.5</v>
+      </c>
+      <c r="K35">
+        <v>43.5</v>
+      </c>
+      <c r="L35">
+        <v>-13</v>
+      </c>
+      <c r="M35">
+        <v>35.26479</v>
+      </c>
+      <c r="N35">
+        <v>-48.26479</v>
+      </c>
+      <c r="O35">
+        <v>-9.652957999999998</v>
+      </c>
+      <c r="P35">
+        <v>-38.61183200000001</v>
+      </c>
+      <c r="Q35">
+        <v>4.888167999999993</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1228128978737869</v>
+      </c>
+      <c r="T35">
+        <v>1.272159767184951</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>-0.07372793089084038</v>
+      </c>
+      <c r="W35">
+        <v>0.2564062298967327</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>-0.3686396544542021</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.168898697441359</v>
+      </c>
+      <c r="C36">
+        <v>21.11509064197892</v>
+      </c>
+      <c r="D36">
+        <v>168.8550906419789</v>
+      </c>
+      <c r="E36">
+        <v>-146.95</v>
+      </c>
+      <c r="F36">
+        <v>152.15</v>
+      </c>
+      <c r="G36">
+        <v>4.41</v>
+      </c>
+      <c r="H36">
+        <v>148.4</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>30.5</v>
+      </c>
+      <c r="K36">
+        <v>43.5</v>
+      </c>
+      <c r="L36">
+        <v>-13</v>
+      </c>
+      <c r="M36">
+        <v>36.33342</v>
+      </c>
+      <c r="N36">
+        <v>-49.33342</v>
+      </c>
+      <c r="O36">
+        <v>-9.866683999999999</v>
+      </c>
+      <c r="P36">
+        <v>-39.466736</v>
+      </c>
+      <c r="Q36">
+        <v>4.033263999999996</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1240858205688442</v>
+      </c>
+      <c r="T36">
+        <v>1.291434915172602</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>-0.07155946233522743</v>
+      </c>
+      <c r="W36">
+        <v>0.2558883996056523</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>-0.3577973116761373</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.170898697441359</v>
+      </c>
+      <c r="C37">
+        <v>14.08359169213975</v>
+      </c>
+      <c r="D37">
+        <v>166.2985916921398</v>
+      </c>
+      <c r="E37">
+        <v>-142.475</v>
+      </c>
+      <c r="F37">
+        <v>156.625</v>
+      </c>
+      <c r="G37">
+        <v>4.41</v>
+      </c>
+      <c r="H37">
+        <v>148.4</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>30.5</v>
+      </c>
+      <c r="K37">
+        <v>43.5</v>
+      </c>
+      <c r="L37">
+        <v>-13</v>
+      </c>
+      <c r="M37">
+        <v>37.40205000000001</v>
+      </c>
+      <c r="N37">
+        <v>-50.40205000000001</v>
+      </c>
+      <c r="O37">
+        <v>-10.08041</v>
+      </c>
+      <c r="P37">
+        <v>-40.32164000000001</v>
+      </c>
+      <c r="Q37">
+        <v>3.178359999999991</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1253979101160572</v>
+      </c>
+      <c r="T37">
+        <v>1.311303144636796</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>-0.06951490626850665</v>
+      </c>
+      <c r="W37">
+        <v>0.2554001596169194</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>-0.3475745313425334</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.172898697441359</v>
+      </c>
+      <c r="C38">
+        <v>7.12834997666954</v>
+      </c>
+      <c r="D38">
+        <v>163.8183499766695</v>
+      </c>
+      <c r="E38">
+        <v>-138</v>
+      </c>
+      <c r="F38">
+        <v>161.1</v>
+      </c>
+      <c r="G38">
+        <v>4.41</v>
+      </c>
+      <c r="H38">
+        <v>148.4</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>30.5</v>
+      </c>
+      <c r="K38">
+        <v>43.5</v>
+      </c>
+      <c r="L38">
+        <v>-13</v>
+      </c>
+      <c r="M38">
+        <v>38.47068</v>
+      </c>
+      <c r="N38">
+        <v>-51.47068</v>
+      </c>
+      <c r="O38">
+        <v>-10.294136</v>
+      </c>
+      <c r="P38">
+        <v>-41.17654400000001</v>
+      </c>
+      <c r="Q38">
+        <v>2.323455999999993</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1267510024616206</v>
+      </c>
+      <c r="T38">
+        <v>1.331792256271746</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>-0.06758393664993702</v>
+      </c>
+      <c r="W38">
+        <v>0.254939044072005</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>-0.3379196832496851</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.174898697441359</v>
+      </c>
+      <c r="C39">
+        <v>0.2460036455666454</v>
+      </c>
+      <c r="D39">
+        <v>161.4110036455666</v>
+      </c>
+      <c r="E39">
+        <v>-133.525</v>
+      </c>
+      <c r="F39">
+        <v>165.575</v>
+      </c>
+      <c r="G39">
+        <v>4.41</v>
+      </c>
+      <c r="H39">
+        <v>148.4</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>30.5</v>
+      </c>
+      <c r="K39">
+        <v>43.5</v>
+      </c>
+      <c r="L39">
+        <v>-13</v>
+      </c>
+      <c r="M39">
+        <v>39.53931</v>
+      </c>
+      <c r="N39">
+        <v>-52.53931</v>
+      </c>
+      <c r="O39">
+        <v>-10.507862</v>
+      </c>
+      <c r="P39">
+        <v>-42.031448</v>
+      </c>
+      <c r="Q39">
+        <v>1.468551999999995</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1281470501197416</v>
+      </c>
+      <c r="T39">
+        <v>1.352931815895106</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>-0.0657573437675063</v>
+      </c>
+      <c r="W39">
+        <v>0.2545028536916805</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>-0.3287867188375315</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.176898697441359</v>
+      </c>
+      <c r="C40">
+        <v>-6.56661440060077</v>
+      </c>
+      <c r="D40">
+        <v>159.0733855993992</v>
+      </c>
+      <c r="E40">
+        <v>-129.05</v>
+      </c>
+      <c r="F40">
+        <v>170.05</v>
+      </c>
+      <c r="G40">
+        <v>4.41</v>
+      </c>
+      <c r="H40">
+        <v>148.4</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>30.5</v>
+      </c>
+      <c r="K40">
+        <v>43.5</v>
+      </c>
+      <c r="L40">
+        <v>-13</v>
+      </c>
+      <c r="M40">
+        <v>40.60794000000001</v>
+      </c>
+      <c r="N40">
+        <v>-53.60794000000001</v>
+      </c>
+      <c r="O40">
+        <v>-10.721588</v>
+      </c>
+      <c r="P40">
+        <v>-42.88635200000001</v>
+      </c>
+      <c r="Q40">
+        <v>0.6136479999999906</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1295881315732858</v>
+      </c>
+      <c r="T40">
+        <v>1.37475329679664</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>-0.06402688735257191</v>
+      </c>
+      <c r="W40">
+        <v>0.2540896206997942</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>-0.3201344367628596</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.178898697441359</v>
+      </c>
+      <c r="C41">
+        <v>-13.31249041164978</v>
+      </c>
+      <c r="D41">
+        <v>156.8025095883502</v>
+      </c>
+      <c r="E41">
+        <v>-124.575</v>
+      </c>
+      <c r="F41">
+        <v>174.525</v>
+      </c>
+      <c r="G41">
+        <v>4.41</v>
+      </c>
+      <c r="H41">
+        <v>148.4</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>30.5</v>
+      </c>
+      <c r="K41">
+        <v>43.5</v>
+      </c>
+      <c r="L41">
+        <v>-13</v>
+      </c>
+      <c r="M41">
+        <v>41.67657000000001</v>
+      </c>
+      <c r="N41">
+        <v>-54.67657000000001</v>
+      </c>
+      <c r="O41">
+        <v>-10.935314</v>
+      </c>
+      <c r="P41">
+        <v>-43.74125600000001</v>
+      </c>
+      <c r="Q41">
+        <v>-0.241256000000007</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1310764615990774</v>
+      </c>
+      <c r="T41">
+        <v>1.397290236088389</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>-0.06238517229224955</v>
+      </c>
+      <c r="W41">
+        <v>0.2536975791433892</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>-0.3119258614612479</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.180898697441359</v>
+      </c>
+      <c r="C42">
+        <v>-19.99444251482524</v>
+      </c>
+      <c r="D42">
+        <v>154.5955574851748</v>
+      </c>
+      <c r="E42">
+        <v>-120.1</v>
+      </c>
+      <c r="F42">
+        <v>179</v>
+      </c>
+      <c r="G42">
+        <v>4.41</v>
+      </c>
+      <c r="H42">
+        <v>148.4</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>30.5</v>
+      </c>
+      <c r="K42">
+        <v>43.5</v>
+      </c>
+      <c r="L42">
+        <v>-13</v>
+      </c>
+      <c r="M42">
+        <v>42.7452</v>
+      </c>
+      <c r="N42">
+        <v>-55.7452</v>
+      </c>
+      <c r="O42">
+        <v>-11.14904</v>
+      </c>
+      <c r="P42">
+        <v>-44.59616</v>
+      </c>
+      <c r="Q42">
+        <v>-1.096160000000005</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1326144026257287</v>
+      </c>
+      <c r="T42">
+        <v>1.420578406689862</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>-0.06082554298494332</v>
+      </c>
+      <c r="W42">
+        <v>0.2533251396648045</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>-0.3041277149247166</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.182898697441359</v>
+      </c>
+      <c r="C43">
+        <v>-26.6151323819816</v>
+      </c>
+      <c r="D43">
+        <v>152.4498676180184</v>
+      </c>
+      <c r="E43">
+        <v>-115.625</v>
+      </c>
+      <c r="F43">
+        <v>183.475</v>
+      </c>
+      <c r="G43">
+        <v>4.41</v>
+      </c>
+      <c r="H43">
+        <v>148.4</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>30.5</v>
+      </c>
+      <c r="K43">
+        <v>43.5</v>
+      </c>
+      <c r="L43">
+        <v>-13</v>
+      </c>
+      <c r="M43">
+        <v>43.81383000000001</v>
+      </c>
+      <c r="N43">
+        <v>-56.81383000000001</v>
+      </c>
+      <c r="O43">
+        <v>-11.362766</v>
+      </c>
+      <c r="P43">
+        <v>-45.45106400000001</v>
+      </c>
+      <c r="Q43">
+        <v>-1.951064000000009</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1342044772465038</v>
+      </c>
+      <c r="T43">
+        <v>1.444656006803249</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>-0.05934199315604226</v>
+      </c>
+      <c r="W43">
+        <v>0.2529708679656629</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>-0.2967099657802112</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.184898697441359</v>
+      </c>
+      <c r="C44">
+        <v>-33.1770759384662</v>
+      </c>
+      <c r="D44">
+        <v>150.3629240615338</v>
+      </c>
+      <c r="E44">
+        <v>-111.15</v>
+      </c>
+      <c r="F44">
+        <v>187.95</v>
+      </c>
+      <c r="G44">
+        <v>4.41</v>
+      </c>
+      <c r="H44">
+        <v>148.4</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>30.5</v>
+      </c>
+      <c r="K44">
+        <v>43.5</v>
+      </c>
+      <c r="L44">
+        <v>-13</v>
+      </c>
+      <c r="M44">
+        <v>44.88246</v>
+      </c>
+      <c r="N44">
+        <v>-57.88246</v>
+      </c>
+      <c r="O44">
+        <v>-11.576492</v>
+      </c>
+      <c r="P44">
+        <v>-46.30596800000001</v>
+      </c>
+      <c r="Q44">
+        <v>-2.805968000000007</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1358493820266159</v>
+      </c>
+      <c r="T44">
+        <v>1.469563868989512</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>-0.05792908855708888</v>
+      </c>
+      <c r="W44">
+        <v>0.2526334663474328</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>-0.2896454427854445</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.186898697441359</v>
+      </c>
+      <c r="C45">
+        <v>-39.68265320429353</v>
+      </c>
+      <c r="D45">
+        <v>148.3323467957065</v>
+      </c>
+      <c r="E45">
+        <v>-106.675</v>
+      </c>
+      <c r="F45">
+        <v>192.425</v>
+      </c>
+      <c r="G45">
+        <v>4.41</v>
+      </c>
+      <c r="H45">
+        <v>148.4</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>30.5</v>
+      </c>
+      <c r="K45">
+        <v>43.5</v>
+      </c>
+      <c r="L45">
+        <v>-13</v>
+      </c>
+      <c r="M45">
+        <v>45.95109</v>
+      </c>
+      <c r="N45">
+        <v>-58.95109</v>
+      </c>
+      <c r="O45">
+        <v>-11.790218</v>
+      </c>
+      <c r="P45">
+        <v>-47.160872</v>
+      </c>
+      <c r="Q45">
+        <v>-3.660872000000005</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1375520027639249</v>
+      </c>
+      <c r="T45">
+        <v>1.495345691252486</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>-0.05658190045111006</v>
+      </c>
+      <c r="W45">
+        <v>0.2523117578277251</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>-0.2829095022555503</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.188898697441359</v>
+      </c>
+      <c r="C46">
+        <v>-46.13411734854316</v>
+      </c>
+      <c r="D46">
+        <v>146.3558826514569</v>
+      </c>
+      <c r="E46">
+        <v>-102.2</v>
+      </c>
+      <c r="F46">
+        <v>196.9</v>
+      </c>
+      <c r="G46">
+        <v>4.41</v>
+      </c>
+      <c r="H46">
+        <v>148.4</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>30.5</v>
+      </c>
+      <c r="K46">
+        <v>43.5</v>
+      </c>
+      <c r="L46">
+        <v>-13</v>
+      </c>
+      <c r="M46">
+        <v>47.01972000000001</v>
+      </c>
+      <c r="N46">
+        <v>-60.01972000000001</v>
+      </c>
+      <c r="O46">
+        <v>-12.003944</v>
+      </c>
+      <c r="P46">
+        <v>-48.01577600000001</v>
+      </c>
+      <c r="Q46">
+        <v>-4.51577600000001</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1393154313847093</v>
+      </c>
+      <c r="T46">
+        <v>1.522048292881995</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>-0.05529594816813029</v>
+      </c>
+      <c r="W46">
+        <v>0.2520046724225495</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>-0.2764797408406514</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.190898697441359</v>
+      </c>
+      <c r="C47">
+        <v>-52.53360302940024</v>
+      </c>
+      <c r="D47">
+        <v>144.4313969705998</v>
+      </c>
+      <c r="E47">
+        <v>-97.72500000000002</v>
+      </c>
+      <c r="F47">
+        <v>201.375</v>
+      </c>
+      <c r="G47">
+        <v>4.41</v>
+      </c>
+      <c r="H47">
+        <v>148.4</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>30.5</v>
+      </c>
+      <c r="K47">
+        <v>43.5</v>
+      </c>
+      <c r="L47">
+        <v>-13</v>
+      </c>
+      <c r="M47">
+        <v>48.08835000000001</v>
+      </c>
+      <c r="N47">
+        <v>-61.08835000000001</v>
+      </c>
+      <c r="O47">
+        <v>-12.21767</v>
+      </c>
+      <c r="P47">
+        <v>-48.87068000000001</v>
+      </c>
+      <c r="Q47">
+        <v>-5.370680000000007</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1411429846826131</v>
+      </c>
+      <c r="T47">
+        <v>1.549721898207122</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>-0.05406714931994961</v>
+      </c>
+      <c r="W47">
+        <v>0.251711235257604</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>-0.2703357465997482</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.192898697441359</v>
+      </c>
+      <c r="C48">
+        <v>-58.88313408473977</v>
+      </c>
+      <c r="D48">
+        <v>142.5568659152603</v>
+      </c>
+      <c r="E48">
+        <v>-93.25</v>
+      </c>
+      <c r="F48">
+        <v>205.85</v>
+      </c>
+      <c r="G48">
+        <v>4.41</v>
+      </c>
+      <c r="H48">
+        <v>148.4</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>30.5</v>
+      </c>
+      <c r="K48">
+        <v>43.5</v>
+      </c>
+      <c r="L48">
+        <v>-13</v>
+      </c>
+      <c r="M48">
+        <v>49.15698000000001</v>
+      </c>
+      <c r="N48">
+        <v>-62.15698000000001</v>
+      </c>
+      <c r="O48">
+        <v>-12.431396</v>
+      </c>
+      <c r="P48">
+        <v>-49.72558400000001</v>
+      </c>
+      <c r="Q48">
+        <v>-6.225584000000012</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1430382251396985</v>
+      </c>
+      <c r="T48">
+        <v>1.578420451877624</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>-0.05289177650864636</v>
+      </c>
+      <c r="W48">
+        <v>0.2514305562302647</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>-0.2644588825432319</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.194898697441359</v>
+      </c>
+      <c r="C49">
+        <v>-65.18463063150071</v>
+      </c>
+      <c r="D49">
+        <v>140.7303693684993</v>
+      </c>
+      <c r="E49">
+        <v>-88.77500000000001</v>
+      </c>
+      <c r="F49">
+        <v>210.325</v>
+      </c>
+      <c r="G49">
+        <v>4.41</v>
+      </c>
+      <c r="H49">
+        <v>148.4</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>30.5</v>
+      </c>
+      <c r="K49">
+        <v>43.5</v>
+      </c>
+      <c r="L49">
+        <v>-13</v>
+      </c>
+      <c r="M49">
+        <v>50.22561</v>
+      </c>
+      <c r="N49">
+        <v>-63.22561</v>
+      </c>
+      <c r="O49">
+        <v>-12.645122</v>
+      </c>
+      <c r="P49">
+        <v>-50.580488</v>
+      </c>
+      <c r="Q49">
+        <v>-7.080488000000003</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1450049841045985</v>
+      </c>
+      <c r="T49">
+        <v>1.608201969837579</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>-0.05176641956165388</v>
+      </c>
+      <c r="W49">
+        <v>0.2511618209913229</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>-0.2588320978082694</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.196898697441359</v>
+      </c>
+      <c r="C50">
+        <v>-71.43991562620405</v>
+      </c>
+      <c r="D50">
+        <v>138.9500843737959</v>
+      </c>
+      <c r="E50">
+        <v>-84.30000000000004</v>
+      </c>
+      <c r="F50">
+        <v>214.8</v>
+      </c>
+      <c r="G50">
+        <v>4.41</v>
+      </c>
+      <c r="H50">
+        <v>148.4</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>30.5</v>
+      </c>
+      <c r="K50">
+        <v>43.5</v>
+      </c>
+      <c r="L50">
+        <v>-13</v>
+      </c>
+      <c r="M50">
+        <v>51.29424</v>
+      </c>
+      <c r="N50">
+        <v>-64.29424</v>
+      </c>
+      <c r="O50">
+        <v>-12.858848</v>
+      </c>
+      <c r="P50">
+        <v>-51.43539200000001</v>
+      </c>
+      <c r="Q50">
+        <v>-7.935392000000007</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1470473876450716</v>
+      </c>
+      <c r="T50">
+        <v>1.639128930795995</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>-0.05068795248745277</v>
+      </c>
+      <c r="W50">
+        <v>0.2509042830540038</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>-0.253439762437264</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.198898697441359</v>
+      </c>
+      <c r="C51">
+        <v>-77.65072093373558</v>
+      </c>
+      <c r="D51">
+        <v>137.2142790662644</v>
+      </c>
+      <c r="E51">
+        <v>-79.82500000000002</v>
+      </c>
+      <c r="F51">
+        <v>219.275</v>
+      </c>
+      <c r="G51">
+        <v>4.41</v>
+      </c>
+      <c r="H51">
+        <v>148.4</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>30.5</v>
+      </c>
+      <c r="K51">
+        <v>43.5</v>
+      </c>
+      <c r="L51">
+        <v>-13</v>
+      </c>
+      <c r="M51">
+        <v>52.36287</v>
+      </c>
+      <c r="N51">
+        <v>-65.36287</v>
+      </c>
+      <c r="O51">
+        <v>-13.072574</v>
+      </c>
+      <c r="P51">
+        <v>-52.290296</v>
+      </c>
+      <c r="Q51">
+        <v>-8.790296000000005</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1491698854420337</v>
+      </c>
+      <c r="T51">
+        <v>1.671268713752779</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>-0.04965350447750476</v>
+      </c>
+      <c r="W51">
+        <v>0.2506572568692282</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>-0.2482675223875239</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.200898697441359</v>
+      </c>
+      <c r="C52">
+        <v>-83.81869294686234</v>
+      </c>
+      <c r="D52">
+        <v>135.5213070531377</v>
+      </c>
+      <c r="E52">
+        <v>-75.35000000000002</v>
+      </c>
+      <c r="F52">
+        <v>223.75</v>
+      </c>
+      <c r="G52">
+        <v>4.41</v>
+      </c>
+      <c r="H52">
+        <v>148.4</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>30.5</v>
+      </c>
+      <c r="K52">
+        <v>43.5</v>
+      </c>
+      <c r="L52">
+        <v>-13</v>
+      </c>
+      <c r="M52">
+        <v>53.4315</v>
+      </c>
+      <c r="N52">
+        <v>-66.4315</v>
+      </c>
+      <c r="O52">
+        <v>-13.2863</v>
+      </c>
+      <c r="P52">
+        <v>-53.1452</v>
+      </c>
+      <c r="Q52">
+        <v>-9.645200000000003</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1513772831508744</v>
+      </c>
+      <c r="T52">
+        <v>1.704694088027834</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>-0.04866043438795466</v>
+      </c>
+      <c r="W52">
+        <v>0.2504201117318436</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>-0.2433021719397734</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.202898697441359</v>
+      </c>
+      <c r="C53">
+        <v>-89.945397794813</v>
+      </c>
+      <c r="D53">
+        <v>133.869602205187</v>
+      </c>
+      <c r="E53">
+        <v>-70.87500000000003</v>
+      </c>
+      <c r="F53">
+        <v>228.225</v>
+      </c>
+      <c r="G53">
+        <v>4.41</v>
+      </c>
+      <c r="H53">
+        <v>148.4</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>30.5</v>
+      </c>
+      <c r="K53">
+        <v>43.5</v>
+      </c>
+      <c r="L53">
+        <v>-13</v>
+      </c>
+      <c r="M53">
+        <v>54.50013</v>
+      </c>
+      <c r="N53">
+        <v>-67.50013</v>
+      </c>
+      <c r="O53">
+        <v>-13.500026</v>
+      </c>
+      <c r="P53">
+        <v>-54.000104</v>
+      </c>
+      <c r="Q53">
+        <v>-10.500104</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.153674778725382</v>
+      </c>
+      <c r="T53">
+        <v>1.739483763293709</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>-0.04770630822348496</v>
+      </c>
+      <c r="W53">
+        <v>0.2501922664037682</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>-0.2385315411174249</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.204898697441359</v>
+      </c>
+      <c r="C54">
+        <v>-96.03232617555722</v>
+      </c>
+      <c r="D54">
+        <v>132.2576738244428</v>
+      </c>
+      <c r="E54">
+        <v>-66.40000000000001</v>
+      </c>
+      <c r="F54">
+        <v>232.7</v>
+      </c>
+      <c r="G54">
+        <v>4.41</v>
+      </c>
+      <c r="H54">
+        <v>148.4</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>30.5</v>
+      </c>
+      <c r="K54">
+        <v>43.5</v>
+      </c>
+      <c r="L54">
+        <v>-13</v>
+      </c>
+      <c r="M54">
+        <v>55.56876</v>
+      </c>
+      <c r="N54">
+        <v>-68.56876</v>
+      </c>
+      <c r="O54">
+        <v>-13.713752</v>
+      </c>
+      <c r="P54">
+        <v>-54.855008</v>
+      </c>
+      <c r="Q54">
+        <v>-11.355008</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1560680032821608</v>
+      </c>
+      <c r="T54">
+        <v>1.775723008362327</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>-0.04678887921918717</v>
+      </c>
+      <c r="W54">
+        <v>0.2499731843575419</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>-0.2339443960959358</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.206898697441359</v>
+      </c>
+      <c r="C55">
+        <v>-102.0808978431257</v>
+      </c>
+      <c r="D55">
+        <v>130.6841021568743</v>
+      </c>
+      <c r="E55">
+        <v>-61.92500000000001</v>
+      </c>
+      <c r="F55">
+        <v>237.175</v>
+      </c>
+      <c r="G55">
+        <v>4.41</v>
+      </c>
+      <c r="H55">
+        <v>148.4</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>30.5</v>
+      </c>
+      <c r="K55">
+        <v>43.5</v>
+      </c>
+      <c r="L55">
+        <v>-13</v>
+      </c>
+      <c r="M55">
+        <v>56.63739</v>
+      </c>
+      <c r="N55">
+        <v>-69.63739000000001</v>
+      </c>
+      <c r="O55">
+        <v>-13.927478</v>
+      </c>
+      <c r="P55">
+        <v>-55.70991200000001</v>
+      </c>
+      <c r="Q55">
+        <v>-12.20991200000001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1585630671817813</v>
+      </c>
+      <c r="T55">
+        <v>1.813504348965781</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>-0.04590607017731571</v>
+      </c>
+      <c r="W55">
+        <v>0.249762369558343</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>-0.2295303508865787</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.208898697441359</v>
+      </c>
+      <c r="C56">
+        <v>-108.0924657783613</v>
+      </c>
+      <c r="D56">
+        <v>129.1475342216387</v>
+      </c>
+      <c r="E56">
+        <v>-57.45000000000002</v>
+      </c>
+      <c r="F56">
+        <v>241.65</v>
+      </c>
+      <c r="G56">
+        <v>4.41</v>
+      </c>
+      <c r="H56">
+        <v>148.4</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>30.5</v>
+      </c>
+      <c r="K56">
+        <v>43.5</v>
+      </c>
+      <c r="L56">
+        <v>-13</v>
+      </c>
+      <c r="M56">
+        <v>57.70602</v>
+      </c>
+      <c r="N56">
+        <v>-70.70602</v>
+      </c>
+      <c r="O56">
+        <v>-14.141204</v>
+      </c>
+      <c r="P56">
+        <v>-56.564816</v>
+      </c>
+      <c r="Q56">
+        <v>-13.064816</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1611666121205156</v>
+      </c>
+      <c r="T56">
+        <v>1.852928356551994</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>-0.04505595776662468</v>
+      </c>
+      <c r="W56">
+        <v>0.24955936271467</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>-0.2252797888331233</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.210898697441359</v>
+      </c>
+      <c r="C57">
+        <v>-114.0683200688553</v>
+      </c>
+      <c r="D57">
+        <v>127.6466799311447</v>
+      </c>
+      <c r="E57">
+        <v>-52.97499999999999</v>
+      </c>
+      <c r="F57">
+        <v>246.125</v>
+      </c>
+      <c r="G57">
+        <v>4.41</v>
+      </c>
+      <c r="H57">
+        <v>148.4</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>30.5</v>
+      </c>
+      <c r="K57">
+        <v>43.5</v>
+      </c>
+      <c r="L57">
+        <v>-13</v>
+      </c>
+      <c r="M57">
+        <v>58.77465000000001</v>
+      </c>
+      <c r="N57">
+        <v>-71.77465000000001</v>
+      </c>
+      <c r="O57">
+        <v>-14.35493</v>
+      </c>
+      <c r="P57">
+        <v>-57.41972000000001</v>
+      </c>
+      <c r="Q57">
+        <v>-13.91972000000001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1638858701676383</v>
+      </c>
+      <c r="T57">
+        <v>1.89410454225315</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>-0.04423675853450423</v>
+      </c>
+      <c r="W57">
+        <v>0.2493637379380396</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>-0.2211837926725213</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.212898697441359</v>
+      </c>
+      <c r="C58">
+        <v>-120.009691521452</v>
+      </c>
+      <c r="D58">
+        <v>126.180308478548</v>
+      </c>
+      <c r="E58">
+        <v>-48.5</v>
+      </c>
+      <c r="F58">
+        <v>250.6</v>
+      </c>
+      <c r="G58">
+        <v>4.41</v>
+      </c>
+      <c r="H58">
+        <v>148.4</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>30.5</v>
+      </c>
+      <c r="K58">
+        <v>43.5</v>
+      </c>
+      <c r="L58">
+        <v>-13</v>
+      </c>
+      <c r="M58">
+        <v>59.84328000000001</v>
+      </c>
+      <c r="N58">
+        <v>-72.84328000000001</v>
+      </c>
+      <c r="O58">
+        <v>-14.568656</v>
+      </c>
+      <c r="P58">
+        <v>-58.27462400000001</v>
+      </c>
+      <c r="Q58">
+        <v>-14.77462400000001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1667287308532664</v>
+      </c>
+      <c r="T58">
+        <v>1.937152372758903</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>-0.04344681641781666</v>
+      </c>
+      <c r="W58">
+        <v>0.2491750997605746</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>-0.2172340820890832</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.214898697441359</v>
+      </c>
+      <c r="C59">
+        <v>-125.9177550285864</v>
+      </c>
+      <c r="D59">
+        <v>124.7472449714136</v>
+      </c>
+      <c r="E59">
+        <v>-44.02500000000001</v>
+      </c>
+      <c r="F59">
+        <v>255.075</v>
+      </c>
+      <c r="G59">
+        <v>4.41</v>
+      </c>
+      <c r="H59">
+        <v>148.4</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>30.5</v>
+      </c>
+      <c r="K59">
+        <v>43.5</v>
+      </c>
+      <c r="L59">
+        <v>-13</v>
+      </c>
+      <c r="M59">
+        <v>60.91191000000001</v>
+      </c>
+      <c r="N59">
+        <v>-73.91191000000001</v>
+      </c>
+      <c r="O59">
+        <v>-14.782382</v>
+      </c>
+      <c r="P59">
+        <v>-59.12952800000001</v>
+      </c>
+      <c r="Q59">
+        <v>-15.62952800000001</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1697038176172958</v>
+      </c>
+      <c r="T59">
+        <v>1.982202427939342</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>-0.04268459156838127</v>
+      </c>
+      <c r="W59">
+        <v>0.2489930804665295</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>-0.2134229578419065</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.216898697441359</v>
+      </c>
+      <c r="C60">
+        <v>-131.793632707801</v>
+      </c>
+      <c r="D60">
+        <v>123.3463672921989</v>
+      </c>
+      <c r="E60">
+        <v>-39.55000000000007</v>
+      </c>
+      <c r="F60">
+        <v>259.55</v>
+      </c>
+      <c r="G60">
+        <v>4.41</v>
+      </c>
+      <c r="H60">
+        <v>148.4</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>30.5</v>
+      </c>
+      <c r="K60">
+        <v>43.5</v>
+      </c>
+      <c r="L60">
+        <v>-13</v>
+      </c>
+      <c r="M60">
+        <v>61.98053999999999</v>
+      </c>
+      <c r="N60">
+        <v>-74.98053999999999</v>
+      </c>
+      <c r="O60">
+        <v>-14.99610799999999</v>
+      </c>
+      <c r="P60">
+        <v>-59.984432</v>
+      </c>
+      <c r="Q60">
+        <v>-16.484432</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1728205751796124</v>
+      </c>
+      <c r="T60">
+        <v>2.02939772384266</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>-0.04194865033444368</v>
+      </c>
+      <c r="W60">
+        <v>0.2488173376998652</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>-0.2097432516722184</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.218898697441359</v>
+      </c>
+      <c r="C61">
+        <v>-137.6383968320793</v>
+      </c>
+      <c r="D61">
+        <v>121.9766031679207</v>
+      </c>
+      <c r="E61">
+        <v>-35.07500000000005</v>
+      </c>
+      <c r="F61">
+        <v>264.025</v>
+      </c>
+      <c r="G61">
+        <v>4.41</v>
+      </c>
+      <c r="H61">
+        <v>148.4</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>30.5</v>
+      </c>
+      <c r="K61">
+        <v>43.5</v>
+      </c>
+      <c r="L61">
+        <v>-13</v>
+      </c>
+      <c r="M61">
+        <v>63.04917</v>
+      </c>
+      <c r="N61">
+        <v>-76.04917</v>
+      </c>
+      <c r="O61">
+        <v>-15.209834</v>
+      </c>
+      <c r="P61">
+        <v>-60.839336</v>
+      </c>
+      <c r="Q61">
+        <v>-17.339336</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1760893696961883</v>
+      </c>
+      <c r="T61">
+        <v>2.078895229302237</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>-0.04123765626097853</v>
+      </c>
+      <c r="W61">
+        <v>0.2486475523151217</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>-0.2061882813048928</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.220898697441359</v>
+      </c>
+      <c r="C62">
+        <v>-143.4530725670713</v>
+      </c>
+      <c r="D62">
+        <v>120.6369274329287</v>
+      </c>
+      <c r="E62">
+        <v>-30.60000000000002</v>
+      </c>
+      <c r="F62">
+        <v>268.5</v>
+      </c>
+      <c r="G62">
+        <v>4.41</v>
+      </c>
+      <c r="H62">
+        <v>148.4</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>30.5</v>
+      </c>
+      <c r="K62">
+        <v>43.5</v>
+      </c>
+      <c r="L62">
+        <v>-13</v>
+      </c>
+      <c r="M62">
+        <v>64.1178</v>
+      </c>
+      <c r="N62">
+        <v>-77.1178</v>
+      </c>
+      <c r="O62">
+        <v>-15.42356</v>
+      </c>
+      <c r="P62">
+        <v>-61.69424000000001</v>
+      </c>
+      <c r="Q62">
+        <v>-18.19424000000001</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.179521603938593</v>
+      </c>
+      <c r="T62">
+        <v>2.130867610034793</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>-0.04055036198996222</v>
+      </c>
+      <c r="W62">
+        <v>0.248483426443203</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>-0.2027518099498111</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.222898697441359</v>
+      </c>
+      <c r="C63">
+        <v>-149.2386405299039</v>
+      </c>
+      <c r="D63">
+        <v>119.3263594700961</v>
+      </c>
+      <c r="E63">
+        <v>-26.12500000000006</v>
+      </c>
+      <c r="F63">
+        <v>272.975</v>
+      </c>
+      <c r="G63">
+        <v>4.41</v>
+      </c>
+      <c r="H63">
+        <v>148.4</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>30.5</v>
+      </c>
+      <c r="K63">
+        <v>43.5</v>
+      </c>
+      <c r="L63">
+        <v>-13</v>
+      </c>
+      <c r="M63">
+        <v>65.18643</v>
+      </c>
+      <c r="N63">
+        <v>-78.18643</v>
+      </c>
+      <c r="O63">
+        <v>-15.637286</v>
+      </c>
+      <c r="P63">
+        <v>-62.54914400000001</v>
+      </c>
+      <c r="Q63">
+        <v>-19.04914400000001</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1831298501934287</v>
+      </c>
+      <c r="T63">
+        <v>2.185505241061326</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>-0.03988560195733989</v>
+      </c>
+      <c r="W63">
+        <v>0.2483246817474128</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>-0.1994280097866994</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.224898697441359</v>
+      </c>
+      <c r="C64">
+        <v>-154.9960391829917</v>
+      </c>
+      <c r="D64">
+        <v>118.0439608170083</v>
+      </c>
+      <c r="E64">
+        <v>-21.65000000000003</v>
+      </c>
+      <c r="F64">
+        <v>277.45</v>
+      </c>
+      <c r="G64">
+        <v>4.41</v>
+      </c>
+      <c r="H64">
+        <v>148.4</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>30.5</v>
+      </c>
+      <c r="K64">
+        <v>43.5</v>
+      </c>
+      <c r="L64">
+        <v>-13</v>
+      </c>
+      <c r="M64">
+        <v>66.25506</v>
+      </c>
+      <c r="N64">
+        <v>-79.25506</v>
+      </c>
+      <c r="O64">
+        <v>-15.851012</v>
+      </c>
+      <c r="P64">
+        <v>-63.404048</v>
+      </c>
+      <c r="Q64">
+        <v>-19.904048</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1869280041458874</v>
+      </c>
+      <c r="T64">
+        <v>2.243018536878729</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>-0.03924228579673763</v>
+      </c>
+      <c r="W64">
+        <v>0.248171057848261</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>-0.1962114289836883</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.226898697441359</v>
+      </c>
+      <c r="C65">
+        <v>-160.7261670751326</v>
+      </c>
+      <c r="D65">
+        <v>116.7888329248674</v>
+      </c>
+      <c r="E65">
+        <v>-17.17500000000001</v>
+      </c>
+      <c r="F65">
+        <v>281.925</v>
+      </c>
+      <c r="G65">
+        <v>4.41</v>
+      </c>
+      <c r="H65">
+        <v>148.4</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>30.5</v>
+      </c>
+      <c r="K65">
+        <v>43.5</v>
+      </c>
+      <c r="L65">
+        <v>-13</v>
+      </c>
+      <c r="M65">
+        <v>67.32369</v>
+      </c>
+      <c r="N65">
+        <v>-80.32369</v>
+      </c>
+      <c r="O65">
+        <v>-16.06473799999999</v>
+      </c>
+      <c r="P65">
+        <v>-64.25895200000001</v>
+      </c>
+      <c r="Q65">
+        <v>-20.75895200000001</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1909314637173979</v>
+      </c>
+      <c r="T65">
+        <v>2.303640659497074</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>-0.03861939237139259</v>
+      </c>
+      <c r="W65">
+        <v>0.2480223108982886</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>-0.1930969618569629</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.228898697441359</v>
+      </c>
+      <c r="C66">
+        <v>-166.4298849411337</v>
+      </c>
+      <c r="D66">
+        <v>115.5601150588664</v>
+      </c>
+      <c r="E66">
+        <v>-12.69999999999999</v>
+      </c>
+      <c r="F66">
+        <v>286.4</v>
+      </c>
+      <c r="G66">
+        <v>4.41</v>
+      </c>
+      <c r="H66">
+        <v>148.4</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>30.5</v>
+      </c>
+      <c r="K66">
+        <v>43.5</v>
+      </c>
+      <c r="L66">
+        <v>-13</v>
+      </c>
+      <c r="M66">
+        <v>68.39232000000001</v>
+      </c>
+      <c r="N66">
+        <v>-81.39232000000001</v>
+      </c>
+      <c r="O66">
+        <v>-16.278464</v>
+      </c>
+      <c r="P66">
+        <v>-65.11385600000001</v>
+      </c>
+      <c r="Q66">
+        <v>-21.61385600000001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1951573377095478</v>
+      </c>
+      <c r="T66">
+        <v>2.367630677816436</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>-0.03801596436558957</v>
+      </c>
+      <c r="W66">
+        <v>0.2478782122905028</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>-0.1900798218279478</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.230898697441359</v>
+      </c>
+      <c r="C67">
+        <v>-172.1080176702782</v>
+      </c>
+      <c r="D67">
+        <v>114.3569823297218</v>
+      </c>
+      <c r="E67">
+        <v>-8.225000000000023</v>
+      </c>
+      <c r="F67">
+        <v>290.875</v>
+      </c>
+      <c r="G67">
+        <v>4.41</v>
+      </c>
+      <c r="H67">
+        <v>148.4</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>30.5</v>
+      </c>
+      <c r="K67">
+        <v>43.5</v>
+      </c>
+      <c r="L67">
+        <v>-13</v>
+      </c>
+      <c r="M67">
+        <v>69.46095</v>
+      </c>
+      <c r="N67">
+        <v>-82.46095</v>
+      </c>
+      <c r="O67">
+        <v>-16.49219</v>
+      </c>
+      <c r="P67">
+        <v>-65.96876</v>
+      </c>
+      <c r="Q67">
+        <v>-22.46876</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1996246902155348</v>
+      </c>
+      <c r="T67">
+        <v>2.435277268611192</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>-0.03743110337534974</v>
+      </c>
+      <c r="W67">
+        <v>0.2477385474860336</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>-0.1871555168767487</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.232898697441359</v>
+      </c>
+      <c r="C68">
+        <v>-177.7613561530933</v>
+      </c>
+      <c r="D68">
+        <v>113.1786438469067</v>
+      </c>
+      <c r="E68">
+        <v>-3.75</v>
+      </c>
+      <c r="F68">
+        <v>295.35</v>
+      </c>
+      <c r="G68">
+        <v>4.41</v>
+      </c>
+      <c r="H68">
+        <v>148.4</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>30.5</v>
+      </c>
+      <c r="K68">
+        <v>43.5</v>
+      </c>
+      <c r="L68">
+        <v>-13</v>
+      </c>
+      <c r="M68">
+        <v>70.52958000000001</v>
+      </c>
+      <c r="N68">
+        <v>-83.52958000000001</v>
+      </c>
+      <c r="O68">
+        <v>-16.705916</v>
+      </c>
+      <c r="P68">
+        <v>-66.82366400000001</v>
+      </c>
+      <c r="Q68">
+        <v>-23.32366400000001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2043548281630506</v>
+      </c>
+      <c r="T68">
+        <v>2.506903070629168</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>-0.03686396544542019</v>
+      </c>
+      <c r="W68">
+        <v>0.2476031149483663</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>-0.1843198272271009</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.234898697441359</v>
+      </c>
+      <c r="C69">
+        <v>-183.3906590151075</v>
+      </c>
+      <c r="D69">
+        <v>112.0243409848925</v>
+      </c>
+      <c r="E69">
+        <v>0.7250000000000227</v>
+      </c>
+      <c r="F69">
+        <v>299.825</v>
+      </c>
+      <c r="G69">
+        <v>4.41</v>
+      </c>
+      <c r="H69">
+        <v>148.4</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>30.5</v>
+      </c>
+      <c r="K69">
+        <v>43.5</v>
+      </c>
+      <c r="L69">
+        <v>-13</v>
+      </c>
+      <c r="M69">
+        <v>71.59821000000001</v>
+      </c>
+      <c r="N69">
+        <v>-84.59821000000001</v>
+      </c>
+      <c r="O69">
+        <v>-16.919642</v>
+      </c>
+      <c r="P69">
+        <v>-67.67856800000001</v>
+      </c>
+      <c r="Q69">
+        <v>-24.17856800000001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2093716411376885</v>
+      </c>
+      <c r="T69">
+        <v>2.582869830345204</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>-0.03631375700593631</v>
+      </c>
+      <c r="W69">
+        <v>0.2474717251730176</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>-0.1815687850296817</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.236898697441359</v>
+      </c>
+      <c r="C70">
+        <v>-188.996654245584</v>
+      </c>
+      <c r="D70">
+        <v>110.893345754416</v>
+      </c>
+      <c r="E70">
+        <v>5.199999999999989</v>
+      </c>
+      <c r="F70">
+        <v>304.3</v>
+      </c>
+      <c r="G70">
+        <v>4.41</v>
+      </c>
+      <c r="H70">
+        <v>148.4</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>30.5</v>
+      </c>
+      <c r="K70">
+        <v>43.5</v>
+      </c>
+      <c r="L70">
+        <v>-13</v>
+      </c>
+      <c r="M70">
+        <v>72.66684000000001</v>
+      </c>
+      <c r="N70">
+        <v>-85.66684000000001</v>
+      </c>
+      <c r="O70">
+        <v>-17.133368</v>
+      </c>
+      <c r="P70">
+        <v>-68.53347200000002</v>
+      </c>
+      <c r="Q70">
+        <v>-25.03347200000002</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2147020049232413</v>
+      </c>
+      <c r="T70">
+        <v>2.663584512543491</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>-0.03577973116761372</v>
+      </c>
+      <c r="W70">
+        <v>0.2473441998028262</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>-0.1788986558380685</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.238898697441359</v>
+      </c>
+      <c r="C71">
+        <v>-194.5800407285786</v>
+      </c>
+      <c r="D71">
+        <v>109.7849592714214</v>
+      </c>
+      <c r="E71">
+        <v>9.675000000000011</v>
+      </c>
+      <c r="F71">
+        <v>308.775</v>
+      </c>
+      <c r="G71">
+        <v>4.41</v>
+      </c>
+      <c r="H71">
+        <v>148.4</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>30.5</v>
+      </c>
+      <c r="K71">
+        <v>43.5</v>
+      </c>
+      <c r="L71">
+        <v>-13</v>
+      </c>
+      <c r="M71">
+        <v>73.73547000000001</v>
+      </c>
+      <c r="N71">
+        <v>-86.73547000000001</v>
+      </c>
+      <c r="O71">
+        <v>-17.347094</v>
+      </c>
+      <c r="P71">
+        <v>-69.38837600000001</v>
+      </c>
+      <c r="Q71">
+        <v>-25.88837600000001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2203762631465716</v>
+      </c>
+      <c r="T71">
+        <v>2.749506593593281</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>-0.03526118433909758</v>
+      </c>
+      <c r="W71">
+        <v>0.2472203708201765</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>-0.1763059216954879</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.240898697441359</v>
+      </c>
+      <c r="C72">
+        <v>-200.1414896830879</v>
+      </c>
+      <c r="D72">
+        <v>108.6985103169121</v>
+      </c>
+      <c r="E72">
+        <v>14.15000000000003</v>
+      </c>
+      <c r="F72">
+        <v>313.2500000000001</v>
+      </c>
+      <c r="G72">
+        <v>4.41</v>
+      </c>
+      <c r="H72">
+        <v>148.4</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>30.5</v>
+      </c>
+      <c r="K72">
+        <v>43.5</v>
+      </c>
+      <c r="L72">
+        <v>-13</v>
+      </c>
+      <c r="M72">
+        <v>74.80410000000002</v>
+      </c>
+      <c r="N72">
+        <v>-87.80410000000002</v>
+      </c>
+      <c r="O72">
+        <v>-17.56082</v>
+      </c>
+      <c r="P72">
+        <v>-70.24328000000003</v>
+      </c>
+      <c r="Q72">
+        <v>-26.74328000000003</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2264288052514574</v>
+      </c>
+      <c r="T72">
+        <v>2.841156813379724</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>-0.03475745313425332</v>
+      </c>
+      <c r="W72">
+        <v>0.2471000798084597</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>-0.1737872656712667</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.242898697441359</v>
+      </c>
+      <c r="C73">
+        <v>-205.6816460185235</v>
+      </c>
+      <c r="D73">
+        <v>107.6333539814765</v>
+      </c>
+      <c r="E73">
+        <v>18.62499999999994</v>
+      </c>
+      <c r="F73">
+        <v>317.725</v>
+      </c>
+      <c r="G73">
+        <v>4.41</v>
+      </c>
+      <c r="H73">
+        <v>148.4</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>30.5</v>
+      </c>
+      <c r="K73">
+        <v>43.5</v>
+      </c>
+      <c r="L73">
+        <v>-13</v>
+      </c>
+      <c r="M73">
+        <v>75.87272999999999</v>
+      </c>
+      <c r="N73">
+        <v>-88.87272999999999</v>
+      </c>
+      <c r="O73">
+        <v>-17.77454599999999</v>
+      </c>
+      <c r="P73">
+        <v>-71.098184</v>
+      </c>
+      <c r="Q73">
+        <v>-27.598184</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2328987640532317</v>
+      </c>
+      <c r="T73">
+        <v>2.939127737979025</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>-0.03426791154081314</v>
+      </c>
+      <c r="W73">
+        <v>0.2469831772759462</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>-0.1713395577040657</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.244898697441359</v>
+      </c>
+      <c r="C74">
+        <v>-211.2011296112652</v>
+      </c>
+      <c r="D74">
+        <v>106.5888703887347</v>
+      </c>
+      <c r="E74">
+        <v>23.09999999999997</v>
+      </c>
+      <c r="F74">
+        <v>322.2</v>
+      </c>
+      <c r="G74">
+        <v>4.41</v>
+      </c>
+      <c r="H74">
+        <v>148.4</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>30.5</v>
+      </c>
+      <c r="K74">
+        <v>43.5</v>
+      </c>
+      <c r="L74">
+        <v>-13</v>
+      </c>
+      <c r="M74">
+        <v>76.94136</v>
+      </c>
+      <c r="N74">
+        <v>-89.94136</v>
+      </c>
+      <c r="O74">
+        <v>-17.98827199999999</v>
+      </c>
+      <c r="P74">
+        <v>-71.95308800000001</v>
+      </c>
+      <c r="Q74">
+        <v>-28.45308800000001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2398308627694185</v>
+      </c>
+      <c r="T74">
+        <v>3.044096585763989</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>-0.03379196832496851</v>
+      </c>
+      <c r="W74">
+        <v>0.2468695220360025</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>-0.1689598416248426</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.246898697441359</v>
+      </c>
+      <c r="C75">
+        <v>-216.7005365076013</v>
+      </c>
+      <c r="D75">
+        <v>105.5644634923987</v>
+      </c>
+      <c r="E75">
+        <v>27.57499999999999</v>
+      </c>
+      <c r="F75">
+        <v>326.675</v>
+      </c>
+      <c r="G75">
+        <v>4.41</v>
+      </c>
+      <c r="H75">
+        <v>148.4</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>30.5</v>
+      </c>
+      <c r="K75">
+        <v>43.5</v>
+      </c>
+      <c r="L75">
+        <v>-13</v>
+      </c>
+      <c r="M75">
+        <v>78.00999</v>
+      </c>
+      <c r="N75">
+        <v>-91.00999</v>
+      </c>
+      <c r="O75">
+        <v>-18.201998</v>
+      </c>
+      <c r="P75">
+        <v>-72.80799200000001</v>
+      </c>
+      <c r="Q75">
+        <v>-29.30799200000001</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.247276450279397</v>
+      </c>
+      <c r="T75">
+        <v>3.156840903755248</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>-0.03332906464928401</v>
+      </c>
+      <c r="W75">
+        <v>0.2467589806382491</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>-0.16664532324642</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.248898697441359</v>
+      </c>
+      <c r="C76">
+        <v>-222.1804400579611</v>
+      </c>
+      <c r="D76">
+        <v>104.5595599420389</v>
+      </c>
+      <c r="E76">
+        <v>32.04999999999995</v>
+      </c>
+      <c r="F76">
+        <v>331.15</v>
+      </c>
+      <c r="G76">
+        <v>4.41</v>
+      </c>
+      <c r="H76">
+        <v>148.4</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>30.5</v>
+      </c>
+      <c r="K76">
+        <v>43.5</v>
+      </c>
+      <c r="L76">
+        <v>-13</v>
+      </c>
+      <c r="M76">
+        <v>79.07862</v>
+      </c>
+      <c r="N76">
+        <v>-92.07862</v>
+      </c>
+      <c r="O76">
+        <v>-18.415724</v>
+      </c>
+      <c r="P76">
+        <v>-73.662896</v>
+      </c>
+      <c r="Q76">
+        <v>-30.162896</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2552947752901431</v>
+      </c>
+      <c r="T76">
+        <v>3.278257861591989</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>-0.03287867188375315</v>
+      </c>
+      <c r="W76">
+        <v>0.2466514268458403</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>-0.1643933594187659</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.250898697441359</v>
+      </c>
+      <c r="C77">
+        <v>-227.6413919869771</v>
+      </c>
+      <c r="D77">
+        <v>103.5736080130229</v>
+      </c>
+      <c r="E77">
+        <v>36.52499999999998</v>
+      </c>
+      <c r="F77">
+        <v>335.625</v>
+      </c>
+      <c r="G77">
+        <v>4.41</v>
+      </c>
+      <c r="H77">
+        <v>148.4</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>30.5</v>
+      </c>
+      <c r="K77">
+        <v>43.5</v>
+      </c>
+      <c r="L77">
+        <v>-13</v>
+      </c>
+      <c r="M77">
+        <v>80.14725</v>
+      </c>
+      <c r="N77">
+        <v>-93.14725</v>
+      </c>
+      <c r="O77">
+        <v>-18.62944999999999</v>
+      </c>
+      <c r="P77">
+        <v>-74.51780000000001</v>
+      </c>
+      <c r="Q77">
+        <v>-31.01780000000001</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2639545663017488</v>
+      </c>
+      <c r="T77">
+        <v>3.409388176055669</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>-0.03244028959196977</v>
+      </c>
+      <c r="W77">
+        <v>0.2465467411545624</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>-0.1622014479598488</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.252898697441359</v>
+      </c>
+      <c r="C78">
+        <v>-233.0839234035696</v>
+      </c>
+      <c r="D78">
+        <v>102.6060765964304</v>
+      </c>
+      <c r="E78">
+        <v>41</v>
+      </c>
+      <c r="F78">
+        <v>340.1</v>
+      </c>
+      <c r="G78">
+        <v>4.41</v>
+      </c>
+      <c r="H78">
+        <v>148.4</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>30.5</v>
+      </c>
+      <c r="K78">
+        <v>43.5</v>
+      </c>
+      <c r="L78">
+        <v>-13</v>
+      </c>
+      <c r="M78">
+        <v>81.21588000000001</v>
+      </c>
+      <c r="N78">
+        <v>-94.21588000000001</v>
+      </c>
+      <c r="O78">
+        <v>-18.843176</v>
+      </c>
+      <c r="P78">
+        <v>-75.37270400000001</v>
+      </c>
+      <c r="Q78">
+        <v>-31.87270400000001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2733360065643217</v>
+      </c>
+      <c r="T78">
+        <v>3.551446016724655</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>-0.03201344367628595</v>
+      </c>
+      <c r="W78">
+        <v>0.2464448103498971</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>-0.1600672183814298</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.254898697441359</v>
+      </c>
+      <c r="C79">
+        <v>-238.5085457549423</v>
+      </c>
+      <c r="D79">
+        <v>101.6564542450577</v>
+      </c>
+      <c r="E79">
+        <v>45.47499999999997</v>
+      </c>
+      <c r="F79">
+        <v>344.575</v>
+      </c>
+      <c r="G79">
+        <v>4.41</v>
+      </c>
+      <c r="H79">
+        <v>148.4</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>30.5</v>
+      </c>
+      <c r="K79">
+        <v>43.5</v>
+      </c>
+      <c r="L79">
+        <v>-13</v>
+      </c>
+      <c r="M79">
+        <v>82.28451</v>
+      </c>
+      <c r="N79">
+        <v>-95.28451</v>
+      </c>
+      <c r="O79">
+        <v>-19.05690199999999</v>
+      </c>
+      <c r="P79">
+        <v>-76.227608</v>
+      </c>
+      <c r="Q79">
+        <v>-32.727608</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2835332242410313</v>
+      </c>
+      <c r="T79">
+        <v>3.705856713103987</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>-0.03159768466750303</v>
+      </c>
+      <c r="W79">
+        <v>0.2463455270985997</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>-0.1579884233375151</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.256898697441359</v>
+      </c>
+      <c r="C80">
+        <v>-243.915751728088</v>
+      </c>
+      <c r="D80">
+        <v>100.724248271912</v>
+      </c>
+      <c r="E80">
+        <v>49.94999999999999</v>
+      </c>
+      <c r="F80">
+        <v>349.05</v>
+      </c>
+      <c r="G80">
+        <v>4.41</v>
+      </c>
+      <c r="H80">
+        <v>148.4</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>30.5</v>
+      </c>
+      <c r="K80">
+        <v>43.5</v>
+      </c>
+      <c r="L80">
+        <v>-13</v>
+      </c>
+      <c r="M80">
+        <v>83.35314000000001</v>
+      </c>
+      <c r="N80">
+        <v>-96.35314000000001</v>
+      </c>
+      <c r="O80">
+        <v>-19.270628</v>
+      </c>
+      <c r="P80">
+        <v>-77.08251200000001</v>
+      </c>
+      <c r="Q80">
+        <v>-33.58251200000001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2946574617065327</v>
+      </c>
+      <c r="T80">
+        <v>3.874304745517805</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>-0.03119258614612478</v>
+      </c>
+      <c r="W80">
+        <v>0.2462487895716946</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>-0.1559629307306238</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.258898697441359</v>
+      </c>
+      <c r="C81">
+        <v>-249.3060161021422</v>
+      </c>
+      <c r="D81">
+        <v>99.8089838978578</v>
+      </c>
+      <c r="E81">
+        <v>54.42500000000001</v>
+      </c>
+      <c r="F81">
+        <v>353.525</v>
+      </c>
+      <c r="G81">
+        <v>4.41</v>
+      </c>
+      <c r="H81">
+        <v>148.4</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>30.5</v>
+      </c>
+      <c r="K81">
+        <v>43.5</v>
+      </c>
+      <c r="L81">
+        <v>-13</v>
+      </c>
+      <c r="M81">
+        <v>84.42177000000001</v>
+      </c>
+      <c r="N81">
+        <v>-97.42177000000001</v>
+      </c>
+      <c r="O81">
+        <v>-19.484354</v>
+      </c>
+      <c r="P81">
+        <v>-77.93741600000001</v>
+      </c>
+      <c r="Q81">
+        <v>-34.43741600000001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3068411503592248</v>
+      </c>
+      <c r="T81">
+        <v>4.05879544768532</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>-0.0307977432835156</v>
+      </c>
+      <c r="W81">
+        <v>0.2461545010961035</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>-0.1539887164175782</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.260898697441359</v>
+      </c>
+      <c r="C82">
+        <v>-254.6797965546859</v>
+      </c>
+      <c r="D82">
+        <v>98.91020344531405</v>
+      </c>
+      <c r="E82">
+        <v>58.89999999999998</v>
+      </c>
+      <c r="F82">
+        <v>358</v>
+      </c>
+      <c r="G82">
+        <v>4.41</v>
+      </c>
+      <c r="H82">
+        <v>148.4</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>30.5</v>
+      </c>
+      <c r="K82">
+        <v>43.5</v>
+      </c>
+      <c r="L82">
+        <v>-13</v>
+      </c>
+      <c r="M82">
+        <v>85.49040000000001</v>
+      </c>
+      <c r="N82">
+        <v>-98.49040000000001</v>
+      </c>
+      <c r="O82">
+        <v>-19.69808</v>
+      </c>
+      <c r="P82">
+        <v>-78.79232000000002</v>
+      </c>
+      <c r="Q82">
+        <v>-35.29232000000002</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.320243207877186</v>
+      </c>
+      <c r="T82">
+        <v>4.261735220069585</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>-0.03041277149247166</v>
+      </c>
+      <c r="W82">
+        <v>0.2460625698324022</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>-0.1520638574623583</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.262898697441359</v>
+      </c>
+      <c r="C83">
+        <v>-260.0375344248711</v>
+      </c>
+      <c r="D83">
+        <v>98.02746557512899</v>
+      </c>
+      <c r="E83">
+        <v>63.375</v>
+      </c>
+      <c r="F83">
+        <v>362.475</v>
+      </c>
+      <c r="G83">
+        <v>4.41</v>
+      </c>
+      <c r="H83">
+        <v>148.4</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>30.5</v>
+      </c>
+      <c r="K83">
+        <v>43.5</v>
+      </c>
+      <c r="L83">
+        <v>-13</v>
+      </c>
+      <c r="M83">
+        <v>86.55903000000001</v>
+      </c>
+      <c r="N83">
+        <v>-99.55903000000001</v>
+      </c>
+      <c r="O83">
+        <v>-19.911806</v>
+      </c>
+      <c r="P83">
+        <v>-79.64722400000001</v>
+      </c>
+      <c r="Q83">
+        <v>-36.14722400000001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3350560082917748</v>
+      </c>
+      <c r="T83">
+        <v>4.486037073757459</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>-0.03003730517774979</v>
+      </c>
+      <c r="W83">
+        <v>0.2459729084764467</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>-0.1501865258887489</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.264898697441359</v>
+      </c>
+      <c r="C84">
+        <v>-265.3796554360441</v>
+      </c>
+      <c r="D84">
+        <v>97.16034456395599</v>
+      </c>
+      <c r="E84">
+        <v>67.85000000000002</v>
+      </c>
+      <c r="F84">
+        <v>366.95</v>
+      </c>
+      <c r="G84">
+        <v>4.41</v>
+      </c>
+      <c r="H84">
+        <v>148.4</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>30.5</v>
+      </c>
+      <c r="K84">
+        <v>43.5</v>
+      </c>
+      <c r="L84">
+        <v>-13</v>
+      </c>
+      <c r="M84">
+        <v>87.62766000000002</v>
+      </c>
+      <c r="N84">
+        <v>-100.62766</v>
+      </c>
+      <c r="O84">
+        <v>-20.125532</v>
+      </c>
+      <c r="P84">
+        <v>-80.50212800000003</v>
+      </c>
+      <c r="Q84">
+        <v>-37.00212800000003</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3515146754190956</v>
+      </c>
+      <c r="T84">
+        <v>4.735261355632875</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>-0.02967099657802113</v>
+      </c>
+      <c r="W84">
+        <v>0.2458854339828314</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>-0.1483549828901056</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.266898697441359</v>
+      </c>
+      <c r="C85">
+        <v>-270.7065703803539</v>
+      </c>
+      <c r="D85">
+        <v>96.30842961964608</v>
+      </c>
+      <c r="E85">
+        <v>72.32499999999999</v>
+      </c>
+      <c r="F85">
+        <v>371.425</v>
+      </c>
+      <c r="G85">
+        <v>4.41</v>
+      </c>
+      <c r="H85">
+        <v>148.4</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>30.5</v>
+      </c>
+      <c r="K85">
+        <v>43.5</v>
+      </c>
+      <c r="L85">
+        <v>-13</v>
+      </c>
+      <c r="M85">
+        <v>88.69629</v>
+      </c>
+      <c r="N85">
+        <v>-101.69629</v>
+      </c>
+      <c r="O85">
+        <v>-20.339258</v>
+      </c>
+      <c r="P85">
+        <v>-81.357032</v>
+      </c>
+      <c r="Q85">
+        <v>-37.857032</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3699096563261012</v>
+      </c>
+      <c r="T85">
+        <v>5.013806141258337</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>-0.02931351469153895</v>
+      </c>
+      <c r="W85">
+        <v>0.2458000673083395</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>-0.1465675734576948</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.268898697441359</v>
+      </c>
+      <c r="C86">
+        <v>-276.0186757676557</v>
+      </c>
+      <c r="D86">
+        <v>95.47132423234427</v>
+      </c>
+      <c r="E86">
+        <v>76.79999999999995</v>
+      </c>
+      <c r="F86">
+        <v>375.9</v>
+      </c>
+      <c r="G86">
+        <v>4.41</v>
+      </c>
+      <c r="H86">
+        <v>148.4</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>30.5</v>
+      </c>
+      <c r="K86">
+        <v>43.5</v>
+      </c>
+      <c r="L86">
+        <v>-13</v>
+      </c>
+      <c r="M86">
+        <v>89.76492</v>
+      </c>
+      <c r="N86">
+        <v>-102.76492</v>
+      </c>
+      <c r="O86">
+        <v>-20.552984</v>
+      </c>
+      <c r="P86">
+        <v>-82.21193600000001</v>
+      </c>
+      <c r="Q86">
+        <v>-38.71193600000001</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3906040098464824</v>
+      </c>
+      <c r="T86">
+        <v>5.327169025086981</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>-0.02896454427854444</v>
+      </c>
+      <c r="W86">
+        <v>0.2457167331737164</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>-0.1448227213927222</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.270898697441359</v>
+      </c>
+      <c r="C87">
+        <v>-281.3163544408652</v>
+      </c>
+      <c r="D87">
+        <v>94.64864555913485</v>
+      </c>
+      <c r="E87">
+        <v>81.27499999999998</v>
+      </c>
+      <c r="F87">
+        <v>380.375</v>
+      </c>
+      <c r="G87">
+        <v>4.41</v>
+      </c>
+      <c r="H87">
+        <v>148.4</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>30.5</v>
+      </c>
+      <c r="K87">
+        <v>43.5</v>
+      </c>
+      <c r="L87">
+        <v>-13</v>
+      </c>
+      <c r="M87">
+        <v>90.83355</v>
+      </c>
+      <c r="N87">
+        <v>-103.83355</v>
+      </c>
+      <c r="O87">
+        <v>-20.76671</v>
+      </c>
+      <c r="P87">
+        <v>-83.06684000000001</v>
+      </c>
+      <c r="Q87">
+        <v>-39.56684000000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4140576105029146</v>
+      </c>
+      <c r="T87">
+        <v>5.682313626759447</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>-0.02862378493409098</v>
+      </c>
+      <c r="W87">
+        <v>0.2456353598422609</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>-0.143118924670455</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.272898697441359</v>
+      </c>
+      <c r="C88">
+        <v>-286.5999761597693</v>
+      </c>
+      <c r="D88">
+        <v>93.84002384023066</v>
+      </c>
+      <c r="E88">
+        <v>85.74999999999994</v>
+      </c>
+      <c r="F88">
+        <v>384.85</v>
+      </c>
+      <c r="G88">
+        <v>4.41</v>
+      </c>
+      <c r="H88">
+        <v>148.4</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>30.5</v>
+      </c>
+      <c r="K88">
+        <v>43.5</v>
+      </c>
+      <c r="L88">
+        <v>-13</v>
+      </c>
+      <c r="M88">
+        <v>91.90218</v>
+      </c>
+      <c r="N88">
+        <v>-104.90218</v>
+      </c>
+      <c r="O88">
+        <v>-20.98043599999999</v>
+      </c>
+      <c r="P88">
+        <v>-83.921744</v>
+      </c>
+      <c r="Q88">
+        <v>-40.421744</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4408617255388371</v>
+      </c>
+      <c r="T88">
+        <v>6.088193171527979</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>-0.02829095022555503</v>
+      </c>
+      <c r="W88">
+        <v>0.2455558789138625</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>-0.1414547511277753</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.274898697441359</v>
+      </c>
+      <c r="C89">
+        <v>-291.8698981551653</v>
+      </c>
+      <c r="D89">
+        <v>93.0451018448347</v>
+      </c>
+      <c r="E89">
+        <v>90.22499999999997</v>
+      </c>
+      <c r="F89">
+        <v>389.325</v>
+      </c>
+      <c r="G89">
+        <v>4.41</v>
+      </c>
+      <c r="H89">
+        <v>148.4</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>30.5</v>
+      </c>
+      <c r="K89">
+        <v>43.5</v>
+      </c>
+      <c r="L89">
+        <v>-13</v>
+      </c>
+      <c r="M89">
+        <v>92.97081</v>
+      </c>
+      <c r="N89">
+        <v>-105.97081</v>
+      </c>
+      <c r="O89">
+        <v>-21.194162</v>
+      </c>
+      <c r="P89">
+        <v>-84.77664800000001</v>
+      </c>
+      <c r="Q89">
+        <v>-41.27664800000001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.4717895505802861</v>
+      </c>
+      <c r="T89">
+        <v>6.556515723183978</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>-0.02796576688962912</v>
+      </c>
+      <c r="W89">
+        <v>0.2454782251332435</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>-0.1398288344481455</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.276898697441359</v>
+      </c>
+      <c r="C90">
+        <v>-297.1264656550694</v>
+      </c>
+      <c r="D90">
+        <v>92.2635343449306</v>
+      </c>
+      <c r="E90">
+        <v>94.69999999999999</v>
+      </c>
+      <c r="F90">
+        <v>393.8</v>
+      </c>
+      <c r="G90">
+        <v>4.41</v>
+      </c>
+      <c r="H90">
+        <v>148.4</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>30.5</v>
+      </c>
+      <c r="K90">
+        <v>43.5</v>
+      </c>
+      <c r="L90">
+        <v>-13</v>
+      </c>
+      <c r="M90">
+        <v>94.03944000000001</v>
+      </c>
+      <c r="N90">
+        <v>-107.03944</v>
+      </c>
+      <c r="O90">
+        <v>-21.407888</v>
+      </c>
+      <c r="P90">
+        <v>-85.63155200000001</v>
+      </c>
+      <c r="Q90">
+        <v>-42.13155200000001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5078720131286434</v>
+      </c>
+      <c r="T90">
+        <v>7.10289203344931</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>-0.02764797408406515</v>
+      </c>
+      <c r="W90">
+        <v>0.2454023362112748</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>-0.1382398704203258</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.278898697441359</v>
+      </c>
+      <c r="C91">
+        <v>-302.3700123846281</v>
+      </c>
+      <c r="D91">
+        <v>91.49498761537193</v>
+      </c>
+      <c r="E91">
+        <v>99.17500000000001</v>
+      </c>
+      <c r="F91">
+        <v>398.275</v>
+      </c>
+      <c r="G91">
+        <v>4.41</v>
+      </c>
+      <c r="H91">
+        <v>148.4</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>30.5</v>
+      </c>
+      <c r="K91">
+        <v>43.5</v>
+      </c>
+      <c r="L91">
+        <v>-13</v>
+      </c>
+      <c r="M91">
+        <v>95.10807000000001</v>
+      </c>
+      <c r="N91">
+        <v>-108.10807</v>
+      </c>
+      <c r="O91">
+        <v>-21.621614</v>
+      </c>
+      <c r="P91">
+        <v>-86.48645600000002</v>
+      </c>
+      <c r="Q91">
+        <v>-42.98645600000002</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5505149234130655</v>
+      </c>
+      <c r="T91">
+        <v>7.74860949103561</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>-0.02733732268986216</v>
+      </c>
+      <c r="W91">
+        <v>0.2453281526583391</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>-0.1366866134493108</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.280898697441359</v>
+      </c>
+      <c r="C92">
+        <v>-307.6008610412491</v>
+      </c>
+      <c r="D92">
+        <v>90.73913895875091</v>
+      </c>
+      <c r="E92">
+        <v>103.65</v>
+      </c>
+      <c r="F92">
+        <v>402.75</v>
+      </c>
+      <c r="G92">
+        <v>4.41</v>
+      </c>
+      <c r="H92">
+        <v>148.4</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>30.5</v>
+      </c>
+      <c r="K92">
+        <v>43.5</v>
+      </c>
+      <c r="L92">
+        <v>-13</v>
+      </c>
+      <c r="M92">
+        <v>96.17670000000001</v>
+      </c>
+      <c r="N92">
+        <v>-109.1767</v>
+      </c>
+      <c r="O92">
+        <v>-21.83534</v>
+      </c>
+      <c r="P92">
+        <v>-87.34136000000001</v>
+      </c>
+      <c r="Q92">
+        <v>-43.84136000000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.601686415754372</v>
+      </c>
+      <c r="T92">
+        <v>8.523470440139171</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>-0.02703357465997481</v>
+      </c>
+      <c r="W92">
+        <v>0.245255617628802</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>-0.135167873299874</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.282898697441359</v>
+      </c>
+      <c r="C93">
+        <v>-312.8193237463752</v>
+      </c>
+      <c r="D93">
+        <v>89.99567625362486</v>
+      </c>
+      <c r="E93">
+        <v>108.125</v>
+      </c>
+      <c r="F93">
+        <v>407.225</v>
+      </c>
+      <c r="G93">
+        <v>4.41</v>
+      </c>
+      <c r="H93">
+        <v>148.4</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>30.5</v>
+      </c>
+      <c r="K93">
+        <v>43.5</v>
+      </c>
+      <c r="L93">
+        <v>-13</v>
+      </c>
+      <c r="M93">
+        <v>97.24533000000001</v>
+      </c>
+      <c r="N93">
+        <v>-110.24533</v>
+      </c>
+      <c r="O93">
+        <v>-22.049066</v>
+      </c>
+      <c r="P93">
+        <v>-88.19626400000001</v>
+      </c>
+      <c r="Q93">
+        <v>-44.69626400000001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.6642293508381911</v>
+      </c>
+      <c r="T93">
+        <v>9.470522711265748</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>-0.02673650241096409</v>
+      </c>
+      <c r="W93">
+        <v>0.2451846767757382</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>-0.1336825120548204</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.284898697441359</v>
+      </c>
+      <c r="C94">
+        <v>-318.0257024752291</v>
+      </c>
+      <c r="D94">
+        <v>89.26429752477097</v>
+      </c>
+      <c r="E94">
+        <v>112.6</v>
+      </c>
+      <c r="F94">
+        <v>411.7</v>
+      </c>
+      <c r="G94">
+        <v>4.41</v>
+      </c>
+      <c r="H94">
+        <v>148.4</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>30.5</v>
+      </c>
+      <c r="K94">
+        <v>43.5</v>
+      </c>
+      <c r="L94">
+        <v>-13</v>
+      </c>
+      <c r="M94">
+        <v>98.31396000000002</v>
+      </c>
+      <c r="N94">
+        <v>-111.31396</v>
+      </c>
+      <c r="O94">
+        <v>-22.262792</v>
+      </c>
+      <c r="P94">
+        <v>-89.05116800000002</v>
+      </c>
+      <c r="Q94">
+        <v>-45.55116800000002</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.7424080196929654</v>
+      </c>
+      <c r="T94">
+        <v>10.65433805017397</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>-0.02644588825432318</v>
+      </c>
+      <c r="W94">
+        <v>0.2451152781151324</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>-0.1322294412716158</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.286898697441359</v>
+      </c>
+      <c r="C95">
+        <v>-323.2202894657723</v>
+      </c>
+      <c r="D95">
+        <v>88.5447105342277</v>
+      </c>
+      <c r="E95">
+        <v>117.075</v>
+      </c>
+      <c r="F95">
+        <v>416.175</v>
+      </c>
+      <c r="G95">
+        <v>4.41</v>
+      </c>
+      <c r="H95">
+        <v>148.4</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>30.5</v>
+      </c>
+      <c r="K95">
+        <v>43.5</v>
+      </c>
+      <c r="L95">
+        <v>-13</v>
+      </c>
+      <c r="M95">
+        <v>99.38259000000001</v>
+      </c>
+      <c r="N95">
+        <v>-112.38259</v>
+      </c>
+      <c r="O95">
+        <v>-22.476518</v>
+      </c>
+      <c r="P95">
+        <v>-89.90607200000001</v>
+      </c>
+      <c r="Q95">
+        <v>-46.40607200000001</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.8429234510776749</v>
+      </c>
+      <c r="T95">
+        <v>12.17638634305597</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>-0.02616152386449175</v>
+      </c>
+      <c r="W95">
+        <v>0.2450473718988406</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>-0.1308076193224588</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.288898697441359</v>
+      </c>
+      <c r="C96">
+        <v>-328.4033676080425</v>
+      </c>
+      <c r="D96">
+        <v>87.83663239195758</v>
+      </c>
+      <c r="E96">
+        <v>121.55</v>
+      </c>
+      <c r="F96">
+        <v>420.65</v>
+      </c>
+      <c r="G96">
+        <v>4.41</v>
+      </c>
+      <c r="H96">
+        <v>148.4</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>30.5</v>
+      </c>
+      <c r="K96">
+        <v>43.5</v>
+      </c>
+      <c r="L96">
+        <v>-13</v>
+      </c>
+      <c r="M96">
+        <v>100.45122</v>
+      </c>
+      <c r="N96">
+        <v>-113.45122</v>
+      </c>
+      <c r="O96">
+        <v>-22.690244</v>
+      </c>
+      <c r="P96">
+        <v>-90.76097600000001</v>
+      </c>
+      <c r="Q96">
+        <v>-47.26097600000001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.9769440262572875</v>
+      </c>
+      <c r="T96">
+        <v>14.20578406689863</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>-0.02588320978082694</v>
+      </c>
+      <c r="W96">
+        <v>0.2449809104956615</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>-0.1294160489041347</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.290898697441359</v>
+      </c>
+      <c r="C97">
+        <v>-333.5752108149566</v>
+      </c>
+      <c r="D97">
+        <v>87.13978918504343</v>
+      </c>
+      <c r="E97">
+        <v>126.025</v>
+      </c>
+      <c r="F97">
+        <v>425.1250000000001</v>
+      </c>
+      <c r="G97">
+        <v>4.41</v>
+      </c>
+      <c r="H97">
+        <v>148.4</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>30.5</v>
+      </c>
+      <c r="K97">
+        <v>43.5</v>
+      </c>
+      <c r="L97">
+        <v>-13</v>
+      </c>
+      <c r="M97">
+        <v>101.51985</v>
+      </c>
+      <c r="N97">
+        <v>-114.51985</v>
+      </c>
+      <c r="O97">
+        <v>-22.90397</v>
+      </c>
+      <c r="P97">
+        <v>-91.61588000000002</v>
+      </c>
+      <c r="Q97">
+        <v>-48.11588000000002</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.164572831508745</v>
+      </c>
+      <c r="T97">
+        <v>17.04694088027836</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>-0.02561075494102876</v>
+      </c>
+      <c r="W97">
+        <v>0.2449158482799177</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>-0.1280537747051438</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.292898697441359</v>
+      </c>
+      <c r="C98">
+        <v>-338.7360843756044</v>
+      </c>
+      <c r="D98">
+        <v>86.45391562439556</v>
+      </c>
+      <c r="E98">
+        <v>130.4999999999999</v>
+      </c>
+      <c r="F98">
+        <v>429.6</v>
+      </c>
+      <c r="G98">
+        <v>4.41</v>
+      </c>
+      <c r="H98">
+        <v>148.4</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>30.5</v>
+      </c>
+      <c r="K98">
+        <v>43.5</v>
+      </c>
+      <c r="L98">
+        <v>-13</v>
+      </c>
+      <c r="M98">
+        <v>102.58848</v>
+      </c>
+      <c r="N98">
+        <v>-115.58848</v>
+      </c>
+      <c r="O98">
+        <v>-23.117696</v>
+      </c>
+      <c r="P98">
+        <v>-92.47078400000001</v>
+      </c>
+      <c r="Q98">
+        <v>-48.97078400000001</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.446016039385929</v>
+      </c>
+      <c r="T98">
+        <v>21.30867610034791</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>-0.02534397624372638</v>
+      </c>
+      <c r="W98">
+        <v>0.2448521415270019</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>-0.1267198812186319</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.294898697441359</v>
+      </c>
+      <c r="C99">
+        <v>-343.8862452919866</v>
+      </c>
+      <c r="D99">
+        <v>85.77875470801341</v>
+      </c>
+      <c r="E99">
+        <v>134.975</v>
+      </c>
+      <c r="F99">
+        <v>434.075</v>
+      </c>
+      <c r="G99">
+        <v>4.41</v>
+      </c>
+      <c r="H99">
+        <v>148.4</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>30.5</v>
+      </c>
+      <c r="K99">
+        <v>43.5</v>
+      </c>
+      <c r="L99">
+        <v>-13</v>
+      </c>
+      <c r="M99">
+        <v>103.65711</v>
+      </c>
+      <c r="N99">
+        <v>-116.65711</v>
+      </c>
+      <c r="O99">
+        <v>-23.331422</v>
+      </c>
+      <c r="P99">
+        <v>-93.32568800000001</v>
+      </c>
+      <c r="Q99">
+        <v>-49.82568800000001</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.915088052514572</v>
+      </c>
+      <c r="T99">
+        <v>28.41156813379721</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>-0.02508269813812096</v>
+      </c>
+      <c r="W99">
+        <v>0.2447897483153833</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>-0.1254134906906048</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.296898697441359</v>
+      </c>
+      <c r="C100">
+        <v>-349.0259426000969</v>
+      </c>
+      <c r="D100">
+        <v>85.11405739990313</v>
+      </c>
+      <c r="E100">
+        <v>139.45</v>
+      </c>
+      <c r="F100">
+        <v>438.55</v>
+      </c>
+      <c r="G100">
+        <v>4.41</v>
+      </c>
+      <c r="H100">
+        <v>148.4</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>30.5</v>
+      </c>
+      <c r="K100">
+        <v>43.5</v>
+      </c>
+      <c r="L100">
+        <v>-13</v>
+      </c>
+      <c r="M100">
+        <v>104.72574</v>
+      </c>
+      <c r="N100">
+        <v>-117.72574</v>
+      </c>
+      <c r="O100">
+        <v>-23.54514799999999</v>
+      </c>
+      <c r="P100">
+        <v>-94.180592</v>
+      </c>
+      <c r="Q100">
+        <v>-50.680592</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.853232078771858</v>
+      </c>
+      <c r="T100">
+        <v>42.61735220069582</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>-0.02482675223875238</v>
+      </c>
+      <c r="W100">
+        <v>0.2447286284346141</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>-0.1241337611937618</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2988986974413589</v>
+      </c>
+      <c r="C101">
+        <v>-354.1554176761905</v>
+      </c>
+      <c r="D101">
+        <v>84.45958232380947</v>
+      </c>
+      <c r="E101">
+        <v>143.925</v>
+      </c>
+      <c r="F101">
+        <v>443.025</v>
+      </c>
+      <c r="G101">
+        <v>4.41</v>
+      </c>
+      <c r="H101">
+        <v>148.4</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>30.5</v>
+      </c>
+      <c r="K101">
+        <v>43.5</v>
+      </c>
+      <c r="L101">
+        <v>-13</v>
+      </c>
+      <c r="M101">
+        <v>105.79437</v>
+      </c>
+      <c r="N101">
+        <v>-118.79437</v>
+      </c>
+      <c r="O101">
+        <v>-23.758874</v>
+      </c>
+      <c r="P101">
+        <v>-95.03549600000001</v>
+      </c>
+      <c r="Q101">
+        <v>-51.53549600000001</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>5.667664157543714</v>
+      </c>
+      <c r="T101">
+        <v>85.23470440139162</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>-0.02457597696361346</v>
+      </c>
+      <c r="W101">
+        <v>0.2446687432989109</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>-0.1228798848180674</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/finland/finland_restaurant_dining.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_restaurant_dining.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08687368703443471</v>
+        <v>0.08673593966036583</v>
       </c>
       <c r="C2">
-        <v>512.1369910830084</v>
+        <v>507.4314821565062</v>
       </c>
       <c r="D2">
-        <v>502.2069910830085</v>
+        <v>503.0564821565063</v>
       </c>
       <c r="E2">
-        <v>-382.8</v>
+        <v>-377.245</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.555</v>
       </c>
       <c r="G2">
         <v>9.93</v>
@@ -1451,28 +1451,28 @@
         <v>17.3</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2794165</v>
       </c>
       <c r="N2">
-        <v>17.3</v>
+        <v>17.0205835</v>
       </c>
       <c r="O2">
-        <v>3.46</v>
+        <v>3.404116699999999</v>
       </c>
       <c r="P2">
-        <v>13.84</v>
+        <v>13.6164668</v>
       </c>
       <c r="Q2">
-        <v>79.34</v>
+        <v>79.1164668</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08687368703443471</v>
+        <v>0.08720559561653114</v>
       </c>
       <c r="T2">
-        <v>0.8445182362326223</v>
+        <v>0.8513426260203607</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>61.91474018177166</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08673593966036583</v>
+        <v>0.08659819228629695</v>
       </c>
       <c r="C3">
-        <v>507.4314821565062</v>
+        <v>502.7288519546024</v>
       </c>
       <c r="D3">
-        <v>503.0564821565063</v>
+        <v>503.9088519546024</v>
       </c>
       <c r="E3">
-        <v>-377.245</v>
+        <v>-371.69</v>
       </c>
       <c r="F3">
-        <v>5.555</v>
+        <v>11.11</v>
       </c>
       <c r="G3">
         <v>9.93</v>
@@ -1533,28 +1533,28 @@
         <v>17.3</v>
       </c>
       <c r="M3">
-        <v>0.2794165</v>
+        <v>0.5588329999999999</v>
       </c>
       <c r="N3">
-        <v>17.0205835</v>
+        <v>16.741167</v>
       </c>
       <c r="O3">
-        <v>3.404116699999999</v>
+        <v>3.3482334</v>
       </c>
       <c r="P3">
-        <v>13.6164668</v>
+        <v>13.3929336</v>
       </c>
       <c r="Q3">
-        <v>79.1164668</v>
+        <v>78.89293359999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08720559561653114</v>
+        <v>0.08754427784316016</v>
       </c>
       <c r="T3">
-        <v>0.8513426260203607</v>
+        <v>0.8583062890690732</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>61.91474018177166</v>
+        <v>30.95737009088583</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08659819228629695</v>
+        <v>0.08646044491222808</v>
       </c>
       <c r="C4">
-        <v>502.7288519546024</v>
+        <v>498.0291151351095</v>
       </c>
       <c r="D4">
-        <v>503.9088519546024</v>
+        <v>504.7641151351095</v>
       </c>
       <c r="E4">
-        <v>-371.69</v>
+        <v>-366.135</v>
       </c>
       <c r="F4">
-        <v>11.11</v>
+        <v>16.665</v>
       </c>
       <c r="G4">
         <v>9.93</v>
@@ -1615,28 +1615,28 @@
         <v>17.3</v>
       </c>
       <c r="M4">
-        <v>0.5588329999999999</v>
+        <v>0.8382494999999999</v>
       </c>
       <c r="N4">
-        <v>16.741167</v>
+        <v>16.4617505</v>
       </c>
       <c r="O4">
-        <v>3.3482334</v>
+        <v>3.2923501</v>
       </c>
       <c r="P4">
-        <v>13.3929336</v>
+        <v>13.1694004</v>
       </c>
       <c r="Q4">
-        <v>78.89293359999999</v>
+        <v>78.6694004</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08754427784316016</v>
+        <v>0.08788994320848256</v>
       </c>
       <c r="T4">
-        <v>0.8583062890690732</v>
+        <v>0.8654135327992026</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>30.95737009088583</v>
+        <v>20.63824672725722</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08646044491222808</v>
+        <v>0.08632269753815923</v>
       </c>
       <c r="C5">
-        <v>498.0291151351095</v>
+        <v>493.3322864555215</v>
       </c>
       <c r="D5">
-        <v>504.7641151351095</v>
+        <v>505.6222864555215</v>
       </c>
       <c r="E5">
-        <v>-366.135</v>
+        <v>-360.58</v>
       </c>
       <c r="F5">
-        <v>16.665</v>
+        <v>22.22</v>
       </c>
       <c r="G5">
         <v>9.93</v>
@@ -1697,28 +1697,28 @@
         <v>17.3</v>
       </c>
       <c r="M5">
-        <v>0.8382494999999999</v>
+        <v>1.117666</v>
       </c>
       <c r="N5">
-        <v>16.4617505</v>
+        <v>16.182334</v>
       </c>
       <c r="O5">
-        <v>3.2923501</v>
+        <v>3.2364668</v>
       </c>
       <c r="P5">
-        <v>13.1694004</v>
+        <v>12.9458672</v>
       </c>
       <c r="Q5">
-        <v>78.6694004</v>
+        <v>78.4458672</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08788994320848256</v>
+        <v>0.08824280993558253</v>
       </c>
       <c r="T5">
-        <v>0.8654135327992026</v>
+        <v>0.8726688441070432</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>20.63824672725722</v>
+        <v>15.47868504544291</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08632269753815923</v>
+        <v>0.08624495016409035</v>
       </c>
       <c r="C6">
-        <v>493.3322864555215</v>
+        <v>488.2629450519629</v>
       </c>
       <c r="D6">
-        <v>505.6222864555215</v>
+        <v>506.1079450519629</v>
       </c>
       <c r="E6">
-        <v>-360.58</v>
+        <v>-355.025</v>
       </c>
       <c r="F6">
-        <v>22.22</v>
+        <v>27.775</v>
       </c>
       <c r="G6">
         <v>9.93</v>
@@ -1779,45 +1779,45 @@
         <v>17.3</v>
       </c>
       <c r="M6">
-        <v>1.117666</v>
+        <v>1.438745</v>
       </c>
       <c r="N6">
-        <v>16.182334</v>
+        <v>15.861255</v>
       </c>
       <c r="O6">
-        <v>3.2364668</v>
+        <v>3.172250999999999</v>
       </c>
       <c r="P6">
-        <v>12.9458672</v>
+        <v>12.689004</v>
       </c>
       <c r="Q6">
-        <v>78.4458672</v>
+        <v>78.189004</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08824280993558253</v>
+        <v>0.08860310543588458</v>
       </c>
       <c r="T6">
-        <v>0.8726688441070432</v>
+        <v>0.8800768988108379</v>
       </c>
       <c r="U6">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V6">
         <v>0.2</v>
       </c>
       <c r="W6">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y6">
-        <v>15.47868504544291</v>
+        <v>12.02436846001202</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08624495016409035</v>
+        <v>0.0861192027900215</v>
       </c>
       <c r="C7">
-        <v>488.2629450519629</v>
+        <v>483.4954194334004</v>
       </c>
       <c r="D7">
-        <v>506.1079450519629</v>
+        <v>506.8954194334004</v>
       </c>
       <c r="E7">
-        <v>-355.025</v>
+        <v>-349.47</v>
       </c>
       <c r="F7">
-        <v>27.775</v>
+        <v>33.33000000000001</v>
       </c>
       <c r="G7">
         <v>9.93</v>
@@ -1861,28 +1861,28 @@
         <v>17.3</v>
       </c>
       <c r="M7">
-        <v>1.438745</v>
+        <v>1.726494</v>
       </c>
       <c r="N7">
-        <v>15.861255</v>
+        <v>15.573506</v>
       </c>
       <c r="O7">
-        <v>3.172250999999999</v>
+        <v>3.114701199999999</v>
       </c>
       <c r="P7">
-        <v>12.689004</v>
+        <v>12.4588048</v>
       </c>
       <c r="Q7">
-        <v>78.189004</v>
+        <v>77.9588048</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08860310543588458</v>
+        <v>0.08897106679789521</v>
       </c>
       <c r="T7">
-        <v>0.8800768988108379</v>
+        <v>0.8876425716998202</v>
       </c>
       <c r="U7">
         <v>0.0518</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>12.02436846001202</v>
+        <v>10.02030705001002</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0861192027900215</v>
+        <v>0.08608865541595262</v>
       </c>
       <c r="C8">
-        <v>483.4954194334004</v>
+        <v>478.1320879534798</v>
       </c>
       <c r="D8">
-        <v>506.8954194334004</v>
+        <v>507.0870879534797</v>
       </c>
       <c r="E8">
-        <v>-349.47</v>
+        <v>-343.915</v>
       </c>
       <c r="F8">
-        <v>33.33</v>
+        <v>38.885</v>
       </c>
       <c r="G8">
         <v>9.93</v>
@@ -1943,45 +1943,45 @@
         <v>17.3</v>
       </c>
       <c r="M8">
-        <v>1.726494</v>
+        <v>2.0803475</v>
       </c>
       <c r="N8">
-        <v>15.573506</v>
+        <v>15.2196525</v>
       </c>
       <c r="O8">
-        <v>3.114701199999999</v>
+        <v>3.0439305</v>
       </c>
       <c r="P8">
-        <v>12.4588048</v>
+        <v>12.175722</v>
       </c>
       <c r="Q8">
-        <v>77.9588048</v>
+        <v>77.67572199999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08897106679789521</v>
+        <v>0.08934694130747593</v>
       </c>
       <c r="T8">
-        <v>0.8876425716998202</v>
+        <v>0.8953709472315761</v>
       </c>
       <c r="U8">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y8">
-        <v>10.02030705001002</v>
+        <v>8.315918374213922</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08608865541595261</v>
+        <v>0.08602770804188374</v>
       </c>
       <c r="C9">
-        <v>478.1320879534798</v>
+        <v>472.9599337251805</v>
       </c>
       <c r="D9">
-        <v>507.0870879534798</v>
+        <v>507.4699337251805</v>
       </c>
       <c r="E9">
-        <v>-343.915</v>
+        <v>-338.36</v>
       </c>
       <c r="F9">
-        <v>38.88500000000001</v>
+        <v>44.44</v>
       </c>
       <c r="G9">
         <v>9.93</v>
@@ -2025,45 +2025,45 @@
         <v>17.3</v>
       </c>
       <c r="M9">
-        <v>2.0803475</v>
+        <v>2.413092</v>
       </c>
       <c r="N9">
-        <v>15.2196525</v>
+        <v>14.886908</v>
       </c>
       <c r="O9">
-        <v>3.0439305</v>
+        <v>2.9773816</v>
       </c>
       <c r="P9">
-        <v>12.175722</v>
+        <v>11.9095264</v>
       </c>
       <c r="Q9">
-        <v>77.67572199999999</v>
+        <v>77.4095264</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08934694130747593</v>
+        <v>0.08973098700204754</v>
       </c>
       <c r="T9">
-        <v>0.8953709472315761</v>
+        <v>0.9032673309270657</v>
       </c>
       <c r="U9">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V9">
         <v>0.2</v>
       </c>
       <c r="W9">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y9">
-        <v>8.315918374213922</v>
+        <v>7.169225209813799</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08602770804188374</v>
+        <v>0.08592196066781486</v>
       </c>
       <c r="C10">
-        <v>472.9599337251805</v>
+        <v>468.0705677154518</v>
       </c>
       <c r="D10">
-        <v>507.4699337251805</v>
+        <v>508.1355677154519</v>
       </c>
       <c r="E10">
-        <v>-338.36</v>
+        <v>-332.805</v>
       </c>
       <c r="F10">
-        <v>44.44</v>
+        <v>49.995</v>
       </c>
       <c r="G10">
         <v>9.93</v>
@@ -2107,28 +2107,28 @@
         <v>17.3</v>
       </c>
       <c r="M10">
-        <v>2.413092</v>
+        <v>2.7147285</v>
       </c>
       <c r="N10">
-        <v>14.886908</v>
+        <v>14.5852715</v>
       </c>
       <c r="O10">
-        <v>2.9773816</v>
+        <v>2.9170543</v>
       </c>
       <c r="P10">
-        <v>11.9095264</v>
+        <v>11.6682172</v>
       </c>
       <c r="Q10">
-        <v>77.4095264</v>
+        <v>77.1682172</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08973098700204754</v>
+        <v>0.09012347326133502</v>
       </c>
       <c r="T10">
-        <v>0.9032673309270657</v>
+        <v>0.9113372615169616</v>
       </c>
       <c r="U10">
         <v>0.0543</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>7.169225209813799</v>
+        <v>6.372644630945598</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08592196066781486</v>
+        <v>0.08589621329374601</v>
       </c>
       <c r="C11">
-        <v>468.0705677154518</v>
+        <v>462.6779007254125</v>
       </c>
       <c r="D11">
-        <v>508.1355677154519</v>
+        <v>508.2979007254125</v>
       </c>
       <c r="E11">
-        <v>-332.805</v>
+        <v>-327.25</v>
       </c>
       <c r="F11">
-        <v>49.995</v>
+        <v>55.55</v>
       </c>
       <c r="G11">
         <v>9.93</v>
@@ -2189,45 +2189,45 @@
         <v>17.3</v>
       </c>
       <c r="M11">
-        <v>2.7147285</v>
+        <v>3.071915</v>
       </c>
       <c r="N11">
-        <v>14.5852715</v>
+        <v>14.228085</v>
       </c>
       <c r="O11">
-        <v>2.9170543</v>
+        <v>2.845616999999999</v>
       </c>
       <c r="P11">
-        <v>11.6682172</v>
+        <v>11.382468</v>
       </c>
       <c r="Q11">
-        <v>77.1682172</v>
+        <v>76.882468</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09012347326133502</v>
+        <v>0.09052468143749556</v>
       </c>
       <c r="T11">
-        <v>0.9113372615169616</v>
+        <v>0.9195865238977442</v>
       </c>
       <c r="U11">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V11">
         <v>0.2</v>
       </c>
       <c r="W11">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y11">
-        <v>6.372644630945598</v>
+        <v>5.631666240765124</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08589621329374601</v>
+        <v>0.08579846591967713</v>
       </c>
       <c r="C12">
-        <v>462.6779007254125</v>
+        <v>457.7401275088598</v>
       </c>
       <c r="D12">
-        <v>508.2979007254125</v>
+        <v>508.9151275088598</v>
       </c>
       <c r="E12">
-        <v>-327.25</v>
+        <v>-321.695</v>
       </c>
       <c r="F12">
-        <v>55.55</v>
+        <v>61.105</v>
       </c>
       <c r="G12">
         <v>9.93</v>
@@ -2271,28 +2271,28 @@
         <v>17.3</v>
       </c>
       <c r="M12">
-        <v>3.071915</v>
+        <v>3.3791065</v>
       </c>
       <c r="N12">
-        <v>14.228085</v>
+        <v>13.9208935</v>
       </c>
       <c r="O12">
-        <v>2.845616999999999</v>
+        <v>2.7841787</v>
       </c>
       <c r="P12">
-        <v>11.382468</v>
+        <v>11.1367148</v>
       </c>
       <c r="Q12">
-        <v>76.882468</v>
+        <v>76.63671479999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09052468143749556</v>
+        <v>0.09093490552772712</v>
       </c>
       <c r="T12">
-        <v>0.9195865238977444</v>
+        <v>0.9280211629612412</v>
       </c>
       <c r="U12">
         <v>0.0553</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>5.631666240765124</v>
+        <v>5.11969658251375</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08579846591967713</v>
+        <v>0.08570071854560826</v>
       </c>
       <c r="C13">
-        <v>457.7401275088598</v>
+        <v>452.8038551132829</v>
       </c>
       <c r="D13">
-        <v>508.9151275088598</v>
+        <v>509.5338551132829</v>
       </c>
       <c r="E13">
-        <v>-321.695</v>
+        <v>-316.14</v>
       </c>
       <c r="F13">
-        <v>61.105</v>
+        <v>66.66</v>
       </c>
       <c r="G13">
         <v>9.93</v>
@@ -2353,28 +2353,28 @@
         <v>17.3</v>
       </c>
       <c r="M13">
-        <v>3.3791065</v>
+        <v>3.686298</v>
       </c>
       <c r="N13">
-        <v>13.9208935</v>
+        <v>13.613702</v>
       </c>
       <c r="O13">
-        <v>2.7841787</v>
+        <v>2.722740399999999</v>
       </c>
       <c r="P13">
-        <v>11.1367148</v>
+        <v>10.8909616</v>
       </c>
       <c r="Q13">
-        <v>76.63671479999999</v>
+        <v>76.3909616</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09093490552772712</v>
+        <v>0.09135445289273667</v>
       </c>
       <c r="T13">
-        <v>0.9280211629612412</v>
+        <v>0.9366474983670903</v>
       </c>
       <c r="U13">
         <v>0.0553</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.11969658251375</v>
+        <v>4.693055200637604</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08570071854560826</v>
+        <v>0.08586297117153939</v>
       </c>
       <c r="C14">
-        <v>452.8038551132829</v>
+        <v>446.222640370117</v>
       </c>
       <c r="D14">
-        <v>509.5338551132829</v>
+        <v>508.5076403701171</v>
       </c>
       <c r="E14">
-        <v>-316.14</v>
+        <v>-310.585</v>
       </c>
       <c r="F14">
-        <v>66.66</v>
+        <v>72.215</v>
       </c>
       <c r="G14">
         <v>9.93</v>
@@ -2435,45 +2435,45 @@
         <v>17.3</v>
       </c>
       <c r="M14">
-        <v>3.686298</v>
+        <v>4.174027000000001</v>
       </c>
       <c r="N14">
-        <v>13.613702</v>
+        <v>13.125973</v>
       </c>
       <c r="O14">
-        <v>2.722740399999999</v>
+        <v>2.625194599999999</v>
       </c>
       <c r="P14">
-        <v>10.8909616</v>
+        <v>10.5007784</v>
       </c>
       <c r="Q14">
-        <v>76.3909616</v>
+        <v>76.0007784</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09135445289273667</v>
+        <v>0.09178364502475793</v>
       </c>
       <c r="T14">
-        <v>0.9366474983670903</v>
+        <v>0.9454721403339933</v>
       </c>
       <c r="U14">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V14">
         <v>0.2</v>
       </c>
       <c r="W14">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y14">
-        <v>4.693055200637604</v>
+        <v>4.144678508308642</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08586297117153939</v>
+        <v>0.08617722379747053</v>
       </c>
       <c r="C15">
-        <v>446.222640370117</v>
+        <v>438.6917671599118</v>
       </c>
       <c r="D15">
-        <v>508.5076403701171</v>
+        <v>506.5317671599118</v>
       </c>
       <c r="E15">
-        <v>-310.585</v>
+        <v>-305.03</v>
       </c>
       <c r="F15">
-        <v>72.215</v>
+        <v>77.77000000000001</v>
       </c>
       <c r="G15">
         <v>9.93</v>
@@ -2517,45 +2517,45 @@
         <v>17.3</v>
       </c>
       <c r="M15">
-        <v>4.174027000000001</v>
+        <v>4.767301000000001</v>
       </c>
       <c r="N15">
-        <v>13.125973</v>
+        <v>12.532699</v>
       </c>
       <c r="O15">
-        <v>2.625194599999999</v>
+        <v>2.5065398</v>
       </c>
       <c r="P15">
-        <v>10.5007784</v>
+        <v>10.0261592</v>
       </c>
       <c r="Q15">
-        <v>76.0007784</v>
+        <v>75.5261592</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09178364502475793</v>
+        <v>0.09222281836915178</v>
       </c>
       <c r="T15">
-        <v>0.9454721403339933</v>
+        <v>0.9545020065326848</v>
       </c>
       <c r="U15">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>4.144678508308642</v>
+        <v>3.628887708160235</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08617722379747053</v>
+        <v>0.08646347642340166</v>
       </c>
       <c r="C16">
-        <v>438.6917671599118</v>
+        <v>431.3502614658732</v>
       </c>
       <c r="D16">
-        <v>506.5317671599118</v>
+        <v>504.7452614658733</v>
       </c>
       <c r="E16">
-        <v>-305.03</v>
+        <v>-299.475</v>
       </c>
       <c r="F16">
-        <v>77.77000000000001</v>
+        <v>83.32500000000002</v>
       </c>
       <c r="G16">
         <v>9.93</v>
@@ -2599,45 +2599,45 @@
         <v>17.3</v>
       </c>
       <c r="M16">
-        <v>4.767301000000001</v>
+        <v>5.341132500000001</v>
       </c>
       <c r="N16">
-        <v>12.532699</v>
+        <v>11.9588675</v>
       </c>
       <c r="O16">
-        <v>2.5065398</v>
+        <v>2.391773499999999</v>
       </c>
       <c r="P16">
-        <v>10.0261592</v>
+        <v>9.567093999999997</v>
       </c>
       <c r="Q16">
-        <v>75.5261592</v>
+        <v>75.067094</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09222281836915178</v>
+        <v>0.09267232520400195</v>
       </c>
       <c r="T16">
-        <v>0.9545020065326848</v>
+        <v>0.9637443401713455</v>
       </c>
       <c r="U16">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y16">
-        <v>3.628887708160235</v>
+        <v>3.239013448926795</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08646347642340166</v>
+        <v>0.08643612904933279</v>
       </c>
       <c r="C17">
-        <v>431.3502614658733</v>
+        <v>425.9653920837706</v>
       </c>
       <c r="D17">
-        <v>504.7452614658733</v>
+        <v>504.9153920837705</v>
       </c>
       <c r="E17">
-        <v>-299.475</v>
+        <v>-293.92</v>
       </c>
       <c r="F17">
-        <v>83.325</v>
+        <v>88.88</v>
       </c>
       <c r="G17">
         <v>9.93</v>
@@ -2681,28 +2681,28 @@
         <v>17.3</v>
       </c>
       <c r="M17">
-        <v>5.341132500000001</v>
+        <v>5.697208</v>
       </c>
       <c r="N17">
-        <v>11.9588675</v>
+        <v>11.602792</v>
       </c>
       <c r="O17">
-        <v>2.391773499999999</v>
+        <v>2.320558399999999</v>
       </c>
       <c r="P17">
-        <v>9.567093999999997</v>
+        <v>9.282233599999998</v>
       </c>
       <c r="Q17">
-        <v>75.067094</v>
+        <v>74.7822336</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09267232520400195</v>
+        <v>0.09313253458253903</v>
       </c>
       <c r="T17">
-        <v>0.9637443401713455</v>
+        <v>0.9732067293728314</v>
       </c>
       <c r="U17">
         <v>0.0641</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>3.239013448926795</v>
+        <v>3.036575108368871</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08643612904933279</v>
+        <v>0.08746958167526392</v>
       </c>
       <c r="C18">
-        <v>425.9653920837706</v>
+        <v>414.0599073373596</v>
       </c>
       <c r="D18">
-        <v>504.9153920837705</v>
+        <v>498.5649073373596</v>
       </c>
       <c r="E18">
-        <v>-293.92</v>
+        <v>-288.365</v>
       </c>
       <c r="F18">
-        <v>88.88</v>
+        <v>94.435</v>
       </c>
       <c r="G18">
         <v>9.93</v>
@@ -2763,45 +2763,45 @@
         <v>17.3</v>
       </c>
       <c r="M18">
-        <v>5.697208</v>
+        <v>6.789876500000001</v>
       </c>
       <c r="N18">
-        <v>11.602792</v>
+        <v>10.5101235</v>
       </c>
       <c r="O18">
-        <v>2.320558399999999</v>
+        <v>2.102024699999999</v>
       </c>
       <c r="P18">
-        <v>9.282233599999998</v>
+        <v>8.408098799999996</v>
       </c>
       <c r="Q18">
-        <v>74.7822336</v>
+        <v>73.90809879999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09313253458253903</v>
+        <v>0.09360383334369146</v>
       </c>
       <c r="T18">
-        <v>0.9732067293728314</v>
+        <v>0.9828971279526665</v>
       </c>
       <c r="U18">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V18">
         <v>0.2</v>
       </c>
       <c r="W18">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>3.036575108368871</v>
+        <v>2.547910849335771</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08746958167526392</v>
+        <v>0.08806623430119506</v>
       </c>
       <c r="C19">
-        <v>414.0599073373596</v>
+        <v>404.9107360257805</v>
       </c>
       <c r="D19">
-        <v>498.5649073373596</v>
+        <v>494.9707360257805</v>
       </c>
       <c r="E19">
-        <v>-288.365</v>
+        <v>-282.81</v>
       </c>
       <c r="F19">
-        <v>94.435</v>
+        <v>99.99000000000001</v>
       </c>
       <c r="G19">
         <v>9.93</v>
@@ -2845,45 +2845,45 @@
         <v>17.3</v>
       </c>
       <c r="M19">
-        <v>6.789876500000001</v>
+        <v>7.579242000000002</v>
       </c>
       <c r="N19">
-        <v>10.5101235</v>
+        <v>9.720757999999996</v>
       </c>
       <c r="O19">
-        <v>2.102024699999999</v>
+        <v>1.944151599999999</v>
       </c>
       <c r="P19">
-        <v>8.408098799999996</v>
+        <v>7.776606399999997</v>
       </c>
       <c r="Q19">
-        <v>73.90809879999999</v>
+        <v>73.27660639999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09360383334369146</v>
+        <v>0.09408662719657934</v>
       </c>
       <c r="T19">
-        <v>0.9828971279526665</v>
+        <v>0.9928238777173757</v>
       </c>
       <c r="U19">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y19">
-        <v>2.547910849335771</v>
+        <v>2.282550154751622</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08806623430119505</v>
+        <v>0.08813248692712621</v>
       </c>
       <c r="C20">
-        <v>404.9107360257807</v>
+        <v>398.9598313613956</v>
       </c>
       <c r="D20">
-        <v>494.9707360257807</v>
+        <v>494.5748313613956</v>
       </c>
       <c r="E20">
-        <v>-282.81</v>
+        <v>-277.255</v>
       </c>
       <c r="F20">
-        <v>99.98999999999999</v>
+        <v>105.545</v>
       </c>
       <c r="G20">
         <v>9.93</v>
@@ -2927,28 +2927,28 @@
         <v>17.3</v>
       </c>
       <c r="M20">
-        <v>7.579242</v>
+        <v>8.000311</v>
       </c>
       <c r="N20">
-        <v>9.720757999999996</v>
+        <v>9.299688999999997</v>
       </c>
       <c r="O20">
-        <v>1.944151599999999</v>
+        <v>1.8599378</v>
       </c>
       <c r="P20">
-        <v>7.776606399999997</v>
+        <v>7.439751199999998</v>
       </c>
       <c r="Q20">
-        <v>73.27660639999999</v>
+        <v>72.9397512</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09408662719657933</v>
+        <v>0.09458134188534098</v>
       </c>
       <c r="T20">
-        <v>0.9928238777173755</v>
+        <v>1.002995732414547</v>
       </c>
       <c r="U20">
         <v>0.07580000000000001</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>2.282550154751623</v>
+        <v>2.162415936080484</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08813248692712621</v>
+        <v>0.08819873955305732</v>
       </c>
       <c r="C21">
-        <v>398.9598313613956</v>
+        <v>393.0095595232465</v>
       </c>
       <c r="D21">
-        <v>494.5748313613956</v>
+        <v>494.1795595232466</v>
       </c>
       <c r="E21">
-        <v>-277.255</v>
+        <v>-271.7</v>
       </c>
       <c r="F21">
-        <v>105.545</v>
+        <v>111.1</v>
       </c>
       <c r="G21">
         <v>9.93</v>
@@ -3009,28 +3009,28 @@
         <v>17.3</v>
       </c>
       <c r="M21">
-        <v>8.000311</v>
+        <v>8.421380000000001</v>
       </c>
       <c r="N21">
-        <v>9.299688999999997</v>
+        <v>8.878619999999996</v>
       </c>
       <c r="O21">
-        <v>1.8599378</v>
+        <v>1.775723999999999</v>
       </c>
       <c r="P21">
-        <v>7.439751199999998</v>
+        <v>7.102895999999997</v>
       </c>
       <c r="Q21">
-        <v>72.9397512</v>
+        <v>72.602896</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09458134188534098</v>
+        <v>0.09508842444132165</v>
       </c>
       <c r="T21">
-        <v>1.002995732414547</v>
+        <v>1.013421883479147</v>
       </c>
       <c r="U21">
         <v>0.07580000000000001</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>2.162415936080484</v>
+        <v>2.05429513927646</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08819873955305732</v>
+        <v>0.09065059217898845</v>
       </c>
       <c r="C22">
-        <v>393.0095595232465</v>
+        <v>373.2580674344962</v>
       </c>
       <c r="D22">
-        <v>494.1795595232466</v>
+        <v>479.9830674344963</v>
       </c>
       <c r="E22">
-        <v>-271.7</v>
+        <v>-266.145</v>
       </c>
       <c r="F22">
-        <v>111.1</v>
+        <v>116.655</v>
       </c>
       <c r="G22">
         <v>9.93</v>
@@ -3091,45 +3091,45 @@
         <v>17.3</v>
       </c>
       <c r="M22">
-        <v>8.421380000000001</v>
+        <v>10.49895</v>
       </c>
       <c r="N22">
-        <v>8.878619999999996</v>
+        <v>6.801049999999996</v>
       </c>
       <c r="O22">
-        <v>1.775723999999999</v>
+        <v>1.360209999999999</v>
       </c>
       <c r="P22">
-        <v>7.102895999999997</v>
+        <v>5.440839999999997</v>
       </c>
       <c r="Q22">
-        <v>72.602896</v>
+        <v>70.94083999999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09508842444132165</v>
+        <v>0.09560834453036512</v>
       </c>
       <c r="T22">
-        <v>1.013421883479147</v>
+        <v>1.024111987735256</v>
       </c>
       <c r="U22">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V22">
         <v>0.2</v>
       </c>
       <c r="W22">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>2.05429513927646</v>
+        <v>1.647783826001648</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09065059217898845</v>
+        <v>0.09083044480491959</v>
       </c>
       <c r="C23">
-        <v>373.2580674344963</v>
+        <v>366.6937439120154</v>
       </c>
       <c r="D23">
-        <v>479.9830674344963</v>
+        <v>478.9737439120154</v>
       </c>
       <c r="E23">
-        <v>-266.145</v>
+        <v>-260.59</v>
       </c>
       <c r="F23">
-        <v>116.655</v>
+        <v>122.21</v>
       </c>
       <c r="G23">
         <v>9.93</v>
@@ -3173,28 +3173,28 @@
         <v>17.3</v>
       </c>
       <c r="M23">
-        <v>10.49895</v>
+        <v>10.9989</v>
       </c>
       <c r="N23">
-        <v>6.801049999999998</v>
+        <v>6.301099999999998</v>
       </c>
       <c r="O23">
-        <v>1.36021</v>
+        <v>1.26022</v>
       </c>
       <c r="P23">
-        <v>5.440839999999999</v>
+        <v>5.040879999999999</v>
       </c>
       <c r="Q23">
-        <v>70.94083999999999</v>
+        <v>70.54088</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09560834453036512</v>
+        <v>0.09614159590374305</v>
       </c>
       <c r="T23">
-        <v>1.024111987735256</v>
+        <v>1.035076197228701</v>
       </c>
       <c r="U23">
         <v>0.09</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>1.647783826001648</v>
+        <v>1.572884561183391</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09083044480491959</v>
+        <v>0.09101029743085071</v>
       </c>
       <c r="C24">
-        <v>366.6937439120154</v>
+        <v>360.1336563566401</v>
       </c>
       <c r="D24">
-        <v>478.9737439120154</v>
+        <v>477.9686563566401</v>
       </c>
       <c r="E24">
-        <v>-260.59</v>
+        <v>-255.035</v>
       </c>
       <c r="F24">
-        <v>122.21</v>
+        <v>127.765</v>
       </c>
       <c r="G24">
         <v>9.93</v>
@@ -3255,28 +3255,28 @@
         <v>17.3</v>
       </c>
       <c r="M24">
-        <v>10.9989</v>
+        <v>11.49885</v>
       </c>
       <c r="N24">
-        <v>6.301099999999998</v>
+        <v>5.801149999999998</v>
       </c>
       <c r="O24">
-        <v>1.26022</v>
+        <v>1.16023</v>
       </c>
       <c r="P24">
-        <v>5.040879999999999</v>
+        <v>4.640919999999999</v>
       </c>
       <c r="Q24">
-        <v>70.54088</v>
+        <v>70.14091999999999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09614159590374305</v>
+        <v>0.09668869796214377</v>
       </c>
       <c r="T24">
-        <v>1.035076197228701</v>
+        <v>1.046325191384314</v>
       </c>
       <c r="U24">
         <v>0.09</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>1.572884561183391</v>
+        <v>1.504498275914548</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09101029743085071</v>
+        <v>0.1031423359289532</v>
       </c>
       <c r="C25">
-        <v>360.1336563566401</v>
+        <v>295.3115464147407</v>
       </c>
       <c r="D25">
-        <v>477.9686563566401</v>
+        <v>418.7015464147407</v>
       </c>
       <c r="E25">
-        <v>-255.035</v>
+        <v>-249.48</v>
       </c>
       <c r="F25">
-        <v>127.765</v>
+        <v>133.32</v>
       </c>
       <c r="G25">
         <v>9.93</v>
@@ -3337,45 +3337,45 @@
         <v>17.3</v>
       </c>
       <c r="M25">
-        <v>11.49885</v>
+        <v>19.571376</v>
       </c>
       <c r="N25">
-        <v>5.801149999999998</v>
+        <v>-2.271376000000007</v>
       </c>
       <c r="O25">
-        <v>1.16023</v>
+        <v>-0.4542752000000014</v>
       </c>
       <c r="P25">
-        <v>4.640919999999999</v>
+        <v>-1.817100800000006</v>
       </c>
       <c r="Q25">
-        <v>70.14091999999999</v>
+        <v>63.68289919999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09668869796214377</v>
+        <v>0.09755126156742028</v>
       </c>
       <c r="T25">
-        <v>1.046325191384314</v>
+        <v>1.064060406972724</v>
       </c>
       <c r="U25">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V25">
-        <v>0.2</v>
+        <v>0.1767887960458171</v>
       </c>
       <c r="W25">
-        <v>0.07199999999999999</v>
+        <v>0.1208474047404741</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y25">
-        <v>1.504498275914548</v>
+        <v>0.8839439802290853</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1031423359289532</v>
+        <v>0.1041523359289532</v>
       </c>
       <c r="C26">
-        <v>295.3115464147407</v>
+        <v>285.4784921190051</v>
       </c>
       <c r="D26">
-        <v>418.7015464147407</v>
+        <v>414.4234921190051</v>
       </c>
       <c r="E26">
-        <v>-249.48</v>
+        <v>-243.925</v>
       </c>
       <c r="F26">
-        <v>133.32</v>
+        <v>138.875</v>
       </c>
       <c r="G26">
         <v>9.93</v>
@@ -3419,37 +3419,37 @@
         <v>17.3</v>
       </c>
       <c r="M26">
-        <v>19.571376</v>
+        <v>20.38685</v>
       </c>
       <c r="N26">
-        <v>-2.271376000000004</v>
+        <v>-3.086850000000005</v>
       </c>
       <c r="O26">
-        <v>-0.4542752000000008</v>
+        <v>-0.6173700000000011</v>
       </c>
       <c r="P26">
-        <v>-1.817100800000003</v>
+        <v>-2.469480000000004</v>
       </c>
       <c r="Q26">
-        <v>63.68289919999999</v>
+        <v>63.03052</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09755126156742028</v>
+        <v>0.0982412783883192</v>
       </c>
       <c r="T26">
-        <v>1.064060406972724</v>
+        <v>1.078247879065693</v>
       </c>
       <c r="U26">
         <v>0.1468</v>
       </c>
       <c r="V26">
-        <v>0.1767887960458171</v>
+        <v>0.1697172442039844</v>
       </c>
       <c r="W26">
-        <v>0.1208474047404741</v>
+        <v>0.1218855085508551</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.8839439802290854</v>
+        <v>0.8485862210199219</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1041523359289532</v>
+        <v>0.1051623359289532</v>
       </c>
       <c r="C27">
-        <v>285.4784921190051</v>
+        <v>275.7319750866577</v>
       </c>
       <c r="D27">
-        <v>414.4234921190051</v>
+        <v>410.2319750866577</v>
       </c>
       <c r="E27">
-        <v>-243.925</v>
+        <v>-238.37</v>
       </c>
       <c r="F27">
-        <v>138.875</v>
+        <v>144.43</v>
       </c>
       <c r="G27">
         <v>9.93</v>
@@ -3501,37 +3501,37 @@
         <v>17.3</v>
       </c>
       <c r="M27">
-        <v>20.38685</v>
+        <v>21.202324</v>
       </c>
       <c r="N27">
-        <v>-3.086850000000005</v>
+        <v>-3.902324000000007</v>
       </c>
       <c r="O27">
-        <v>-0.6173700000000011</v>
+        <v>-0.7804648000000015</v>
       </c>
       <c r="P27">
-        <v>-2.469480000000004</v>
+        <v>-3.121859200000006</v>
       </c>
       <c r="Q27">
-        <v>63.03052</v>
+        <v>62.3781408</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0982412783883192</v>
+        <v>0.09894994431248569</v>
       </c>
       <c r="T27">
-        <v>1.078247879065693</v>
+        <v>1.092818796350365</v>
       </c>
       <c r="U27">
         <v>0.1468</v>
       </c>
       <c r="V27">
-        <v>0.1697172442039844</v>
+        <v>0.1631896578884465</v>
       </c>
       <c r="W27">
-        <v>0.1218855085508551</v>
+        <v>0.1228437582219761</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.8485862210199219</v>
+        <v>0.8159482894422325</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1051623359289532</v>
+        <v>0.1212209979067049</v>
       </c>
       <c r="C28">
-        <v>275.7319750866577</v>
+        <v>213.3462797223793</v>
       </c>
       <c r="D28">
-        <v>410.2319750866577</v>
+        <v>353.4012797223793</v>
       </c>
       <c r="E28">
-        <v>-238.37</v>
+        <v>-232.815</v>
       </c>
       <c r="F28">
-        <v>144.43</v>
+        <v>149.985</v>
       </c>
       <c r="G28">
         <v>9.93</v>
@@ -3583,45 +3583,45 @@
         <v>17.3</v>
       </c>
       <c r="M28">
-        <v>21.202324</v>
+        <v>30.116988</v>
       </c>
       <c r="N28">
-        <v>-3.902324000000007</v>
+        <v>-12.81698800000001</v>
       </c>
       <c r="O28">
-        <v>-0.7804648000000015</v>
+        <v>-2.563397600000001</v>
       </c>
       <c r="P28">
-        <v>-3.121859200000006</v>
+        <v>-10.2535904</v>
       </c>
       <c r="Q28">
-        <v>62.3781408</v>
+        <v>55.24640959999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09894994431248569</v>
+        <v>0.1003200284506728</v>
       </c>
       <c r="T28">
-        <v>1.092818796350365</v>
+        <v>1.120989168270032</v>
       </c>
       <c r="U28">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V28">
-        <v>0.1631896578884465</v>
+        <v>0.1148853265140591</v>
       </c>
       <c r="W28">
-        <v>0.1228437582219761</v>
+        <v>0.177731026435977</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y28">
-        <v>0.8159482894422325</v>
+        <v>0.5744266325702954</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1212209979067049</v>
+        <v>0.1227709979067049</v>
       </c>
       <c r="C29">
-        <v>213.3462797223793</v>
+        <v>203.1281736730165</v>
       </c>
       <c r="D29">
-        <v>353.4012797223793</v>
+        <v>348.7381736730165</v>
       </c>
       <c r="E29">
-        <v>-232.815</v>
+        <v>-227.26</v>
       </c>
       <c r="F29">
-        <v>149.985</v>
+        <v>155.54</v>
       </c>
       <c r="G29">
         <v>9.93</v>
@@ -3665,37 +3665,37 @@
         <v>17.3</v>
       </c>
       <c r="M29">
-        <v>30.116988</v>
+        <v>31.23243200000001</v>
       </c>
       <c r="N29">
-        <v>-12.81698800000001</v>
+        <v>-13.93243200000001</v>
       </c>
       <c r="O29">
-        <v>-2.563397600000001</v>
+        <v>-2.786486400000002</v>
       </c>
       <c r="P29">
-        <v>-10.2535904</v>
+        <v>-11.14594560000001</v>
       </c>
       <c r="Q29">
-        <v>55.24640959999999</v>
+        <v>54.3540544</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1003200284506728</v>
+        <v>0.1010772510680432</v>
       </c>
       <c r="T29">
-        <v>1.120989168270032</v>
+        <v>1.136558462273783</v>
       </c>
       <c r="U29">
         <v>0.2008</v>
       </c>
       <c r="V29">
-        <v>0.1148853265140591</v>
+        <v>0.110782279138557</v>
       </c>
       <c r="W29">
-        <v>0.177731026435977</v>
+        <v>0.1785549183489778</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.5744266325702954</v>
+        <v>0.5539113956927848</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1227709979067049</v>
+        <v>0.1243209979067049</v>
       </c>
       <c r="C30">
-        <v>203.1281736730165</v>
+        <v>193.0315237577551</v>
       </c>
       <c r="D30">
-        <v>348.7381736730165</v>
+        <v>344.1965237577551</v>
       </c>
       <c r="E30">
-        <v>-227.26</v>
+        <v>-221.705</v>
       </c>
       <c r="F30">
-        <v>155.54</v>
+        <v>161.095</v>
       </c>
       <c r="G30">
         <v>9.93</v>
@@ -3747,37 +3747,37 @@
         <v>17.3</v>
       </c>
       <c r="M30">
-        <v>31.23243200000001</v>
+        <v>32.34787600000001</v>
       </c>
       <c r="N30">
-        <v>-13.93243200000001</v>
+        <v>-15.04787600000001</v>
       </c>
       <c r="O30">
-        <v>-2.786486400000002</v>
+        <v>-3.009575200000002</v>
       </c>
       <c r="P30">
-        <v>-11.14594560000001</v>
+        <v>-12.03830080000001</v>
       </c>
       <c r="Q30">
-        <v>54.3540544</v>
+        <v>53.46169919999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1010772510680432</v>
+        <v>0.1018558038999875</v>
       </c>
       <c r="T30">
-        <v>1.136558462273783</v>
+        <v>1.152566327939611</v>
       </c>
       <c r="U30">
         <v>0.2008</v>
       </c>
       <c r="V30">
-        <v>0.110782279138557</v>
+        <v>0.1069622005475722</v>
       </c>
       <c r="W30">
-        <v>0.1785549183489778</v>
+        <v>0.1793219901300475</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.5539113956927848</v>
+        <v>0.5348110027378612</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1243209979067049</v>
+        <v>0.1258709979067049</v>
       </c>
       <c r="C31">
-        <v>193.0315237577552</v>
+        <v>183.0516457755371</v>
       </c>
       <c r="D31">
-        <v>344.1965237577552</v>
+        <v>339.7716457755371</v>
       </c>
       <c r="E31">
-        <v>-221.705</v>
+        <v>-216.15</v>
       </c>
       <c r="F31">
-        <v>161.095</v>
+        <v>166.65</v>
       </c>
       <c r="G31">
         <v>9.93</v>
@@ -3829,37 +3829,37 @@
         <v>17.3</v>
       </c>
       <c r="M31">
-        <v>32.347876</v>
+        <v>33.46332</v>
       </c>
       <c r="N31">
-        <v>-15.047876</v>
+        <v>-16.16332000000001</v>
       </c>
       <c r="O31">
-        <v>-3.0095752</v>
+        <v>-3.232664000000002</v>
       </c>
       <c r="P31">
-        <v>-12.0383008</v>
+        <v>-12.930656</v>
       </c>
       <c r="Q31">
-        <v>53.4616992</v>
+        <v>52.56934399999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1018558038999875</v>
+        <v>0.1026566010985588</v>
       </c>
       <c r="T31">
-        <v>1.152566327939611</v>
+        <v>1.169031561195891</v>
       </c>
       <c r="U31">
         <v>0.2008</v>
       </c>
       <c r="V31">
-        <v>0.1069622005475723</v>
+        <v>0.1033967938626532</v>
       </c>
       <c r="W31">
-        <v>0.1793219901300475</v>
+        <v>0.1800379237923792</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.5348110027378613</v>
+        <v>0.5169839693132658</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1258709979067049</v>
+        <v>0.1274209979067049</v>
       </c>
       <c r="C32">
-        <v>183.0516457755371</v>
+        <v>173.184093342237</v>
       </c>
       <c r="D32">
-        <v>339.7716457755371</v>
+        <v>335.459093342237</v>
       </c>
       <c r="E32">
-        <v>-216.15</v>
+        <v>-210.595</v>
       </c>
       <c r="F32">
-        <v>166.65</v>
+        <v>172.205</v>
       </c>
       <c r="G32">
         <v>9.93</v>
@@ -3911,37 +3911,37 @@
         <v>17.3</v>
       </c>
       <c r="M32">
-        <v>33.46332</v>
+        <v>34.57876400000001</v>
       </c>
       <c r="N32">
-        <v>-16.16332000000001</v>
+        <v>-17.27876400000001</v>
       </c>
       <c r="O32">
-        <v>-3.232664000000002</v>
+        <v>-3.455752800000002</v>
       </c>
       <c r="P32">
-        <v>-12.930656</v>
+        <v>-13.82301120000001</v>
       </c>
       <c r="Q32">
-        <v>52.56934399999999</v>
+        <v>51.67698879999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1026566010985588</v>
+        <v>0.1034806098101321</v>
       </c>
       <c r="T32">
-        <v>1.169031561195891</v>
+        <v>1.185974047590034</v>
       </c>
       <c r="U32">
         <v>0.2008</v>
       </c>
       <c r="V32">
-        <v>0.1033967938626532</v>
+        <v>0.1000614134154708</v>
       </c>
       <c r="W32">
-        <v>0.1800379237923792</v>
+        <v>0.1807076681861735</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.5169839693132658</v>
+        <v>0.500307067077354</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1274209979067049</v>
+        <v>0.1403601086755366</v>
       </c>
       <c r="C33">
-        <v>173.184093342237</v>
+        <v>135.4908421883108</v>
       </c>
       <c r="D33">
-        <v>335.459093342237</v>
+        <v>303.3208421883108</v>
       </c>
       <c r="E33">
-        <v>-210.595</v>
+        <v>-205.04</v>
       </c>
       <c r="F33">
-        <v>172.205</v>
+        <v>177.76</v>
       </c>
       <c r="G33">
         <v>9.93</v>
@@ -3993,45 +3993,45 @@
         <v>17.3</v>
       </c>
       <c r="M33">
-        <v>34.57876400000001</v>
+        <v>41.915808</v>
       </c>
       <c r="N33">
-        <v>-17.27876400000001</v>
+        <v>-24.615808</v>
       </c>
       <c r="O33">
-        <v>-3.455752800000002</v>
+        <v>-4.9231616</v>
       </c>
       <c r="P33">
-        <v>-13.82301120000001</v>
+        <v>-19.6926464</v>
       </c>
       <c r="Q33">
-        <v>51.67698879999999</v>
+        <v>45.8073536</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1034806098101321</v>
+        <v>0.1046069581438572</v>
       </c>
       <c r="T33">
-        <v>1.185974047590034</v>
+        <v>1.209132954833584</v>
       </c>
       <c r="U33">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.1000614134154708</v>
+        <v>0.08254642258118941</v>
       </c>
       <c r="W33">
-        <v>0.1807076681861735</v>
+        <v>0.2163355535553556</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y33">
-        <v>0.500307067077354</v>
+        <v>0.412732112905947</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1403601086755366</v>
+        <v>0.1422601086755367</v>
       </c>
       <c r="C34">
-        <v>135.4908421883108</v>
+        <v>125.7279265562564</v>
       </c>
       <c r="D34">
-        <v>303.3208421883108</v>
+        <v>299.1129265562564</v>
       </c>
       <c r="E34">
-        <v>-205.04</v>
+        <v>-199.485</v>
       </c>
       <c r="F34">
-        <v>177.76</v>
+        <v>183.315</v>
       </c>
       <c r="G34">
         <v>9.93</v>
@@ -4075,37 +4075,37 @@
         <v>17.3</v>
       </c>
       <c r="M34">
-        <v>41.915808</v>
+        <v>43.225677</v>
       </c>
       <c r="N34">
-        <v>-24.615808</v>
+        <v>-25.92567700000001</v>
       </c>
       <c r="O34">
-        <v>-4.9231616</v>
+        <v>-5.185135400000002</v>
       </c>
       <c r="P34">
-        <v>-19.6926464</v>
+        <v>-20.74054160000001</v>
       </c>
       <c r="Q34">
-        <v>45.8073536</v>
+        <v>44.75945839999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1046069581438572</v>
+        <v>0.1054846739370491</v>
       </c>
       <c r="T34">
-        <v>1.209132954833584</v>
+        <v>1.227179715353488</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.08254642258118941</v>
+        <v>0.08004501583630487</v>
       </c>
       <c r="W34">
-        <v>0.2163355535553556</v>
+        <v>0.2169253852657993</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.412732112905947</v>
+        <v>0.4002250791815244</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1422601086755367</v>
+        <v>0.1441601086755366</v>
       </c>
       <c r="C35">
-        <v>125.7279265562564</v>
+        <v>116.0801647335042</v>
       </c>
       <c r="D35">
-        <v>299.1129265562564</v>
+        <v>295.0201647335042</v>
       </c>
       <c r="E35">
-        <v>-199.485</v>
+        <v>-193.93</v>
       </c>
       <c r="F35">
-        <v>183.315</v>
+        <v>188.87</v>
       </c>
       <c r="G35">
         <v>9.93</v>
@@ -4157,37 +4157,37 @@
         <v>17.3</v>
       </c>
       <c r="M35">
-        <v>43.225677</v>
+        <v>44.535546</v>
       </c>
       <c r="N35">
-        <v>-25.92567700000001</v>
+        <v>-27.23554600000001</v>
       </c>
       <c r="O35">
-        <v>-5.185135400000002</v>
+        <v>-5.447109200000002</v>
       </c>
       <c r="P35">
-        <v>-20.74054160000001</v>
+        <v>-21.78843680000001</v>
       </c>
       <c r="Q35">
-        <v>44.75945839999999</v>
+        <v>43.71156319999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1054846739370491</v>
+        <v>0.1063889871785195</v>
       </c>
       <c r="T35">
-        <v>1.227179715353488</v>
+        <v>1.245773347404299</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.08004501583630487</v>
+        <v>0.07769075066464885</v>
       </c>
       <c r="W35">
-        <v>0.2169253852657993</v>
+        <v>0.2174805209932758</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.4002250791815244</v>
+        <v>0.3884537533232442</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1441601086755366</v>
+        <v>0.1460601086755366</v>
       </c>
       <c r="C36">
-        <v>116.0801647335042</v>
+        <v>106.5428935775157</v>
       </c>
       <c r="D36">
-        <v>295.0201647335042</v>
+        <v>291.0378935775157</v>
       </c>
       <c r="E36">
-        <v>-193.93</v>
+        <v>-188.375</v>
       </c>
       <c r="F36">
-        <v>188.87</v>
+        <v>194.425</v>
       </c>
       <c r="G36">
         <v>9.93</v>
@@ -4239,37 +4239,37 @@
         <v>17.3</v>
       </c>
       <c r="M36">
-        <v>44.535546</v>
+        <v>45.845415</v>
       </c>
       <c r="N36">
-        <v>-27.23554600000001</v>
+        <v>-28.54541500000001</v>
       </c>
       <c r="O36">
-        <v>-5.447109200000002</v>
+        <v>-5.709083000000001</v>
       </c>
       <c r="P36">
-        <v>-21.78843680000001</v>
+        <v>-22.83633200000001</v>
       </c>
       <c r="Q36">
-        <v>43.71156319999999</v>
+        <v>42.66366799999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1063889871785195</v>
+        <v>0.1073211254428044</v>
       </c>
       <c r="T36">
-        <v>1.245773347404299</v>
+        <v>1.264939091210519</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.07769075066464885</v>
+        <v>0.07547101493137316</v>
       </c>
       <c r="W36">
-        <v>0.2174805209932758</v>
+        <v>0.2180039346791822</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.3884537533232442</v>
+        <v>0.3773550746568658</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1460601086755366</v>
+        <v>0.1479601086755367</v>
       </c>
       <c r="C37">
-        <v>106.5428935775157</v>
+        <v>97.1116983704581</v>
       </c>
       <c r="D37">
-        <v>291.0378935775157</v>
+        <v>287.1616983704581</v>
       </c>
       <c r="E37">
-        <v>-188.375</v>
+        <v>-182.82</v>
       </c>
       <c r="F37">
-        <v>194.425</v>
+        <v>199.98</v>
       </c>
       <c r="G37">
         <v>9.93</v>
@@ -4321,37 +4321,37 @@
         <v>17.3</v>
       </c>
       <c r="M37">
-        <v>45.845415</v>
+        <v>47.15528400000001</v>
       </c>
       <c r="N37">
-        <v>-28.54541500000001</v>
+        <v>-29.85528400000001</v>
       </c>
       <c r="O37">
-        <v>-5.709083000000001</v>
+        <v>-5.971056800000003</v>
       </c>
       <c r="P37">
-        <v>-22.83633200000001</v>
+        <v>-23.88422720000001</v>
       </c>
       <c r="Q37">
-        <v>42.66366799999999</v>
+        <v>41.61577279999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1073211254428044</v>
+        <v>0.1082823930278482</v>
       </c>
       <c r="T37">
-        <v>1.264939091210519</v>
+        <v>1.284703764510683</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.07547101493137316</v>
+        <v>0.07337459784994613</v>
       </c>
       <c r="W37">
-        <v>0.2180039346791822</v>
+        <v>0.2184982698269827</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.3773550746568658</v>
+        <v>0.3668729892497307</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1479601086755367</v>
+        <v>0.1498601086755366</v>
       </c>
       <c r="C38">
-        <v>97.11169837045813</v>
+        <v>87.78239649338789</v>
       </c>
       <c r="D38">
-        <v>287.1616983704581</v>
+        <v>283.3873964933879</v>
       </c>
       <c r="E38">
-        <v>-182.82</v>
+        <v>-177.265</v>
       </c>
       <c r="F38">
-        <v>199.98</v>
+        <v>205.535</v>
       </c>
       <c r="G38">
         <v>9.93</v>
@@ -4403,37 +4403,37 @@
         <v>17.3</v>
       </c>
       <c r="M38">
-        <v>47.155284</v>
+        <v>48.465153</v>
       </c>
       <c r="N38">
-        <v>-29.855284</v>
+        <v>-31.165153</v>
       </c>
       <c r="O38">
-        <v>-5.971056800000001</v>
+        <v>-6.233030600000001</v>
       </c>
       <c r="P38">
-        <v>-23.88422720000001</v>
+        <v>-24.9321224</v>
       </c>
       <c r="Q38">
-        <v>41.61577279999999</v>
+        <v>40.5678776</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1082823930278482</v>
+        <v>0.1092741770441633</v>
       </c>
       <c r="T38">
-        <v>1.284703764510683</v>
+        <v>1.305095887756884</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.07337459784994614</v>
+        <v>0.0713915006107584</v>
       </c>
       <c r="W38">
-        <v>0.2184982698269827</v>
+        <v>0.2189658841559832</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.3668729892497307</v>
+        <v>0.356957503053792</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1498601086755366</v>
+        <v>0.1517601086755366</v>
       </c>
       <c r="C39">
-        <v>87.78239649338789</v>
+        <v>78.55102237119942</v>
       </c>
       <c r="D39">
-        <v>283.3873964933879</v>
+        <v>279.7110223711994</v>
       </c>
       <c r="E39">
-        <v>-177.265</v>
+        <v>-171.71</v>
       </c>
       <c r="F39">
-        <v>205.535</v>
+        <v>211.09</v>
       </c>
       <c r="G39">
         <v>9.93</v>
@@ -4485,37 +4485,37 @@
         <v>17.3</v>
       </c>
       <c r="M39">
-        <v>48.465153</v>
+        <v>49.775022</v>
       </c>
       <c r="N39">
-        <v>-31.165153</v>
+        <v>-32.475022</v>
       </c>
       <c r="O39">
-        <v>-6.233030600000001</v>
+        <v>-6.495004400000001</v>
       </c>
       <c r="P39">
-        <v>-24.9321224</v>
+        <v>-25.9800176</v>
       </c>
       <c r="Q39">
-        <v>40.5678776</v>
+        <v>39.5199824</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1092741770441633</v>
+        <v>0.1102979540932627</v>
       </c>
       <c r="T39">
-        <v>1.305095887756884</v>
+        <v>1.326145821430382</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.0713915006107584</v>
+        <v>0.06951277691047529</v>
       </c>
       <c r="W39">
-        <v>0.2189658841559832</v>
+        <v>0.2194088872045099</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.356957503053792</v>
+        <v>0.3475638845523764</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1517601086755366</v>
+        <v>0.1536601086755366</v>
       </c>
       <c r="C40">
-        <v>78.55102237119942</v>
+        <v>69.4138135744179</v>
       </c>
       <c r="D40">
-        <v>279.7110223711994</v>
+        <v>276.1288135744179</v>
       </c>
       <c r="E40">
-        <v>-171.71</v>
+        <v>-166.155</v>
       </c>
       <c r="F40">
-        <v>211.09</v>
+        <v>216.645</v>
       </c>
       <c r="G40">
         <v>9.93</v>
@@ -4567,37 +4567,37 @@
         <v>17.3</v>
       </c>
       <c r="M40">
-        <v>49.775022</v>
+        <v>51.08489100000001</v>
       </c>
       <c r="N40">
-        <v>-32.475022</v>
+        <v>-33.78489100000001</v>
       </c>
       <c r="O40">
-        <v>-6.495004400000001</v>
+        <v>-6.756978200000002</v>
       </c>
       <c r="P40">
-        <v>-25.9800176</v>
+        <v>-27.02791280000001</v>
       </c>
       <c r="Q40">
-        <v>39.5199824</v>
+        <v>38.47208719999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1102979540932627</v>
+        <v>0.1113552976029883</v>
       </c>
       <c r="T40">
-        <v>1.326145821430382</v>
+        <v>1.347885916863667</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.06951277691047529</v>
+        <v>0.0677303980153349</v>
       </c>
       <c r="W40">
-        <v>0.2194088872045099</v>
+        <v>0.2198291721479841</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.3475638845523764</v>
+        <v>0.3386519900766745</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1536601086755366</v>
+        <v>0.1555601086755367</v>
       </c>
       <c r="C41">
-        <v>69.4138135744179</v>
+        <v>60.36719797543955</v>
       </c>
       <c r="D41">
-        <v>276.1288135744179</v>
+        <v>272.6371979754396</v>
       </c>
       <c r="E41">
-        <v>-166.155</v>
+        <v>-160.6</v>
       </c>
       <c r="F41">
-        <v>216.645</v>
+        <v>222.2</v>
       </c>
       <c r="G41">
         <v>9.93</v>
@@ -4649,37 +4649,37 @@
         <v>17.3</v>
       </c>
       <c r="M41">
-        <v>51.08489100000001</v>
+        <v>52.39476000000001</v>
       </c>
       <c r="N41">
-        <v>-33.78489100000001</v>
+        <v>-35.09476000000001</v>
       </c>
       <c r="O41">
-        <v>-6.756978200000002</v>
+        <v>-7.018952000000002</v>
       </c>
       <c r="P41">
-        <v>-27.02791280000001</v>
+        <v>-28.07580800000001</v>
       </c>
       <c r="Q41">
-        <v>38.47208719999999</v>
+        <v>37.42419199999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1113552976029883</v>
+        <v>0.1124478858963714</v>
       </c>
       <c r="T41">
-        <v>1.347885916863667</v>
+        <v>1.370350682144728</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.0677303980153349</v>
+        <v>0.06603713806495153</v>
       </c>
       <c r="W41">
-        <v>0.2198291721479841</v>
+        <v>0.2202284428442844</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.3386519900766745</v>
+        <v>0.3301856903247575</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1555601086755367</v>
+        <v>0.1574601086755366</v>
       </c>
       <c r="C42">
-        <v>60.36719797543955</v>
+        <v>51.40778186704969</v>
       </c>
       <c r="D42">
-        <v>272.6371979754396</v>
+        <v>269.2327818670497</v>
       </c>
       <c r="E42">
-        <v>-160.6</v>
+        <v>-155.045</v>
       </c>
       <c r="F42">
-        <v>222.2</v>
+        <v>227.755</v>
       </c>
       <c r="G42">
         <v>9.93</v>
@@ -4731,37 +4731,37 @@
         <v>17.3</v>
       </c>
       <c r="M42">
-        <v>52.39476000000001</v>
+        <v>53.70462900000001</v>
       </c>
       <c r="N42">
-        <v>-35.09476000000001</v>
+        <v>-36.40462900000001</v>
       </c>
       <c r="O42">
-        <v>-7.018952000000002</v>
+        <v>-7.280925800000003</v>
       </c>
       <c r="P42">
-        <v>-28.07580800000001</v>
+        <v>-29.12370320000001</v>
       </c>
       <c r="Q42">
-        <v>37.42419199999999</v>
+        <v>36.37629679999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1124478858963714</v>
+        <v>0.1135775110810557</v>
       </c>
       <c r="T42">
-        <v>1.370350682144728</v>
+        <v>1.393576964892944</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.06603713806495153</v>
+        <v>0.06442647616092831</v>
       </c>
       <c r="W42">
-        <v>0.2202284428442844</v>
+        <v>0.2206082369212531</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3301856903247575</v>
+        <v>0.3221323808046415</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1574601086755366</v>
+        <v>0.1593601086755367</v>
       </c>
       <c r="C43">
-        <v>51.40778186704969</v>
+        <v>42.53233896014629</v>
       </c>
       <c r="D43">
-        <v>269.2327818670497</v>
+        <v>265.9123389601463</v>
       </c>
       <c r="E43">
-        <v>-155.045</v>
+        <v>-149.49</v>
       </c>
       <c r="F43">
-        <v>227.755</v>
+        <v>233.31</v>
       </c>
       <c r="G43">
         <v>9.93</v>
@@ -4813,37 +4813,37 @@
         <v>17.3</v>
       </c>
       <c r="M43">
-        <v>53.70462900000001</v>
+        <v>55.01449800000001</v>
       </c>
       <c r="N43">
-        <v>-36.40462900000001</v>
+        <v>-37.71449800000001</v>
       </c>
       <c r="O43">
-        <v>-7.280925800000003</v>
+        <v>-7.542899600000003</v>
       </c>
       <c r="P43">
-        <v>-29.12370320000001</v>
+        <v>-30.17159840000001</v>
       </c>
       <c r="Q43">
-        <v>36.37629679999999</v>
+        <v>35.32840159999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1135775110810557</v>
+        <v>0.1147460888583153</v>
       </c>
       <c r="T43">
-        <v>1.393576964892944</v>
+        <v>1.417604153942823</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.06442647616092831</v>
+        <v>0.06289251244281097</v>
       </c>
       <c r="W43">
-        <v>0.2206082369212531</v>
+        <v>0.2209699455659852</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3221323808046415</v>
+        <v>0.3144625622140548</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1593601086755367</v>
+        <v>0.1612601086755366</v>
       </c>
       <c r="C44">
-        <v>42.53233896014632</v>
+        <v>33.73780018569022</v>
       </c>
       <c r="D44">
-        <v>265.9123389601463</v>
+        <v>262.6728001856902</v>
       </c>
       <c r="E44">
-        <v>-149.49</v>
+        <v>-143.935</v>
       </c>
       <c r="F44">
-        <v>233.31</v>
+        <v>238.865</v>
       </c>
       <c r="G44">
         <v>9.93</v>
@@ -4895,37 +4895,37 @@
         <v>17.3</v>
       </c>
       <c r="M44">
-        <v>55.014498</v>
+        <v>56.324367</v>
       </c>
       <c r="N44">
-        <v>-37.71449800000001</v>
+        <v>-39.02436700000001</v>
       </c>
       <c r="O44">
-        <v>-7.542899600000002</v>
+        <v>-7.804873400000002</v>
       </c>
       <c r="P44">
-        <v>-30.1715984</v>
+        <v>-31.2194936</v>
       </c>
       <c r="Q44">
-        <v>35.32840159999999</v>
+        <v>34.28050639999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1147460888583153</v>
+        <v>0.1159556693646015</v>
       </c>
       <c r="T44">
-        <v>1.417604153942823</v>
+        <v>1.442474402257609</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.06289251244281097</v>
+        <v>0.06142989587437351</v>
       </c>
       <c r="W44">
-        <v>0.2209699455659852</v>
+        <v>0.2213148305528227</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3144625622140549</v>
+        <v>0.3071494793718675</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1612601086755366</v>
+        <v>0.1631601086755367</v>
       </c>
       <c r="C45">
-        <v>33.73780018569022</v>
+        <v>25.02124423312281</v>
       </c>
       <c r="D45">
-        <v>262.6728001856902</v>
+        <v>259.5112442331228</v>
       </c>
       <c r="E45">
-        <v>-143.935</v>
+        <v>-138.38</v>
       </c>
       <c r="F45">
-        <v>238.865</v>
+        <v>244.42</v>
       </c>
       <c r="G45">
         <v>9.93</v>
@@ -4977,37 +4977,37 @@
         <v>17.3</v>
       </c>
       <c r="M45">
-        <v>56.324367</v>
+        <v>57.634236</v>
       </c>
       <c r="N45">
-        <v>-39.02436700000001</v>
+        <v>-40.334236</v>
       </c>
       <c r="O45">
-        <v>-7.804873400000002</v>
+        <v>-8.066847200000002</v>
       </c>
       <c r="P45">
-        <v>-31.2194936</v>
+        <v>-32.26738880000001</v>
       </c>
       <c r="Q45">
-        <v>34.28050639999999</v>
+        <v>33.23261119999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1159556693646015</v>
+        <v>0.1172084491746837</v>
       </c>
       <c r="T45">
-        <v>1.442474402257609</v>
+        <v>1.468232873726495</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.06142989587437351</v>
+        <v>0.06003376187722866</v>
       </c>
       <c r="W45">
-        <v>0.2213148305528227</v>
+        <v>0.2216440389493495</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3071494793718675</v>
+        <v>0.3001688093861433</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1631601086755367</v>
+        <v>0.1650601086755367</v>
       </c>
       <c r="C46">
-        <v>25.02124423312281</v>
+        <v>16.37988876394226</v>
       </c>
       <c r="D46">
-        <v>259.5112442331228</v>
+        <v>256.4248887639422</v>
       </c>
       <c r="E46">
-        <v>-138.38</v>
+        <v>-132.825</v>
       </c>
       <c r="F46">
-        <v>244.42</v>
+        <v>249.975</v>
       </c>
       <c r="G46">
         <v>9.93</v>
@@ -5059,37 +5059,37 @@
         <v>17.3</v>
       </c>
       <c r="M46">
-        <v>57.634236</v>
+        <v>58.944105</v>
       </c>
       <c r="N46">
-        <v>-40.334236</v>
+        <v>-41.644105</v>
       </c>
       <c r="O46">
-        <v>-8.066847200000002</v>
+        <v>-8.328821000000001</v>
       </c>
       <c r="P46">
-        <v>-32.26738880000001</v>
+        <v>-33.31528400000001</v>
       </c>
       <c r="Q46">
-        <v>33.23261119999999</v>
+        <v>32.18471599999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1172084491746837</v>
+        <v>0.1185067846142234</v>
       </c>
       <c r="T46">
-        <v>1.468232873726495</v>
+        <v>1.494928016885158</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.06003376187722866</v>
+        <v>0.05869967827995692</v>
       </c>
       <c r="W46">
-        <v>0.2216440389493495</v>
+        <v>0.2219586158615862</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3001688093861433</v>
+        <v>0.2934983913997845</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1650601086755367</v>
+        <v>0.1669601086755367</v>
       </c>
       <c r="C47">
-        <v>16.37988876394226</v>
+        <v>7.811082244888695</v>
       </c>
       <c r="D47">
-        <v>256.4248887639422</v>
+        <v>253.4110822448887</v>
       </c>
       <c r="E47">
-        <v>-132.825</v>
+        <v>-127.27</v>
       </c>
       <c r="F47">
-        <v>249.975</v>
+        <v>255.53</v>
       </c>
       <c r="G47">
         <v>9.93</v>
@@ -5141,37 +5141,37 @@
         <v>17.3</v>
       </c>
       <c r="M47">
-        <v>58.944105</v>
+        <v>60.253974</v>
       </c>
       <c r="N47">
-        <v>-41.644105</v>
+        <v>-42.953974</v>
       </c>
       <c r="O47">
-        <v>-8.328821000000001</v>
+        <v>-8.590794800000001</v>
       </c>
       <c r="P47">
-        <v>-33.31528400000001</v>
+        <v>-34.3631792</v>
       </c>
       <c r="Q47">
-        <v>32.18471599999999</v>
+        <v>31.1368208</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1185067846142234</v>
+        <v>0.1198532065515238</v>
       </c>
       <c r="T47">
-        <v>1.494928016885158</v>
+        <v>1.522611869049698</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.05869967827995692</v>
+        <v>0.05742359831734916</v>
       </c>
       <c r="W47">
-        <v>0.2219586158615862</v>
+        <v>0.2222595155167691</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2934983913997845</v>
+        <v>0.2871179915867458</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1669601086755367</v>
+        <v>0.1688601086755366</v>
       </c>
       <c r="C48">
-        <v>7.811082244888695</v>
+        <v>-0.6877036496439928</v>
       </c>
       <c r="D48">
-        <v>253.4110822448887</v>
+        <v>250.4672963503561</v>
       </c>
       <c r="E48">
-        <v>-127.27</v>
+        <v>-121.715</v>
       </c>
       <c r="F48">
-        <v>255.53</v>
+        <v>261.085</v>
       </c>
       <c r="G48">
         <v>9.93</v>
@@ -5223,37 +5223,37 @@
         <v>17.3</v>
       </c>
       <c r="M48">
-        <v>60.253974</v>
+        <v>61.56384300000001</v>
       </c>
       <c r="N48">
-        <v>-42.953974</v>
+        <v>-44.26384300000002</v>
       </c>
       <c r="O48">
-        <v>-8.590794800000001</v>
+        <v>-8.852768600000003</v>
       </c>
       <c r="P48">
-        <v>-34.3631792</v>
+        <v>-35.41107440000001</v>
       </c>
       <c r="Q48">
-        <v>31.1368208</v>
+        <v>30.08892559999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1198532065515238</v>
+        <v>0.1212504368638167</v>
       </c>
       <c r="T48">
-        <v>1.522611869049698</v>
+        <v>1.551340394880825</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.05742359831734916</v>
+        <v>0.05620181962974596</v>
       </c>
       <c r="W48">
-        <v>0.2222595155167691</v>
+        <v>0.2225476109313059</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2871179915867458</v>
+        <v>0.2810090981487299</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1688601086755366</v>
+        <v>0.1707601086755366</v>
       </c>
       <c r="C49">
-        <v>-0.6877036496439928</v>
+        <v>-9.118881111727262</v>
       </c>
       <c r="D49">
-        <v>250.4672963503561</v>
+        <v>247.5911188882728</v>
       </c>
       <c r="E49">
-        <v>-121.715</v>
+        <v>-116.16</v>
       </c>
       <c r="F49">
-        <v>261.085</v>
+        <v>266.64</v>
       </c>
       <c r="G49">
         <v>9.93</v>
@@ -5305,37 +5305,37 @@
         <v>17.3</v>
       </c>
       <c r="M49">
-        <v>61.56384300000001</v>
+        <v>62.87371200000001</v>
       </c>
       <c r="N49">
-        <v>-44.26384300000002</v>
+        <v>-45.57371200000001</v>
       </c>
       <c r="O49">
-        <v>-8.852768600000003</v>
+        <v>-9.114742400000003</v>
       </c>
       <c r="P49">
-        <v>-35.41107440000001</v>
+        <v>-36.45896960000001</v>
       </c>
       <c r="Q49">
-        <v>30.08892559999999</v>
+        <v>29.04103039999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1212504368638167</v>
+        <v>0.1227014068035055</v>
       </c>
       <c r="T49">
-        <v>1.551340394880825</v>
+        <v>1.581173864013149</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.05620181962974596</v>
+        <v>0.05503094838745959</v>
       </c>
       <c r="W49">
-        <v>0.2225476109313059</v>
+        <v>0.222823702370237</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2810090981487299</v>
+        <v>0.2751547419372979</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1707601086755366</v>
+        <v>0.1726601086755366</v>
       </c>
       <c r="C50">
-        <v>-9.118881111727205</v>
+        <v>-17.48475279214639</v>
       </c>
       <c r="D50">
-        <v>247.5911188882728</v>
+        <v>244.7802472078536</v>
       </c>
       <c r="E50">
-        <v>-116.16</v>
+        <v>-110.605</v>
       </c>
       <c r="F50">
-        <v>266.64</v>
+        <v>272.195</v>
       </c>
       <c r="G50">
         <v>9.93</v>
@@ -5387,37 +5387,37 @@
         <v>17.3</v>
       </c>
       <c r="M50">
-        <v>62.873712</v>
+        <v>64.183581</v>
       </c>
       <c r="N50">
-        <v>-45.573712</v>
+        <v>-46.88358100000001</v>
       </c>
       <c r="O50">
-        <v>-9.114742400000001</v>
+        <v>-9.376716200000002</v>
       </c>
       <c r="P50">
-        <v>-36.4589696</v>
+        <v>-37.5068648</v>
       </c>
       <c r="Q50">
-        <v>29.0410304</v>
+        <v>27.9931352</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1227014068035055</v>
+        <v>0.1242092775251429</v>
       </c>
       <c r="T50">
-        <v>1.581173864013148</v>
+        <v>1.612177273111445</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.0550309483874596</v>
+        <v>0.05390786780812369</v>
       </c>
       <c r="W50">
-        <v>0.222823702370237</v>
+        <v>0.2230885247708444</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2751547419372981</v>
+        <v>0.2695393390406184</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1726601086755366</v>
+        <v>0.1745601086755366</v>
       </c>
       <c r="C51">
-        <v>-17.48475279214639</v>
+        <v>-25.7875179486451</v>
       </c>
       <c r="D51">
-        <v>244.7802472078536</v>
+        <v>242.0324820513549</v>
       </c>
       <c r="E51">
-        <v>-110.605</v>
+        <v>-105.05</v>
       </c>
       <c r="F51">
-        <v>272.195</v>
+        <v>277.75</v>
       </c>
       <c r="G51">
         <v>9.93</v>
@@ -5469,37 +5469,37 @@
         <v>17.3</v>
       </c>
       <c r="M51">
-        <v>64.183581</v>
+        <v>65.49345</v>
       </c>
       <c r="N51">
-        <v>-46.88358100000001</v>
+        <v>-48.19345</v>
       </c>
       <c r="O51">
-        <v>-9.376716200000002</v>
+        <v>-9.63869</v>
       </c>
       <c r="P51">
-        <v>-37.5068648</v>
+        <v>-38.55476</v>
       </c>
       <c r="Q51">
-        <v>27.9931352</v>
+        <v>26.94524</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1242092775251429</v>
+        <v>0.1257774630756457</v>
       </c>
       <c r="T51">
-        <v>1.612177273111445</v>
+        <v>1.644420818573674</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.05390786780812369</v>
+        <v>0.05282971045196122</v>
       </c>
       <c r="W51">
-        <v>0.2230885247708444</v>
+        <v>0.2233427542754275</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2695393390406184</v>
+        <v>0.2641485522598062</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1745601086755366</v>
+        <v>0.1764601086755367</v>
       </c>
       <c r="C52">
-        <v>-25.7875179486451</v>
+        <v>-34.02927818466517</v>
       </c>
       <c r="D52">
-        <v>242.0324820513549</v>
+        <v>239.3457218153348</v>
       </c>
       <c r="E52">
-        <v>-105.05</v>
+        <v>-99.495</v>
       </c>
       <c r="F52">
-        <v>277.75</v>
+        <v>283.305</v>
       </c>
       <c r="G52">
         <v>9.93</v>
@@ -5551,37 +5551,37 @@
         <v>17.3</v>
       </c>
       <c r="M52">
-        <v>65.49345</v>
+        <v>66.803319</v>
       </c>
       <c r="N52">
-        <v>-48.19345</v>
+        <v>-49.503319</v>
       </c>
       <c r="O52">
-        <v>-9.63869</v>
+        <v>-9.900663800000002</v>
       </c>
       <c r="P52">
-        <v>-38.55476</v>
+        <v>-39.6026552</v>
       </c>
       <c r="Q52">
-        <v>26.94524</v>
+        <v>25.8973448</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1257774630756457</v>
+        <v>0.1274096561996385</v>
       </c>
       <c r="T52">
-        <v>1.644420818573674</v>
+        <v>1.677980427115994</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.05282971045196122</v>
+        <v>0.05179383377643257</v>
       </c>
       <c r="W52">
-        <v>0.2233427542754275</v>
+        <v>0.2235870139955172</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2641485522598062</v>
+        <v>0.2589691688821628</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1764601086755367</v>
+        <v>0.1783601086755366</v>
       </c>
       <c r="C53">
-        <v>-34.02927818466517</v>
+        <v>-42.21204281005495</v>
       </c>
       <c r="D53">
-        <v>239.3457218153348</v>
+        <v>236.7179571899451</v>
       </c>
       <c r="E53">
-        <v>-99.495</v>
+        <v>-93.94</v>
       </c>
       <c r="F53">
-        <v>283.305</v>
+        <v>288.86</v>
       </c>
       <c r="G53">
         <v>9.93</v>
@@ -5633,37 +5633,37 @@
         <v>17.3</v>
       </c>
       <c r="M53">
-        <v>66.803319</v>
+        <v>68.11318800000001</v>
       </c>
       <c r="N53">
-        <v>-49.503319</v>
+        <v>-50.81318800000001</v>
       </c>
       <c r="O53">
-        <v>-9.900663800000002</v>
+        <v>-10.1626376</v>
       </c>
       <c r="P53">
-        <v>-39.6026552</v>
+        <v>-40.65055040000001</v>
       </c>
       <c r="Q53">
-        <v>25.8973448</v>
+        <v>24.84944959999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1274096561996385</v>
+        <v>0.1291098573704643</v>
       </c>
       <c r="T53">
-        <v>1.677980427115994</v>
+        <v>1.712938352680911</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.05179383377643257</v>
+        <v>0.05079779851150117</v>
       </c>
       <c r="W53">
-        <v>0.2235870139955172</v>
+        <v>0.2238218791109881</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2589691688821628</v>
+        <v>0.2539889925575058</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1783601086755366</v>
+        <v>0.1802601086755367</v>
       </c>
       <c r="C54">
-        <v>-42.21204281005495</v>
+        <v>-50.33773385248307</v>
       </c>
       <c r="D54">
-        <v>236.7179571899451</v>
+        <v>234.1472661475169</v>
       </c>
       <c r="E54">
-        <v>-93.94</v>
+        <v>-88.38499999999999</v>
       </c>
       <c r="F54">
-        <v>288.86</v>
+        <v>294.415</v>
       </c>
       <c r="G54">
         <v>9.93</v>
@@ -5715,37 +5715,37 @@
         <v>17.3</v>
       </c>
       <c r="M54">
-        <v>68.11318800000001</v>
+        <v>69.42305700000001</v>
       </c>
       <c r="N54">
-        <v>-50.81318800000001</v>
+        <v>-52.12305700000002</v>
       </c>
       <c r="O54">
-        <v>-10.1626376</v>
+        <v>-10.4246114</v>
       </c>
       <c r="P54">
-        <v>-40.65055040000001</v>
+        <v>-41.69844560000001</v>
       </c>
       <c r="Q54">
-        <v>24.84944959999999</v>
+        <v>23.80155439999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1291098573704643</v>
+        <v>0.1308824075272827</v>
       </c>
       <c r="T54">
-        <v>1.712938352680911</v>
+        <v>1.749383849546462</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.05079779851150117</v>
+        <v>0.04983934948298227</v>
       </c>
       <c r="W54">
-        <v>0.2238218791109881</v>
+        <v>0.2240478813919128</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2539889925575058</v>
+        <v>0.2491967474149114</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1802601086755367</v>
+        <v>0.1821601086755367</v>
       </c>
       <c r="C55">
-        <v>-50.33773385248307</v>
+        <v>-58.40819074582444</v>
       </c>
       <c r="D55">
-        <v>234.1472661475169</v>
+        <v>231.6318092541756</v>
       </c>
       <c r="E55">
-        <v>-88.38499999999999</v>
+        <v>-82.82999999999998</v>
       </c>
       <c r="F55">
-        <v>294.415</v>
+        <v>299.97</v>
       </c>
       <c r="G55">
         <v>9.93</v>
@@ -5797,37 +5797,37 @@
         <v>17.3</v>
       </c>
       <c r="M55">
-        <v>69.42305700000001</v>
+        <v>70.73292600000001</v>
       </c>
       <c r="N55">
-        <v>-52.12305700000002</v>
+        <v>-53.43292600000001</v>
       </c>
       <c r="O55">
-        <v>-10.4246114</v>
+        <v>-10.6865852</v>
       </c>
       <c r="P55">
-        <v>-41.69844560000001</v>
+        <v>-42.74634080000001</v>
       </c>
       <c r="Q55">
-        <v>23.80155439999999</v>
+        <v>22.75365919999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1308824075272827</v>
+        <v>0.1327320250822236</v>
       </c>
       <c r="T55">
-        <v>1.749383849546462</v>
+        <v>1.787413933232255</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.04983934948298227</v>
+        <v>0.04891639856663076</v>
       </c>
       <c r="W55">
-        <v>0.2240478813919128</v>
+        <v>0.2242655132179885</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2491967474149114</v>
+        <v>0.2445819928331537</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1821601086755367</v>
+        <v>0.1840601086755367</v>
       </c>
       <c r="C56">
-        <v>-58.40819074582444</v>
+        <v>-66.42517471955296</v>
       </c>
       <c r="D56">
-        <v>231.6318092541756</v>
+        <v>229.1698252804471</v>
       </c>
       <c r="E56">
-        <v>-82.82999999999998</v>
+        <v>-77.27499999999998</v>
       </c>
       <c r="F56">
-        <v>299.97</v>
+        <v>305.525</v>
       </c>
       <c r="G56">
         <v>9.93</v>
@@ -5879,37 +5879,37 @@
         <v>17.3</v>
       </c>
       <c r="M56">
-        <v>70.73292600000001</v>
+        <v>72.04279500000001</v>
       </c>
       <c r="N56">
-        <v>-53.43292600000001</v>
+        <v>-54.74279500000002</v>
       </c>
       <c r="O56">
-        <v>-10.6865852</v>
+        <v>-10.948559</v>
       </c>
       <c r="P56">
-        <v>-42.74634080000001</v>
+        <v>-43.79423600000001</v>
       </c>
       <c r="Q56">
-        <v>22.75365919999999</v>
+        <v>21.70576399999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1327320250822236</v>
+        <v>0.1346638478618286</v>
       </c>
       <c r="T56">
-        <v>1.787413933232255</v>
+        <v>1.827134242859638</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.04891639856663076</v>
+        <v>0.04802700950178292</v>
       </c>
       <c r="W56">
-        <v>0.2242655132179885</v>
+        <v>0.2244752311594796</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2445819928331537</v>
+        <v>0.2401350475089146</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1840601086755367</v>
+        <v>0.1859601086755367</v>
       </c>
       <c r="C57">
-        <v>-66.42517471955296</v>
+        <v>-74.3903729111527</v>
       </c>
       <c r="D57">
-        <v>229.1698252804471</v>
+        <v>226.7596270888473</v>
       </c>
       <c r="E57">
-        <v>-77.27499999999998</v>
+        <v>-71.71999999999997</v>
       </c>
       <c r="F57">
-        <v>305.525</v>
+        <v>311.08</v>
       </c>
       <c r="G57">
         <v>9.93</v>
@@ -5961,37 +5961,37 @@
         <v>17.3</v>
       </c>
       <c r="M57">
-        <v>72.04279500000001</v>
+        <v>73.35266400000002</v>
       </c>
       <c r="N57">
-        <v>-54.74279500000002</v>
+        <v>-56.05266400000002</v>
       </c>
       <c r="O57">
-        <v>-10.948559</v>
+        <v>-11.2105328</v>
       </c>
       <c r="P57">
-        <v>-43.79423600000001</v>
+        <v>-44.84213120000002</v>
       </c>
       <c r="Q57">
-        <v>21.70576399999999</v>
+        <v>20.65786879999998</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1346638478618286</v>
+        <v>0.1366834807677793</v>
       </c>
       <c r="T57">
-        <v>1.827134242859638</v>
+        <v>1.868660021106448</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.04802700950178292</v>
+        <v>0.04716938433210822</v>
       </c>
       <c r="W57">
-        <v>0.2244752311594796</v>
+        <v>0.2246774591744889</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2401350475089146</v>
+        <v>0.2358469216605411</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1859601086755367</v>
+        <v>0.1878601086755367</v>
       </c>
       <c r="C58">
-        <v>-74.3903729111527</v>
+        <v>-82.30540222172641</v>
       </c>
       <c r="D58">
-        <v>226.7596270888473</v>
+        <v>224.3995977782736</v>
       </c>
       <c r="E58">
-        <v>-71.71999999999997</v>
+        <v>-66.16499999999996</v>
       </c>
       <c r="F58">
-        <v>311.08</v>
+        <v>316.635</v>
       </c>
       <c r="G58">
         <v>9.93</v>
@@ -6043,37 +6043,37 @@
         <v>17.3</v>
       </c>
       <c r="M58">
-        <v>73.35266400000002</v>
+        <v>74.66253300000001</v>
       </c>
       <c r="N58">
-        <v>-56.05266400000002</v>
+        <v>-57.36253300000001</v>
       </c>
       <c r="O58">
-        <v>-11.2105328</v>
+        <v>-11.4725066</v>
       </c>
       <c r="P58">
-        <v>-44.84213120000002</v>
+        <v>-45.89002640000001</v>
       </c>
       <c r="Q58">
-        <v>20.65786879999998</v>
+        <v>19.60997359999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1366834807677793</v>
+        <v>0.1387970500879602</v>
       </c>
       <c r="T58">
-        <v>1.868660021106448</v>
+        <v>1.912117230899621</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.04716938433210822</v>
+        <v>0.04634185127365019</v>
       </c>
       <c r="W58">
-        <v>0.2246774591744889</v>
+        <v>0.2248725914696733</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2358469216605411</v>
+        <v>0.2317092563682509</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1878601086755367</v>
+        <v>0.1897601086755367</v>
       </c>
       <c r="C59">
-        <v>-82.30540222172641</v>
+        <v>-90.17181293331745</v>
       </c>
       <c r="D59">
-        <v>224.3995977782736</v>
+        <v>222.0881870666826</v>
       </c>
       <c r="E59">
-        <v>-66.16499999999996</v>
+        <v>-60.60999999999996</v>
       </c>
       <c r="F59">
-        <v>316.635</v>
+        <v>322.1900000000001</v>
       </c>
       <c r="G59">
         <v>9.93</v>
@@ -6125,37 +6125,37 @@
         <v>17.3</v>
       </c>
       <c r="M59">
-        <v>74.66253300000001</v>
+        <v>75.97240200000002</v>
       </c>
       <c r="N59">
-        <v>-57.36253300000001</v>
+        <v>-58.67240200000002</v>
       </c>
       <c r="O59">
-        <v>-11.4725066</v>
+        <v>-11.7344804</v>
       </c>
       <c r="P59">
-        <v>-45.89002640000001</v>
+        <v>-46.93792160000002</v>
       </c>
       <c r="Q59">
-        <v>19.60997359999999</v>
+        <v>18.56207839999998</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1387970500879602</v>
+        <v>0.1410112655662449</v>
       </c>
       <c r="T59">
-        <v>1.912117230899621</v>
+        <v>1.957643831635327</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.04634185127365019</v>
+        <v>0.04554285383789759</v>
       </c>
       <c r="W59">
-        <v>0.2248725914696733</v>
+        <v>0.2250609950650238</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2317092563682509</v>
+        <v>0.227714269189488</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1897601086755366</v>
+        <v>0.1916601086755366</v>
       </c>
       <c r="C60">
-        <v>-90.17181293331734</v>
+        <v>-97.99109210495143</v>
       </c>
       <c r="D60">
-        <v>222.0881870666827</v>
+        <v>219.8239078950486</v>
       </c>
       <c r="E60">
-        <v>-60.61000000000001</v>
+        <v>-55.05500000000001</v>
       </c>
       <c r="F60">
-        <v>322.19</v>
+        <v>327.745</v>
       </c>
       <c r="G60">
         <v>9.93</v>
@@ -6207,37 +6207,37 @@
         <v>17.3</v>
       </c>
       <c r="M60">
-        <v>75.972402</v>
+        <v>77.28227100000001</v>
       </c>
       <c r="N60">
-        <v>-58.67240200000001</v>
+        <v>-59.98227100000001</v>
       </c>
       <c r="O60">
-        <v>-11.7344804</v>
+        <v>-11.9964542</v>
       </c>
       <c r="P60">
-        <v>-46.9379216</v>
+        <v>-47.98581680000001</v>
       </c>
       <c r="Q60">
-        <v>18.5620784</v>
+        <v>17.51418319999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1410112655662449</v>
+        <v>0.1433334915556655</v>
       </c>
       <c r="T60">
-        <v>1.957643831635326</v>
+        <v>2.005391242163017</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.04554285383789761</v>
+        <v>0.04477094106098408</v>
       </c>
       <c r="W60">
-        <v>0.2250609950650238</v>
+        <v>0.22524301209782</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.227714269189488</v>
+        <v>0.2238547053049204</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1916601086755366</v>
+        <v>0.1935601086755366</v>
       </c>
       <c r="C61">
-        <v>-97.99109210495143</v>
+        <v>-105.7646667630309</v>
       </c>
       <c r="D61">
-        <v>219.8239078950486</v>
+        <v>217.6053332369691</v>
       </c>
       <c r="E61">
-        <v>-55.05500000000001</v>
+        <v>-49.5</v>
       </c>
       <c r="F61">
-        <v>327.745</v>
+        <v>333.3</v>
       </c>
       <c r="G61">
         <v>9.93</v>
@@ -6289,37 +6289,37 @@
         <v>17.3</v>
       </c>
       <c r="M61">
-        <v>77.28227100000001</v>
+        <v>78.59214</v>
       </c>
       <c r="N61">
-        <v>-59.98227100000001</v>
+        <v>-61.29214</v>
       </c>
       <c r="O61">
-        <v>-11.9964542</v>
+        <v>-12.258428</v>
       </c>
       <c r="P61">
-        <v>-47.98581680000001</v>
+        <v>-49.033712</v>
       </c>
       <c r="Q61">
-        <v>17.51418319999999</v>
+        <v>16.466288</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1433334915556655</v>
+        <v>0.1457718288445571</v>
       </c>
       <c r="T61">
-        <v>2.005391242163017</v>
+        <v>2.055526023217092</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.04477094106098408</v>
+        <v>0.04402475870996769</v>
       </c>
       <c r="W61">
-        <v>0.22524301209782</v>
+        <v>0.2254189618961896</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2238547053049204</v>
+        <v>0.2201237935498384</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1935601086755366</v>
+        <v>0.1954601086755366</v>
       </c>
       <c r="C62">
-        <v>-105.7646667630309</v>
+        <v>-113.4939069004649</v>
       </c>
       <c r="D62">
-        <v>217.6053332369691</v>
+        <v>215.4310930995351</v>
       </c>
       <c r="E62">
-        <v>-49.5</v>
+        <v>-43.94499999999999</v>
       </c>
       <c r="F62">
-        <v>333.3</v>
+        <v>338.855</v>
       </c>
       <c r="G62">
         <v>9.93</v>
@@ -6371,37 +6371,37 @@
         <v>17.3</v>
       </c>
       <c r="M62">
-        <v>78.59214</v>
+        <v>79.90200900000001</v>
       </c>
       <c r="N62">
-        <v>-61.29214</v>
+        <v>-62.60200900000001</v>
       </c>
       <c r="O62">
-        <v>-12.258428</v>
+        <v>-12.5204018</v>
       </c>
       <c r="P62">
-        <v>-49.033712</v>
+        <v>-50.08160720000001</v>
       </c>
       <c r="Q62">
-        <v>16.466288</v>
+        <v>15.41839279999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1457718288445571</v>
+        <v>0.1483352090713407</v>
       </c>
       <c r="T62">
-        <v>2.055526023217092</v>
+        <v>2.108231818684198</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.04402475870996769</v>
+        <v>0.04330304135406657</v>
       </c>
       <c r="W62">
-        <v>0.2254189618961896</v>
+        <v>0.2255891428487111</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2201237935498384</v>
+        <v>0.2165152067703329</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1954601086755366</v>
+        <v>0.1973601086755367</v>
       </c>
       <c r="C63">
-        <v>-113.4939069004649</v>
+        <v>-121.1801282977798</v>
       </c>
       <c r="D63">
-        <v>215.4310930995351</v>
+        <v>213.2998717022202</v>
       </c>
       <c r="E63">
-        <v>-43.94499999999999</v>
+        <v>-38.38999999999999</v>
       </c>
       <c r="F63">
-        <v>338.855</v>
+        <v>344.41</v>
       </c>
       <c r="G63">
         <v>9.93</v>
@@ -6453,37 +6453,37 @@
         <v>17.3</v>
       </c>
       <c r="M63">
-        <v>79.90200900000001</v>
+        <v>81.21187800000001</v>
       </c>
       <c r="N63">
-        <v>-62.60200900000001</v>
+        <v>-63.91187800000002</v>
       </c>
       <c r="O63">
-        <v>-12.5204018</v>
+        <v>-12.7823756</v>
       </c>
       <c r="P63">
-        <v>-50.08160720000001</v>
+        <v>-51.12950240000001</v>
       </c>
       <c r="Q63">
-        <v>15.41839279999999</v>
+        <v>14.37049759999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1483352090713407</v>
+        <v>0.1510335040469023</v>
       </c>
       <c r="T63">
-        <v>2.108231818684198</v>
+        <v>2.163711603386413</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.04330304135406657</v>
+        <v>0.04260460520319453</v>
       </c>
       <c r="W63">
-        <v>0.2255891428487111</v>
+        <v>0.2257538340930867</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2165152067703329</v>
+        <v>0.2130230260159727</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1973601086755367</v>
+        <v>0.1992601086755367</v>
       </c>
       <c r="C64">
-        <v>-121.1801282977798</v>
+        <v>-128.8245951784187</v>
       </c>
       <c r="D64">
-        <v>213.2998717022202</v>
+        <v>211.2104048215813</v>
       </c>
       <c r="E64">
-        <v>-38.38999999999999</v>
+        <v>-32.83500000000004</v>
       </c>
       <c r="F64">
-        <v>344.41</v>
+        <v>349.965</v>
       </c>
       <c r="G64">
         <v>9.93</v>
@@ -6535,37 +6535,37 @@
         <v>17.3</v>
       </c>
       <c r="M64">
-        <v>81.21187800000001</v>
+        <v>82.52174699999999</v>
       </c>
       <c r="N64">
-        <v>-63.91187800000002</v>
+        <v>-65.22174699999999</v>
       </c>
       <c r="O64">
-        <v>-12.7823756</v>
+        <v>-13.0443494</v>
       </c>
       <c r="P64">
-        <v>-51.12950240000001</v>
+        <v>-52.17739759999999</v>
       </c>
       <c r="Q64">
-        <v>14.37049759999999</v>
+        <v>13.32260240000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1510335040469023</v>
+        <v>0.1538776528049267</v>
       </c>
       <c r="T64">
-        <v>2.163711603386413</v>
+        <v>2.22219029536983</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.04260460520319453</v>
+        <v>0.04192834162854066</v>
       </c>
       <c r="W64">
-        <v>0.2257538340930867</v>
+        <v>0.2259132970439901</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2130230260159727</v>
+        <v>0.2096417081427032</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1992601086755367</v>
+        <v>0.2011601086755367</v>
       </c>
       <c r="C65">
-        <v>-128.8245951784187</v>
+        <v>-136.428522709487</v>
       </c>
       <c r="D65">
-        <v>211.2104048215813</v>
+        <v>209.161477290513</v>
       </c>
       <c r="E65">
-        <v>-32.83500000000004</v>
+        <v>-27.28000000000003</v>
       </c>
       <c r="F65">
-        <v>349.965</v>
+        <v>355.52</v>
       </c>
       <c r="G65">
         <v>9.93</v>
@@ -6617,37 +6617,37 @@
         <v>17.3</v>
       </c>
       <c r="M65">
-        <v>82.52174699999999</v>
+        <v>83.831616</v>
       </c>
       <c r="N65">
-        <v>-65.22174699999999</v>
+        <v>-66.531616</v>
       </c>
       <c r="O65">
-        <v>-13.0443494</v>
+        <v>-13.3063232</v>
       </c>
       <c r="P65">
-        <v>-52.17739759999999</v>
+        <v>-53.2252928</v>
       </c>
       <c r="Q65">
-        <v>13.32260240000001</v>
+        <v>12.2747072</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1538776528049267</v>
+        <v>0.1568798098272858</v>
       </c>
       <c r="T65">
-        <v>2.22219029536983</v>
+        <v>2.283917803574548</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.04192834162854066</v>
+        <v>0.04127321129059471</v>
       </c>
       <c r="W65">
-        <v>0.2259132970439901</v>
+        <v>0.2260677767776778</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2096417081427032</v>
+        <v>0.2063660564529736</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2011601086755367</v>
+        <v>0.2030601086755366</v>
       </c>
       <c r="C66">
-        <v>-136.428522709487</v>
+        <v>-143.9930793583411</v>
       </c>
       <c r="D66">
-        <v>209.161477290513</v>
+        <v>207.1519206416589</v>
       </c>
       <c r="E66">
-        <v>-27.28000000000003</v>
+        <v>-21.72500000000002</v>
       </c>
       <c r="F66">
-        <v>355.52</v>
+        <v>361.075</v>
       </c>
       <c r="G66">
         <v>9.93</v>
@@ -6699,37 +6699,37 @@
         <v>17.3</v>
       </c>
       <c r="M66">
-        <v>83.831616</v>
+        <v>85.141485</v>
       </c>
       <c r="N66">
-        <v>-66.531616</v>
+        <v>-67.84148500000001</v>
       </c>
       <c r="O66">
-        <v>-13.3063232</v>
+        <v>-13.568297</v>
       </c>
       <c r="P66">
-        <v>-53.2252928</v>
+        <v>-54.273188</v>
       </c>
       <c r="Q66">
-        <v>12.2747072</v>
+        <v>11.226812</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1568798098272858</v>
+        <v>0.1600535186794939</v>
       </c>
       <c r="T66">
-        <v>2.283917803574548</v>
+        <v>2.349172597962392</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.04127321129059471</v>
+        <v>0.04063823880920094</v>
       </c>
       <c r="W66">
-        <v>0.2260677767776778</v>
+        <v>0.2262175032887904</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2063660564529736</v>
+        <v>0.2031911940460047</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2030601086755366</v>
+        <v>0.2049601086755367</v>
       </c>
       <c r="C67">
-        <v>-143.9930793583411</v>
+        <v>-151.5193891146209</v>
       </c>
       <c r="D67">
-        <v>207.1519206416589</v>
+        <v>205.1806108853791</v>
       </c>
       <c r="E67">
-        <v>-21.72500000000002</v>
+        <v>-16.17000000000002</v>
       </c>
       <c r="F67">
-        <v>361.075</v>
+        <v>366.63</v>
       </c>
       <c r="G67">
         <v>9.93</v>
@@ -6781,37 +6781,37 @@
         <v>17.3</v>
       </c>
       <c r="M67">
-        <v>85.141485</v>
+        <v>86.45135400000001</v>
       </c>
       <c r="N67">
-        <v>-67.84148500000001</v>
+        <v>-69.15135400000001</v>
       </c>
       <c r="O67">
-        <v>-13.568297</v>
+        <v>-13.8302708</v>
       </c>
       <c r="P67">
-        <v>-54.273188</v>
+        <v>-55.32108320000001</v>
       </c>
       <c r="Q67">
-        <v>11.226812</v>
+        <v>10.17891679999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1600535186794939</v>
+        <v>0.1634139162877143</v>
       </c>
       <c r="T67">
-        <v>2.349172597962392</v>
+        <v>2.418265909667168</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.04063823880920094</v>
+        <v>0.04002250791815243</v>
       </c>
       <c r="W67">
-        <v>0.2262175032887904</v>
+        <v>0.2263626926328997</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2031911940460047</v>
+        <v>0.2001125395907621</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2049601086755367</v>
+        <v>0.2068601086755366</v>
       </c>
       <c r="C68">
-        <v>-151.5193891146209</v>
+        <v>-159.0085335866056</v>
       </c>
       <c r="D68">
-        <v>205.1806108853791</v>
+        <v>203.2464664133944</v>
       </c>
       <c r="E68">
-        <v>-16.17000000000002</v>
+        <v>-10.61500000000001</v>
       </c>
       <c r="F68">
-        <v>366.63</v>
+        <v>372.185</v>
       </c>
       <c r="G68">
         <v>9.93</v>
@@ -6863,37 +6863,37 @@
         <v>17.3</v>
       </c>
       <c r="M68">
-        <v>86.45135400000001</v>
+        <v>87.761223</v>
       </c>
       <c r="N68">
-        <v>-69.15135400000001</v>
+        <v>-70.461223</v>
       </c>
       <c r="O68">
-        <v>-13.8302708</v>
+        <v>-14.0922446</v>
       </c>
       <c r="P68">
-        <v>-55.32108320000001</v>
+        <v>-56.3689784</v>
       </c>
       <c r="Q68">
-        <v>10.17891679999999</v>
+        <v>9.131021599999997</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1634139162877143</v>
+        <v>0.166977974357039</v>
       </c>
       <c r="T68">
-        <v>2.418265909667168</v>
+        <v>2.491546694808598</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.04002250791815243</v>
+        <v>0.03942515705370241</v>
       </c>
       <c r="W68">
-        <v>0.2263626926328997</v>
+        <v>0.226503547966737</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2001125395907621</v>
+        <v>0.197125785268512</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2068601086755366</v>
+        <v>0.2087601086755367</v>
       </c>
       <c r="C69">
-        <v>-159.0085335866056</v>
+        <v>-166.4615539801099</v>
       </c>
       <c r="D69">
-        <v>203.2464664133944</v>
+        <v>201.3484460198901</v>
       </c>
       <c r="E69">
-        <v>-10.61500000000001</v>
+        <v>-5.060000000000002</v>
       </c>
       <c r="F69">
-        <v>372.185</v>
+        <v>377.74</v>
       </c>
       <c r="G69">
         <v>9.93</v>
@@ -6945,37 +6945,37 @@
         <v>17.3</v>
       </c>
       <c r="M69">
-        <v>87.761223</v>
+        <v>89.07109200000001</v>
       </c>
       <c r="N69">
-        <v>-70.461223</v>
+        <v>-71.77109200000001</v>
       </c>
       <c r="O69">
-        <v>-14.0922446</v>
+        <v>-14.3542184</v>
       </c>
       <c r="P69">
-        <v>-56.3689784</v>
+        <v>-57.41687360000001</v>
       </c>
       <c r="Q69">
-        <v>9.131021599999997</v>
+        <v>8.08312639999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.166977974357039</v>
+        <v>0.1707647860556965</v>
       </c>
       <c r="T69">
-        <v>2.491546694808598</v>
+        <v>2.569407529021366</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.03942515705370241</v>
+        <v>0.03884537533232443</v>
       </c>
       <c r="W69">
-        <v>0.226503547966737</v>
+        <v>0.2266402604966379</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.197125785268512</v>
+        <v>0.1942268766616221</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2087601086755367</v>
+        <v>0.2106601086755366</v>
       </c>
       <c r="C70">
-        <v>-166.4615539801099</v>
+        <v>-173.8794529675239</v>
       </c>
       <c r="D70">
-        <v>201.3484460198901</v>
+        <v>199.4855470324761</v>
       </c>
       <c r="E70">
-        <v>-5.060000000000002</v>
+        <v>0.4950000000000045</v>
       </c>
       <c r="F70">
-        <v>377.74</v>
+        <v>383.295</v>
       </c>
       <c r="G70">
         <v>9.93</v>
@@ -7027,37 +7027,37 @@
         <v>17.3</v>
       </c>
       <c r="M70">
-        <v>89.07109200000001</v>
+        <v>90.38096100000001</v>
       </c>
       <c r="N70">
-        <v>-71.77109200000001</v>
+        <v>-73.08096100000002</v>
       </c>
       <c r="O70">
-        <v>-14.3542184</v>
+        <v>-14.6161922</v>
       </c>
       <c r="P70">
-        <v>-57.41687360000001</v>
+        <v>-58.46476880000002</v>
       </c>
       <c r="Q70">
-        <v>8.08312639999999</v>
+        <v>7.035231199999984</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1707647860556965</v>
+        <v>0.1747959081865254</v>
       </c>
       <c r="T70">
-        <v>2.569407529021366</v>
+        <v>2.652291642860765</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.03884537533232443</v>
+        <v>0.03828239887823276</v>
       </c>
       <c r="W70">
-        <v>0.2266402604966379</v>
+        <v>0.2267730103445127</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1942268766616221</v>
+        <v>0.1914119943911639</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2106601086755366</v>
+        <v>0.2125601086755367</v>
       </c>
       <c r="C71">
-        <v>-173.8794529675239</v>
+        <v>-181.263196454051</v>
       </c>
       <c r="D71">
-        <v>199.4855470324761</v>
+        <v>197.656803545949</v>
       </c>
       <c r="E71">
-        <v>0.4950000000000045</v>
+        <v>6.050000000000011</v>
       </c>
       <c r="F71">
-        <v>383.295</v>
+        <v>388.85</v>
       </c>
       <c r="G71">
         <v>9.93</v>
@@ -7109,37 +7109,37 @@
         <v>17.3</v>
       </c>
       <c r="M71">
-        <v>90.38096100000001</v>
+        <v>91.69083000000001</v>
       </c>
       <c r="N71">
-        <v>-73.08096100000002</v>
+        <v>-74.39083000000001</v>
       </c>
       <c r="O71">
-        <v>-14.6161922</v>
+        <v>-14.878166</v>
       </c>
       <c r="P71">
-        <v>-58.46476880000002</v>
+        <v>-59.51266400000001</v>
       </c>
       <c r="Q71">
-        <v>7.035231199999984</v>
+        <v>5.987335999999992</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1747959081865254</v>
+        <v>0.1790957717927429</v>
       </c>
       <c r="T71">
-        <v>2.652291642860765</v>
+        <v>2.740701364289458</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.03828239887823276</v>
+        <v>0.03773550746568658</v>
       </c>
       <c r="W71">
-        <v>0.2267730103445127</v>
+        <v>0.2269019673395911</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1914119943911639</v>
+        <v>0.188677537328433</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2125601086755367</v>
+        <v>0.2144601086755367</v>
       </c>
       <c r="C72">
-        <v>-181.263196454051</v>
+        <v>-188.6137152476774</v>
       </c>
       <c r="D72">
-        <v>197.656803545949</v>
+        <v>195.8612847523227</v>
       </c>
       <c r="E72">
-        <v>6.050000000000011</v>
+        <v>11.60500000000002</v>
       </c>
       <c r="F72">
-        <v>388.85</v>
+        <v>394.405</v>
       </c>
       <c r="G72">
         <v>9.93</v>
@@ -7191,37 +7191,37 @@
         <v>17.3</v>
       </c>
       <c r="M72">
-        <v>91.69083000000001</v>
+        <v>93.00069900000001</v>
       </c>
       <c r="N72">
-        <v>-74.39083000000001</v>
+        <v>-75.70069900000001</v>
       </c>
       <c r="O72">
-        <v>-14.878166</v>
+        <v>-15.1401398</v>
       </c>
       <c r="P72">
-        <v>-59.51266400000001</v>
+        <v>-60.56055920000001</v>
       </c>
       <c r="Q72">
-        <v>5.987335999999992</v>
+        <v>4.939440799999986</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1790957717927429</v>
+        <v>0.1836921777166306</v>
       </c>
       <c r="T72">
-        <v>2.740701364289458</v>
+        <v>2.835208307885646</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.03773550746568658</v>
+        <v>0.03720402144504311</v>
       </c>
       <c r="W72">
-        <v>0.2269019673395911</v>
+        <v>0.2270272917432588</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.188677537328433</v>
+        <v>0.1860201072252156</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2144601086755366</v>
+        <v>0.2163601086755366</v>
       </c>
       <c r="C73">
-        <v>-188.6137152476772</v>
+        <v>-195.9319066389405</v>
       </c>
       <c r="D73">
-        <v>195.8612847523227</v>
+        <v>194.0980933610595</v>
       </c>
       <c r="E73">
-        <v>11.60499999999996</v>
+        <v>17.15999999999997</v>
       </c>
       <c r="F73">
-        <v>394.405</v>
+        <v>399.96</v>
       </c>
       <c r="G73">
         <v>9.93</v>
@@ -7273,37 +7273,37 @@
         <v>17.3</v>
       </c>
       <c r="M73">
-        <v>93.000699</v>
+        <v>94.310568</v>
       </c>
       <c r="N73">
-        <v>-75.700699</v>
+        <v>-77.01056800000001</v>
       </c>
       <c r="O73">
-        <v>-15.1401398</v>
+        <v>-15.4021136</v>
       </c>
       <c r="P73">
-        <v>-60.5605592</v>
+        <v>-61.60845440000001</v>
       </c>
       <c r="Q73">
-        <v>4.9394408</v>
+        <v>3.891545599999993</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1836921777166306</v>
+        <v>0.1886168983493674</v>
       </c>
       <c r="T73">
-        <v>2.835208307885645</v>
+        <v>2.93646574745299</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.03720402144504311</v>
+        <v>0.03668729892497307</v>
       </c>
       <c r="W73">
-        <v>0.2270272917432588</v>
+        <v>0.2271491349134914</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1860201072252156</v>
+        <v>0.1834364946248653</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2163601086755366</v>
+        <v>0.2182601086755366</v>
       </c>
       <c r="C74">
-        <v>-195.9319066389405</v>
+        <v>-203.2186358961312</v>
       </c>
       <c r="D74">
-        <v>194.0980933610595</v>
+        <v>192.3663641038688</v>
       </c>
       <c r="E74">
-        <v>17.15999999999997</v>
+        <v>22.71499999999997</v>
       </c>
       <c r="F74">
-        <v>399.96</v>
+        <v>405.515</v>
       </c>
       <c r="G74">
         <v>9.93</v>
@@ -7355,37 +7355,37 @@
         <v>17.3</v>
       </c>
       <c r="M74">
-        <v>94.310568</v>
+        <v>95.620437</v>
       </c>
       <c r="N74">
-        <v>-77.01056800000001</v>
+        <v>-78.320437</v>
       </c>
       <c r="O74">
-        <v>-15.4021136</v>
+        <v>-15.6640874</v>
       </c>
       <c r="P74">
-        <v>-61.60845440000001</v>
+        <v>-62.6563496</v>
       </c>
       <c r="Q74">
-        <v>3.891545599999993</v>
+        <v>2.843650400000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1886168983493674</v>
+        <v>0.1939064131030477</v>
       </c>
       <c r="T74">
-        <v>2.93646574745299</v>
+        <v>3.045223738099396</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.03668729892497307</v>
+        <v>0.03618473318627481</v>
       </c>
       <c r="W74">
-        <v>0.2271491349134914</v>
+        <v>0.2272676399146764</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1834364946248653</v>
+        <v>0.180923665931374</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2182601086755366</v>
+        <v>0.2201601086755366</v>
       </c>
       <c r="C75">
-        <v>-203.2186358961312</v>
+        <v>-210.4747376811615</v>
       </c>
       <c r="D75">
-        <v>192.3663641038688</v>
+        <v>190.6652623188385</v>
       </c>
       <c r="E75">
-        <v>22.71499999999997</v>
+        <v>28.26999999999998</v>
       </c>
       <c r="F75">
-        <v>405.515</v>
+        <v>411.07</v>
       </c>
       <c r="G75">
         <v>9.93</v>
@@ -7437,37 +7437,37 @@
         <v>17.3</v>
       </c>
       <c r="M75">
-        <v>95.620437</v>
+        <v>96.930306</v>
       </c>
       <c r="N75">
-        <v>-78.320437</v>
+        <v>-79.630306</v>
       </c>
       <c r="O75">
-        <v>-15.6640874</v>
+        <v>-15.9260612</v>
       </c>
       <c r="P75">
-        <v>-62.6563496</v>
+        <v>-63.70424480000001</v>
       </c>
       <c r="Q75">
-        <v>2.843650400000001</v>
+        <v>1.795755199999995</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1939064131030477</v>
+        <v>0.199602813607011</v>
       </c>
       <c r="T75">
-        <v>3.045223738099396</v>
+        <v>3.162347728026297</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.03618473318627481</v>
+        <v>0.0356957503053792</v>
       </c>
       <c r="W75">
-        <v>0.2272676399146764</v>
+        <v>0.2273829420779916</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.180923665931374</v>
+        <v>0.178478751526896</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2201601086755366</v>
+        <v>0.2220601086755367</v>
       </c>
       <c r="C76">
-        <v>-210.4747376811615</v>
+        <v>-217.7010173909687</v>
       </c>
       <c r="D76">
-        <v>190.6652623188385</v>
+        <v>188.9939826090313</v>
       </c>
       <c r="E76">
-        <v>28.26999999999998</v>
+        <v>33.82499999999999</v>
       </c>
       <c r="F76">
-        <v>411.07</v>
+        <v>416.625</v>
       </c>
       <c r="G76">
         <v>9.93</v>
@@ -7519,37 +7519,37 @@
         <v>17.3</v>
       </c>
       <c r="M76">
-        <v>96.930306</v>
+        <v>98.24017500000001</v>
       </c>
       <c r="N76">
-        <v>-79.630306</v>
+        <v>-80.94017500000001</v>
       </c>
       <c r="O76">
-        <v>-15.9260612</v>
+        <v>-16.188035</v>
       </c>
       <c r="P76">
-        <v>-63.70424480000001</v>
+        <v>-64.75214000000001</v>
       </c>
       <c r="Q76">
-        <v>1.795755199999995</v>
+        <v>0.7478599999999886</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.199602813607011</v>
+        <v>0.2057549261512915</v>
       </c>
       <c r="T76">
-        <v>3.162347728026297</v>
+        <v>3.288841637147348</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.0356957503053792</v>
+        <v>0.03521980696797414</v>
       </c>
       <c r="W76">
-        <v>0.2273829420779916</v>
+        <v>0.2274951695169517</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.178478751526896</v>
+        <v>0.1760990348398707</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2220601086755367</v>
+        <v>0.2239601086755366</v>
       </c>
       <c r="C77">
-        <v>-217.7010173909687</v>
+        <v>-224.8982524289841</v>
       </c>
       <c r="D77">
-        <v>188.9939826090313</v>
+        <v>187.3517475710159</v>
       </c>
       <c r="E77">
-        <v>33.82499999999999</v>
+        <v>39.38</v>
       </c>
       <c r="F77">
-        <v>416.625</v>
+        <v>422.18</v>
       </c>
       <c r="G77">
         <v>9.93</v>
@@ -7601,37 +7601,37 @@
         <v>17.3</v>
       </c>
       <c r="M77">
-        <v>98.24017500000001</v>
+        <v>99.550044</v>
       </c>
       <c r="N77">
-        <v>-80.94017500000001</v>
+        <v>-82.250044</v>
       </c>
       <c r="O77">
-        <v>-16.188035</v>
+        <v>-16.4500088</v>
       </c>
       <c r="P77">
-        <v>-64.75214000000001</v>
+        <v>-65.8000352</v>
       </c>
       <c r="Q77">
-        <v>0.7478599999999886</v>
+        <v>-0.3000351999999964</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2057549261512915</v>
+        <v>0.2124197147409286</v>
       </c>
       <c r="T77">
-        <v>3.288841637147348</v>
+        <v>3.425876705361822</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03521980696797414</v>
+        <v>0.03475638845523765</v>
       </c>
       <c r="W77">
-        <v>0.2274951695169517</v>
+        <v>0.227604443602255</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1760990348398707</v>
+        <v>0.1737819422761883</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2239601086755366</v>
+        <v>0.2258601086755366</v>
       </c>
       <c r="C78">
-        <v>-224.8982524289841</v>
+        <v>-232.0671934108817</v>
       </c>
       <c r="D78">
-        <v>187.3517475710159</v>
+        <v>185.7378065891183</v>
       </c>
       <c r="E78">
-        <v>39.38</v>
+        <v>44.935</v>
       </c>
       <c r="F78">
-        <v>422.18</v>
+        <v>427.735</v>
       </c>
       <c r="G78">
         <v>9.93</v>
@@ -7683,37 +7683,37 @@
         <v>17.3</v>
       </c>
       <c r="M78">
-        <v>99.550044</v>
+        <v>100.859913</v>
       </c>
       <c r="N78">
-        <v>-82.250044</v>
+        <v>-83.55991300000001</v>
       </c>
       <c r="O78">
-        <v>-16.4500088</v>
+        <v>-16.7119826</v>
       </c>
       <c r="P78">
-        <v>-65.8000352</v>
+        <v>-66.84793040000001</v>
       </c>
       <c r="Q78">
-        <v>-0.3000351999999964</v>
+        <v>-1.34793040000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2124197147409286</v>
+        <v>0.2196640501644473</v>
       </c>
       <c r="T78">
-        <v>3.425876705361822</v>
+        <v>3.574827866464509</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03475638845523765</v>
+        <v>0.0343050067869878</v>
       </c>
       <c r="W78">
-        <v>0.227604443602255</v>
+        <v>0.2277108793996283</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1737819422761883</v>
+        <v>0.171525033934939</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2258601086755366</v>
+        <v>0.2277601086755366</v>
       </c>
       <c r="C79">
-        <v>-232.0671934108817</v>
+        <v>-239.2085653085398</v>
       </c>
       <c r="D79">
-        <v>185.7378065891183</v>
+        <v>184.1514346914603</v>
       </c>
       <c r="E79">
-        <v>44.935</v>
+        <v>50.49000000000001</v>
       </c>
       <c r="F79">
-        <v>427.735</v>
+        <v>433.29</v>
       </c>
       <c r="G79">
         <v>9.93</v>
@@ -7765,37 +7765,37 @@
         <v>17.3</v>
       </c>
       <c r="M79">
-        <v>100.859913</v>
+        <v>102.169782</v>
       </c>
       <c r="N79">
-        <v>-83.55991300000001</v>
+        <v>-84.86978200000001</v>
       </c>
       <c r="O79">
-        <v>-16.7119826</v>
+        <v>-16.9739564</v>
       </c>
       <c r="P79">
-        <v>-66.84793040000001</v>
+        <v>-67.89582560000001</v>
       </c>
       <c r="Q79">
-        <v>-1.34793040000001</v>
+        <v>-2.395825600000009</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2196640501644473</v>
+        <v>0.2275669615355585</v>
       </c>
       <c r="T79">
-        <v>3.574827866464509</v>
+        <v>3.737320042212896</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.0343050067869878</v>
+        <v>0.03386519900766745</v>
       </c>
       <c r="W79">
-        <v>0.2277108793996283</v>
+        <v>0.227814586073992</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.171525033934939</v>
+        <v>0.1693259950383372</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2277601086755366</v>
+        <v>0.2296601086755367</v>
       </c>
       <c r="C80">
-        <v>-239.2085653085398</v>
+        <v>-246.3230685358745</v>
       </c>
       <c r="D80">
-        <v>184.1514346914603</v>
+        <v>182.5919314641256</v>
       </c>
       <c r="E80">
-        <v>50.49000000000001</v>
+        <v>56.04500000000002</v>
       </c>
       <c r="F80">
-        <v>433.29</v>
+        <v>438.845</v>
       </c>
       <c r="G80">
         <v>9.93</v>
@@ -7847,37 +7847,37 @@
         <v>17.3</v>
       </c>
       <c r="M80">
-        <v>102.169782</v>
+        <v>103.479651</v>
       </c>
       <c r="N80">
-        <v>-84.86978200000001</v>
+        <v>-86.17965100000001</v>
       </c>
       <c r="O80">
-        <v>-16.9739564</v>
+        <v>-17.2359302</v>
       </c>
       <c r="P80">
-        <v>-67.89582560000001</v>
+        <v>-68.94372080000001</v>
       </c>
       <c r="Q80">
-        <v>-2.395825600000009</v>
+        <v>-3.443720800000008</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2275669615355585</v>
+        <v>0.2362225311324899</v>
       </c>
       <c r="T80">
-        <v>3.737320042212896</v>
+        <v>3.915287663270654</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03386519900766745</v>
+        <v>0.0334365256025071</v>
       </c>
       <c r="W80">
-        <v>0.227814586073992</v>
+        <v>0.2279156672629288</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1693259950383372</v>
+        <v>0.1671826280125355</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2296601086755367</v>
+        <v>0.2315601086755367</v>
       </c>
       <c r="C81">
-        <v>-246.3230685358745</v>
+        <v>-253.4113799799646</v>
       </c>
       <c r="D81">
-        <v>182.5919314641256</v>
+        <v>181.0586200200355</v>
       </c>
       <c r="E81">
-        <v>56.04500000000002</v>
+        <v>61.60000000000002</v>
       </c>
       <c r="F81">
-        <v>438.845</v>
+        <v>444.4</v>
       </c>
       <c r="G81">
         <v>9.93</v>
@@ -7929,37 +7929,37 @@
         <v>17.3</v>
       </c>
       <c r="M81">
-        <v>103.479651</v>
+        <v>104.78952</v>
       </c>
       <c r="N81">
-        <v>-86.17965100000001</v>
+        <v>-87.48952000000001</v>
       </c>
       <c r="O81">
-        <v>-17.2359302</v>
+        <v>-17.497904</v>
       </c>
       <c r="P81">
-        <v>-68.94372080000001</v>
+        <v>-69.99161600000001</v>
       </c>
       <c r="Q81">
-        <v>-3.443720800000008</v>
+        <v>-4.491616000000008</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2362225311324899</v>
+        <v>0.2457436576891144</v>
       </c>
       <c r="T81">
-        <v>3.915287663270654</v>
+        <v>4.111052046434186</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.0334365256025071</v>
+        <v>0.03301856903247576</v>
       </c>
       <c r="W81">
-        <v>0.2279156672629288</v>
+        <v>0.2280142214221422</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1671826280125355</v>
+        <v>0.1650928451623788</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2315601086755367</v>
+        <v>0.2334601086755367</v>
       </c>
       <c r="C82">
-        <v>-253.4113799799646</v>
+        <v>-260.4741539806553</v>
       </c>
       <c r="D82">
-        <v>181.0586200200355</v>
+        <v>179.5508460193448</v>
       </c>
       <c r="E82">
-        <v>61.60000000000002</v>
+        <v>67.15500000000003</v>
       </c>
       <c r="F82">
-        <v>444.4</v>
+        <v>449.955</v>
       </c>
       <c r="G82">
         <v>9.93</v>
@@ -8011,37 +8011,37 @@
         <v>17.3</v>
       </c>
       <c r="M82">
-        <v>104.78952</v>
+        <v>106.099389</v>
       </c>
       <c r="N82">
-        <v>-87.48952000000001</v>
+        <v>-88.79938900000002</v>
       </c>
       <c r="O82">
-        <v>-17.497904</v>
+        <v>-17.75987780000001</v>
       </c>
       <c r="P82">
-        <v>-69.99161600000001</v>
+        <v>-71.03951120000002</v>
       </c>
       <c r="Q82">
-        <v>-4.491616000000008</v>
+        <v>-5.539511200000021</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2457436576891144</v>
+        <v>0.2562670080938046</v>
       </c>
       <c r="T82">
-        <v>4.111052046434186</v>
+        <v>4.327423206772829</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03301856903247576</v>
+        <v>0.03261093237775383</v>
       </c>
       <c r="W82">
-        <v>0.2280142214221422</v>
+        <v>0.2281103421453257</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1650928451623788</v>
+        <v>0.1630546618887692</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2334601086755367</v>
+        <v>0.2353601086755367</v>
       </c>
       <c r="C83">
-        <v>-260.4741539806553</v>
+        <v>-267.5120232616208</v>
       </c>
       <c r="D83">
-        <v>179.5508460193448</v>
+        <v>178.0679767383792</v>
       </c>
       <c r="E83">
-        <v>67.15500000000003</v>
+        <v>72.71000000000004</v>
       </c>
       <c r="F83">
-        <v>449.955</v>
+        <v>455.51</v>
       </c>
       <c r="G83">
         <v>9.93</v>
@@ -8093,37 +8093,37 @@
         <v>17.3</v>
       </c>
       <c r="M83">
-        <v>106.099389</v>
+        <v>107.409258</v>
       </c>
       <c r="N83">
-        <v>-88.79938900000002</v>
+        <v>-90.10925800000003</v>
       </c>
       <c r="O83">
-        <v>-17.75987780000001</v>
+        <v>-18.02185160000001</v>
       </c>
       <c r="P83">
-        <v>-71.03951120000002</v>
+        <v>-72.08740640000002</v>
       </c>
       <c r="Q83">
-        <v>-5.539511200000021</v>
+        <v>-6.58740640000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2562670080938046</v>
+        <v>0.2679596196545715</v>
       </c>
       <c r="T83">
-        <v>4.327423206772829</v>
+        <v>4.567835607149096</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03261093237775383</v>
+        <v>0.03221323808046415</v>
       </c>
       <c r="W83">
-        <v>0.2281103421453257</v>
+        <v>0.2282041184606265</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1630546618887692</v>
+        <v>0.1610661904023207</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2353601086755367</v>
+        <v>0.2372601086755367</v>
       </c>
       <c r="C84">
-        <v>-267.5120232616208</v>
+        <v>-274.5255998156676</v>
       </c>
       <c r="D84">
-        <v>178.0679767383792</v>
+        <v>176.6094001843324</v>
       </c>
       <c r="E84">
-        <v>72.71000000000004</v>
+        <v>78.26500000000004</v>
       </c>
       <c r="F84">
-        <v>455.51</v>
+        <v>461.0650000000001</v>
       </c>
       <c r="G84">
         <v>9.93</v>
@@ -8175,37 +8175,37 @@
         <v>17.3</v>
       </c>
       <c r="M84">
-        <v>107.409258</v>
+        <v>108.719127</v>
       </c>
       <c r="N84">
-        <v>-90.10925800000003</v>
+        <v>-91.41912700000002</v>
       </c>
       <c r="O84">
-        <v>-18.02185160000001</v>
+        <v>-18.2838254</v>
       </c>
       <c r="P84">
-        <v>-72.08740640000002</v>
+        <v>-73.13530160000002</v>
       </c>
       <c r="Q84">
-        <v>-6.58740640000002</v>
+        <v>-7.63530160000002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2679596196545715</v>
+        <v>0.2810278325754287</v>
       </c>
       <c r="T84">
-        <v>4.567835607149096</v>
+        <v>4.836531819334338</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03221323808046415</v>
+        <v>0.03182512677828989</v>
       </c>
       <c r="W84">
-        <v>0.2282041184606265</v>
+        <v>0.2282956351056793</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1610661904023207</v>
+        <v>0.1591256338914494</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2372601086755367</v>
+        <v>0.2391601086755367</v>
       </c>
       <c r="C85">
-        <v>-274.5255998156676</v>
+        <v>-281.515475746882</v>
       </c>
       <c r="D85">
-        <v>176.6094001843324</v>
+        <v>175.1745242531181</v>
       </c>
       <c r="E85">
-        <v>78.26500000000004</v>
+        <v>83.82000000000005</v>
       </c>
       <c r="F85">
-        <v>461.0650000000001</v>
+        <v>466.6200000000001</v>
       </c>
       <c r="G85">
         <v>9.93</v>
@@ -8257,37 +8257,37 @@
         <v>17.3</v>
       </c>
       <c r="M85">
-        <v>108.719127</v>
+        <v>110.028996</v>
       </c>
       <c r="N85">
-        <v>-91.41912700000002</v>
+        <v>-92.72899600000002</v>
       </c>
       <c r="O85">
-        <v>-18.2838254</v>
+        <v>-18.5457992</v>
       </c>
       <c r="P85">
-        <v>-73.13530160000002</v>
+        <v>-74.18319680000002</v>
       </c>
       <c r="Q85">
-        <v>-7.63530160000002</v>
+        <v>-8.683196800000019</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2810278325754287</v>
+        <v>0.2957295721113931</v>
       </c>
       <c r="T85">
-        <v>4.836531819334338</v>
+        <v>5.138815058042735</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03182512677828989</v>
+        <v>0.03144625622140548</v>
       </c>
       <c r="W85">
-        <v>0.2282956351056793</v>
+        <v>0.2283849727829926</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1591256338914494</v>
+        <v>0.1572312811070274</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2391601086755366</v>
+        <v>0.2410601086755366</v>
       </c>
       <c r="C86">
-        <v>-281.5154757468819</v>
+        <v>-288.4822240720545</v>
       </c>
       <c r="D86">
-        <v>175.1745242531181</v>
+        <v>173.7627759279455</v>
       </c>
       <c r="E86">
-        <v>83.81999999999999</v>
+        <v>89.375</v>
       </c>
       <c r="F86">
-        <v>466.62</v>
+        <v>472.175</v>
       </c>
       <c r="G86">
         <v>9.93</v>
@@ -8339,37 +8339,37 @@
         <v>17.3</v>
       </c>
       <c r="M86">
-        <v>110.028996</v>
+        <v>111.338865</v>
       </c>
       <c r="N86">
-        <v>-92.72899600000001</v>
+        <v>-94.03886500000002</v>
       </c>
       <c r="O86">
-        <v>-18.5457992</v>
+        <v>-18.807773</v>
       </c>
       <c r="P86">
-        <v>-74.1831968</v>
+        <v>-75.23109200000002</v>
       </c>
       <c r="Q86">
-        <v>-8.683196800000005</v>
+        <v>-9.731092000000018</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2957295721113929</v>
+        <v>0.3123915435854858</v>
       </c>
       <c r="T86">
-        <v>5.138815058042732</v>
+        <v>5.481402728578914</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03144625622140548</v>
+        <v>0.03107630026585954</v>
       </c>
       <c r="W86">
-        <v>0.2283849727829926</v>
+        <v>0.2284722083973103</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1572312811070274</v>
+        <v>0.1553815013292977</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2410601086755366</v>
+        <v>0.2429601086755367</v>
       </c>
       <c r="C87">
-        <v>-288.4822240720545</v>
+        <v>-295.4263994836646</v>
       </c>
       <c r="D87">
-        <v>173.7627759279455</v>
+        <v>172.3736005163354</v>
       </c>
       <c r="E87">
-        <v>89.375</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="F87">
-        <v>472.175</v>
+        <v>477.73</v>
       </c>
       <c r="G87">
         <v>9.93</v>
@@ -8421,37 +8421,37 @@
         <v>17.3</v>
       </c>
       <c r="M87">
-        <v>111.338865</v>
+        <v>112.648734</v>
       </c>
       <c r="N87">
-        <v>-94.03886500000002</v>
+        <v>-95.34873400000001</v>
       </c>
       <c r="O87">
-        <v>-18.807773</v>
+        <v>-19.0697468</v>
       </c>
       <c r="P87">
-        <v>-75.23109200000002</v>
+        <v>-76.2789872</v>
       </c>
       <c r="Q87">
-        <v>-9.731092000000018</v>
+        <v>-10.7789872</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3123915435854858</v>
+        <v>0.3314337966987348</v>
       </c>
       <c r="T87">
-        <v>5.481402728578914</v>
+        <v>5.87293149490598</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03107630026585954</v>
+        <v>0.03071494793718675</v>
       </c>
       <c r="W87">
-        <v>0.2284722083973103</v>
+        <v>0.2285574152764114</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1553815013292977</v>
+        <v>0.1535747396859337</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2429601086755367</v>
+        <v>0.2448601086755366</v>
       </c>
       <c r="C88">
-        <v>-295.4263994836646</v>
+        <v>-302.3485390765532</v>
       </c>
       <c r="D88">
-        <v>172.3736005163354</v>
+        <v>171.0064609234469</v>
       </c>
       <c r="E88">
-        <v>94.93000000000001</v>
+        <v>100.485</v>
       </c>
       <c r="F88">
-        <v>477.73</v>
+        <v>483.285</v>
       </c>
       <c r="G88">
         <v>9.93</v>
@@ -8503,37 +8503,37 @@
         <v>17.3</v>
       </c>
       <c r="M88">
-        <v>112.648734</v>
+        <v>113.958603</v>
       </c>
       <c r="N88">
-        <v>-95.34873400000001</v>
+        <v>-96.65860300000001</v>
       </c>
       <c r="O88">
-        <v>-19.0697468</v>
+        <v>-19.3317206</v>
       </c>
       <c r="P88">
-        <v>-76.2789872</v>
+        <v>-77.32688240000002</v>
       </c>
       <c r="Q88">
-        <v>-10.7789872</v>
+        <v>-11.82688240000002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3314337966987348</v>
+        <v>0.3534056272140221</v>
       </c>
       <c r="T88">
-        <v>5.87293149490598</v>
+        <v>6.324695456052593</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03071494793718675</v>
+        <v>0.0303619025585984</v>
       </c>
       <c r="W88">
-        <v>0.2285574152764114</v>
+        <v>0.2286406633766825</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1535747396859337</v>
+        <v>0.151809512792992</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2448601086755366</v>
+        <v>0.2467601086755366</v>
       </c>
       <c r="C89">
-        <v>-302.3485390765532</v>
+        <v>-309.2491630402889</v>
       </c>
       <c r="D89">
-        <v>171.0064609234469</v>
+        <v>169.660836959711</v>
       </c>
       <c r="E89">
-        <v>100.485</v>
+        <v>106.04</v>
       </c>
       <c r="F89">
-        <v>483.285</v>
+        <v>488.84</v>
       </c>
       <c r="G89">
         <v>9.93</v>
@@ -8585,37 +8585,37 @@
         <v>17.3</v>
       </c>
       <c r="M89">
-        <v>113.958603</v>
+        <v>115.268472</v>
       </c>
       <c r="N89">
-        <v>-96.65860300000001</v>
+        <v>-97.96847200000001</v>
       </c>
       <c r="O89">
-        <v>-19.3317206</v>
+        <v>-19.5936944</v>
       </c>
       <c r="P89">
-        <v>-77.32688240000002</v>
+        <v>-78.3747776</v>
       </c>
       <c r="Q89">
-        <v>-11.82688240000002</v>
+        <v>-12.8747776</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3534056272140221</v>
+        <v>0.3790394294818573</v>
       </c>
       <c r="T89">
-        <v>6.324695456052593</v>
+        <v>6.851753410723643</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.0303619025585984</v>
+        <v>0.03001688093861433</v>
       </c>
       <c r="W89">
-        <v>0.2286406633766825</v>
+        <v>0.2287220194746747</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.151809512792992</v>
+        <v>0.1500844046930716</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2467601086755366</v>
+        <v>0.2486601086755367</v>
       </c>
       <c r="C90">
-        <v>-309.2491630402889</v>
+        <v>-316.1287753191014</v>
       </c>
       <c r="D90">
-        <v>169.660836959711</v>
+        <v>168.3362246808986</v>
       </c>
       <c r="E90">
-        <v>106.04</v>
+        <v>111.595</v>
       </c>
       <c r="F90">
-        <v>488.84</v>
+        <v>494.395</v>
       </c>
       <c r="G90">
         <v>9.93</v>
@@ -8667,37 +8667,37 @@
         <v>17.3</v>
       </c>
       <c r="M90">
-        <v>115.268472</v>
+        <v>116.578341</v>
       </c>
       <c r="N90">
-        <v>-97.96847200000001</v>
+        <v>-99.278341</v>
       </c>
       <c r="O90">
-        <v>-19.5936944</v>
+        <v>-19.8556682</v>
       </c>
       <c r="P90">
-        <v>-78.3747776</v>
+        <v>-79.4226728</v>
       </c>
       <c r="Q90">
-        <v>-12.8747776</v>
+        <v>-13.9226728</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3790394294818573</v>
+        <v>0.409333923071117</v>
       </c>
       <c r="T90">
-        <v>6.851753410723643</v>
+        <v>7.474640084425793</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03001688093861433</v>
+        <v>0.02967961261346136</v>
       </c>
       <c r="W90">
-        <v>0.2287220194746747</v>
+        <v>0.2288015473457458</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1500844046930716</v>
+        <v>0.1483980630673069</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2486601086755367</v>
+        <v>0.2505601086755366</v>
       </c>
       <c r="C91">
-        <v>-316.1287753191014</v>
+        <v>-322.9878642411369</v>
       </c>
       <c r="D91">
-        <v>168.3362246808986</v>
+        <v>167.032135758863</v>
       </c>
       <c r="E91">
-        <v>111.595</v>
+        <v>117.15</v>
       </c>
       <c r="F91">
-        <v>494.395</v>
+        <v>499.95</v>
       </c>
       <c r="G91">
         <v>9.93</v>
@@ -8749,37 +8749,37 @@
         <v>17.3</v>
       </c>
       <c r="M91">
-        <v>116.578341</v>
+        <v>117.88821</v>
       </c>
       <c r="N91">
-        <v>-99.278341</v>
+        <v>-100.58821</v>
       </c>
       <c r="O91">
-        <v>-19.8556682</v>
+        <v>-20.117642</v>
       </c>
       <c r="P91">
-        <v>-79.4226728</v>
+        <v>-80.470568</v>
       </c>
       <c r="Q91">
-        <v>-13.9226728</v>
+        <v>-14.970568</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.409333923071117</v>
+        <v>0.4456873153782288</v>
       </c>
       <c r="T91">
-        <v>7.474640084425793</v>
+        <v>8.222104092868372</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02967961261346136</v>
+        <v>0.02934983913997846</v>
       </c>
       <c r="W91">
-        <v>0.2288015473457458</v>
+        <v>0.2288793079307931</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1483980630673069</v>
+        <v>0.1467491956998923</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2505601086755366</v>
+        <v>0.2524601086755366</v>
       </c>
       <c r="C92">
-        <v>-322.9878642411369</v>
+        <v>-329.8269031186936</v>
       </c>
       <c r="D92">
-        <v>167.032135758863</v>
+        <v>165.7480968813063</v>
       </c>
       <c r="E92">
-        <v>117.15</v>
+        <v>122.705</v>
       </c>
       <c r="F92">
-        <v>499.95</v>
+        <v>505.505</v>
       </c>
       <c r="G92">
         <v>9.93</v>
@@ -8831,37 +8831,37 @@
         <v>17.3</v>
       </c>
       <c r="M92">
-        <v>117.88821</v>
+        <v>119.198079</v>
       </c>
       <c r="N92">
-        <v>-100.58821</v>
+        <v>-101.898079</v>
       </c>
       <c r="O92">
-        <v>-20.117642</v>
+        <v>-20.3796158</v>
       </c>
       <c r="P92">
-        <v>-80.470568</v>
+        <v>-81.51846320000001</v>
       </c>
       <c r="Q92">
-        <v>-14.970568</v>
+        <v>-16.01846320000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4456873153782288</v>
+        <v>0.4901192393091431</v>
       </c>
       <c r="T92">
-        <v>8.222104092868372</v>
+        <v>9.135671214298192</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02934983913997846</v>
+        <v>0.02902731343514353</v>
       </c>
       <c r="W92">
-        <v>0.2288793079307931</v>
+        <v>0.2289553594919932</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1467491956998923</v>
+        <v>0.1451365671757177</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2524601086755366</v>
+        <v>0.2543601086755366</v>
       </c>
       <c r="C93">
-        <v>-329.8269031186936</v>
+        <v>-336.6463508209799</v>
       </c>
       <c r="D93">
-        <v>165.7480968813063</v>
+        <v>164.4836491790201</v>
       </c>
       <c r="E93">
-        <v>122.705</v>
+        <v>128.26</v>
       </c>
       <c r="F93">
-        <v>505.505</v>
+        <v>511.06</v>
       </c>
       <c r="G93">
         <v>9.93</v>
@@ -8913,37 +8913,37 @@
         <v>17.3</v>
       </c>
       <c r="M93">
-        <v>119.198079</v>
+        <v>120.507948</v>
       </c>
       <c r="N93">
-        <v>-101.898079</v>
+        <v>-103.207948</v>
       </c>
       <c r="O93">
-        <v>-20.3796158</v>
+        <v>-20.6415896</v>
       </c>
       <c r="P93">
-        <v>-81.51846320000001</v>
+        <v>-82.5663584</v>
       </c>
       <c r="Q93">
-        <v>-16.01846320000001</v>
+        <v>-17.0663584</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4901192393091431</v>
+        <v>0.5456591442227862</v>
       </c>
       <c r="T93">
-        <v>9.135671214298192</v>
+        <v>10.27763011608547</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02902731343514353</v>
+        <v>0.02871179915867458</v>
       </c>
       <c r="W93">
-        <v>0.2289553594919932</v>
+        <v>0.2290297577583845</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1451365671757177</v>
+        <v>0.1435589957933728</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2543601086755366</v>
+        <v>0.2562601086755367</v>
       </c>
       <c r="C94">
-        <v>-336.6463508209799</v>
+        <v>-343.4466523208561</v>
       </c>
       <c r="D94">
-        <v>164.4836491790201</v>
+        <v>163.2383476791439</v>
       </c>
       <c r="E94">
-        <v>128.26</v>
+        <v>133.815</v>
       </c>
       <c r="F94">
-        <v>511.06</v>
+        <v>516.615</v>
       </c>
       <c r="G94">
         <v>9.93</v>
@@ -8995,37 +8995,37 @@
         <v>17.3</v>
       </c>
       <c r="M94">
-        <v>120.507948</v>
+        <v>121.817817</v>
       </c>
       <c r="N94">
-        <v>-103.207948</v>
+        <v>-104.517817</v>
       </c>
       <c r="O94">
-        <v>-20.6415896</v>
+        <v>-20.9035634</v>
       </c>
       <c r="P94">
-        <v>-82.5663584</v>
+        <v>-83.61425360000001</v>
       </c>
       <c r="Q94">
-        <v>-17.0663584</v>
+        <v>-18.11425360000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5456591442227862</v>
+        <v>0.6170675933974699</v>
       </c>
       <c r="T94">
-        <v>10.27763011608547</v>
+        <v>11.74586298981197</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02871179915867458</v>
+        <v>0.02840307013546302</v>
       </c>
       <c r="W94">
-        <v>0.2290297577583845</v>
+        <v>0.2291025560620578</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1435589957933728</v>
+        <v>0.1420153506773151</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2562601086755367</v>
+        <v>0.2581601086755366</v>
       </c>
       <c r="C95">
-        <v>-343.4466523208561</v>
+        <v>-350.2282392169259</v>
       </c>
       <c r="D95">
-        <v>163.2383476791439</v>
+        <v>162.0117607830742</v>
       </c>
       <c r="E95">
-        <v>133.815</v>
+        <v>139.3700000000001</v>
       </c>
       <c r="F95">
-        <v>516.615</v>
+        <v>522.1700000000001</v>
       </c>
       <c r="G95">
         <v>9.93</v>
@@ -9077,37 +9077,37 @@
         <v>17.3</v>
       </c>
       <c r="M95">
-        <v>121.817817</v>
+        <v>123.127686</v>
       </c>
       <c r="N95">
-        <v>-104.517817</v>
+        <v>-105.827686</v>
       </c>
       <c r="O95">
-        <v>-20.9035634</v>
+        <v>-21.16553720000001</v>
       </c>
       <c r="P95">
-        <v>-83.61425360000001</v>
+        <v>-84.66214880000003</v>
       </c>
       <c r="Q95">
-        <v>-18.11425360000001</v>
+        <v>-19.16214880000003</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6170675933974699</v>
+        <v>0.7122788589637151</v>
       </c>
       <c r="T95">
-        <v>11.74586298981197</v>
+        <v>13.7035068214473</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02840307013546302</v>
+        <v>0.02810090981487298</v>
       </c>
       <c r="W95">
-        <v>0.2291025560620578</v>
+        <v>0.2291738054656529</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1420153506773151</v>
+        <v>0.1405045490743649</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2581601086755366</v>
+        <v>0.2600601086755366</v>
       </c>
       <c r="C96">
-        <v>-350.2282392169259</v>
+        <v>-356.9915302322659</v>
       </c>
       <c r="D96">
-        <v>162.0117607830742</v>
+        <v>160.8034697677342</v>
       </c>
       <c r="E96">
-        <v>139.3700000000001</v>
+        <v>144.925</v>
       </c>
       <c r="F96">
-        <v>522.1700000000001</v>
+        <v>527.725</v>
       </c>
       <c r="G96">
         <v>9.93</v>
@@ -9159,37 +9159,37 @@
         <v>17.3</v>
       </c>
       <c r="M96">
-        <v>123.127686</v>
+        <v>124.437555</v>
       </c>
       <c r="N96">
-        <v>-105.827686</v>
+        <v>-107.137555</v>
       </c>
       <c r="O96">
-        <v>-21.16553720000001</v>
+        <v>-21.42751100000001</v>
       </c>
       <c r="P96">
-        <v>-84.66214880000003</v>
+        <v>-85.71004400000001</v>
       </c>
       <c r="Q96">
-        <v>-19.16214880000003</v>
+        <v>-20.21004400000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7122788589637151</v>
+        <v>0.8455746307564584</v>
       </c>
       <c r="T96">
-        <v>13.7035068214473</v>
+        <v>16.44420818573677</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02810090981487298</v>
+        <v>0.02780511076419011</v>
       </c>
       <c r="W96">
-        <v>0.2291738054656529</v>
+        <v>0.229243554881804</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1405045490743649</v>
+        <v>0.1390255538209506</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2600601086755366</v>
+        <v>0.2619601086755367</v>
       </c>
       <c r="C97">
-        <v>-356.9915302322659</v>
+        <v>-363.7369316910023</v>
       </c>
       <c r="D97">
-        <v>160.8034697677342</v>
+        <v>159.6130683089978</v>
       </c>
       <c r="E97">
-        <v>144.925</v>
+        <v>150.4800000000001</v>
       </c>
       <c r="F97">
-        <v>527.725</v>
+        <v>533.2800000000001</v>
       </c>
       <c r="G97">
         <v>9.93</v>
@@ -9241,37 +9241,37 @@
         <v>17.3</v>
       </c>
       <c r="M97">
-        <v>124.437555</v>
+        <v>125.747424</v>
       </c>
       <c r="N97">
-        <v>-107.137555</v>
+        <v>-108.447424</v>
       </c>
       <c r="O97">
-        <v>-21.42751100000001</v>
+        <v>-21.68948480000001</v>
       </c>
       <c r="P97">
-        <v>-85.71004400000001</v>
+        <v>-86.75793920000002</v>
       </c>
       <c r="Q97">
-        <v>-20.21004400000001</v>
+        <v>-21.25793920000002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8455746307564584</v>
+        <v>1.045518288445574</v>
       </c>
       <c r="T97">
-        <v>16.44420818573677</v>
+        <v>20.55526023217097</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02780511076419011</v>
+        <v>0.02751547419372979</v>
       </c>
       <c r="W97">
-        <v>0.229243554881804</v>
+        <v>0.2293118511851185</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1390255538209506</v>
+        <v>0.137577370968649</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2619601086755366</v>
+        <v>0.2638601086755367</v>
       </c>
       <c r="C98">
-        <v>-363.7369316910022</v>
+        <v>-370.4648379738751</v>
       </c>
       <c r="D98">
-        <v>159.6130683089978</v>
+        <v>158.440162026125</v>
       </c>
       <c r="E98">
-        <v>150.48</v>
+        <v>156.035</v>
       </c>
       <c r="F98">
-        <v>533.28</v>
+        <v>538.835</v>
       </c>
       <c r="G98">
         <v>9.93</v>
@@ -9323,37 +9323,37 @@
         <v>17.3</v>
       </c>
       <c r="M98">
-        <v>125.747424</v>
+        <v>127.057293</v>
       </c>
       <c r="N98">
-        <v>-108.447424</v>
+        <v>-109.757293</v>
       </c>
       <c r="O98">
-        <v>-21.6894848</v>
+        <v>-21.95145860000001</v>
       </c>
       <c r="P98">
-        <v>-86.7579392</v>
+        <v>-87.80583440000001</v>
       </c>
       <c r="Q98">
-        <v>-21.2579392</v>
+        <v>-22.30583440000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.045518288445571</v>
+        <v>1.378757717927428</v>
       </c>
       <c r="T98">
-        <v>20.55526023217091</v>
+        <v>27.40701364289455</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0275154741937298</v>
+        <v>0.02723180951132021</v>
       </c>
       <c r="W98">
-        <v>0.2293118511851185</v>
+        <v>0.2293787393172307</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.137577370968649</v>
+        <v>0.136159047556601</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2638601086755367</v>
+        <v>0.2657601086755367</v>
       </c>
       <c r="C99">
-        <v>-370.4648379738751</v>
+        <v>-377.1756319538632</v>
       </c>
       <c r="D99">
-        <v>158.440162026125</v>
+        <v>157.2843680461368</v>
       </c>
       <c r="E99">
-        <v>156.035</v>
+        <v>161.59</v>
       </c>
       <c r="F99">
-        <v>538.835</v>
+        <v>544.39</v>
       </c>
       <c r="G99">
         <v>9.93</v>
@@ -9405,37 +9405,37 @@
         <v>17.3</v>
       </c>
       <c r="M99">
-        <v>127.057293</v>
+        <v>128.367162</v>
       </c>
       <c r="N99">
-        <v>-109.757293</v>
+        <v>-111.067162</v>
       </c>
       <c r="O99">
-        <v>-21.95145860000001</v>
+        <v>-22.2134324</v>
       </c>
       <c r="P99">
-        <v>-87.80583440000001</v>
+        <v>-88.85372960000001</v>
       </c>
       <c r="Q99">
-        <v>-22.30583440000001</v>
+        <v>-23.35372960000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.378757717927428</v>
+        <v>2.045236576891142</v>
       </c>
       <c r="T99">
-        <v>27.40701364289455</v>
+        <v>41.11052046434182</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02723180951132021</v>
+        <v>0.02695393390406185</v>
       </c>
       <c r="W99">
-        <v>0.2293787393172307</v>
+        <v>0.2294442623854222</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.136159047556601</v>
+        <v>0.1347696695203092</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2657601086755367</v>
+        <v>0.2676601086755366</v>
       </c>
       <c r="C100">
-        <v>-377.1756319538632</v>
+        <v>-383.8696854128809</v>
       </c>
       <c r="D100">
-        <v>157.2843680461368</v>
+        <v>156.1453145871192</v>
       </c>
       <c r="E100">
-        <v>161.59</v>
+        <v>167.145</v>
       </c>
       <c r="F100">
-        <v>544.39</v>
+        <v>549.9450000000001</v>
       </c>
       <c r="G100">
         <v>9.93</v>
@@ -9487,37 +9487,37 @@
         <v>17.3</v>
       </c>
       <c r="M100">
-        <v>128.367162</v>
+        <v>129.677031</v>
       </c>
       <c r="N100">
-        <v>-111.067162</v>
+        <v>-112.377031</v>
       </c>
       <c r="O100">
-        <v>-22.2134324</v>
+        <v>-22.47540620000001</v>
       </c>
       <c r="P100">
-        <v>-88.85372960000001</v>
+        <v>-89.90162480000002</v>
       </c>
       <c r="Q100">
-        <v>-23.35372960000001</v>
+        <v>-24.40162480000002</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.045236576891142</v>
+        <v>4.044673153782283</v>
       </c>
       <c r="T100">
-        <v>41.11052046434182</v>
+        <v>82.22104092868364</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02695393390406185</v>
+        <v>0.02668167194543496</v>
       </c>
       <c r="W100">
-        <v>0.2294442623854222</v>
+        <v>0.2295084617552665</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1347696695203092</v>
+        <v>0.1334083597271748</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2676601086755366</v>
-      </c>
-      <c r="C101">
-        <v>-383.8696854128809</v>
-      </c>
-      <c r="D101">
-        <v>156.1453145871192</v>
-      </c>
-      <c r="E101">
-        <v>167.145</v>
-      </c>
-      <c r="F101">
-        <v>549.9450000000001</v>
-      </c>
-      <c r="G101">
-        <v>9.93</v>
-      </c>
-      <c r="H101">
-        <v>172.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>82.8</v>
-      </c>
-      <c r="K101">
-        <v>65.5</v>
-      </c>
-      <c r="L101">
-        <v>17.3</v>
-      </c>
-      <c r="M101">
-        <v>129.677031</v>
-      </c>
-      <c r="N101">
-        <v>-112.377031</v>
-      </c>
-      <c r="O101">
-        <v>-22.47540620000001</v>
-      </c>
-      <c r="P101">
-        <v>-89.90162480000002</v>
-      </c>
-      <c r="Q101">
-        <v>-24.40162480000002</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.044673153782283</v>
-      </c>
-      <c r="T101">
-        <v>82.22104092868364</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02668167194543496</v>
-      </c>
-      <c r="W101">
-        <v>0.2295084617552665</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1334083597271748</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
